--- a/data/PV_complete_parameters_definition.xlsx
+++ b/data/PV_complete_parameters_definition.xlsx
@@ -16375,13 +16375,13 @@
         <v>2.9348865911421</v>
       </c>
       <c r="I2" t="n">
-        <v>2547279.28976441</v>
+        <v>2547279.289764409</v>
       </c>
       <c r="J2" t="n">
         <v>0.01526095200714532</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8264256458975002</v>
+        <v>0.8264256458975006</v>
       </c>
     </row>
     <row r="3">
@@ -16412,7 +16412,7 @@
         <v>8.152462753172502</v>
       </c>
       <c r="I3" t="n">
-        <v>4245465.482940683</v>
+        <v>4245465.482940682</v>
       </c>
       <c r="J3" t="n">
         <v>0.01373215657536467</v>
@@ -16449,13 +16449,13 @@
         <v>15.9788269962181</v>
       </c>
       <c r="I4" t="n">
-        <v>5943651.676116957</v>
+        <v>5943651.676116955</v>
       </c>
       <c r="J4" t="n">
         <v>0.0128476948598514</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2981745601793406</v>
+        <v>0.2981745601793407</v>
       </c>
     </row>
     <row r="5">
@@ -16486,13 +16486,13 @@
         <v>26.41397932027891</v>
       </c>
       <c r="I5" t="n">
-        <v>7641837.869293231</v>
+        <v>7641837.869293228</v>
       </c>
       <c r="J5" t="n">
         <v>0.01224184464939308</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2209773537634846</v>
+        <v>0.2209773537634847</v>
       </c>
     </row>
     <row r="6">
@@ -16523,7 +16523,7 @@
         <v>39.45791972535491</v>
       </c>
       <c r="I6" t="n">
-        <v>9340024.062469503</v>
+        <v>9340024.062469501</v>
       </c>
       <c r="J6" t="n">
         <v>0.01178843874176854</v>
@@ -16560,13 +16560,13 @@
         <v>55.1106482114461</v>
       </c>
       <c r="I7" t="n">
-        <v>11038210.25564578</v>
+        <v>11038210.25564577</v>
       </c>
       <c r="J7" t="n">
         <v>0.01142999900920052</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1428388202180249</v>
+        <v>0.142838820218025</v>
       </c>
     </row>
     <row r="8">
@@ -16603,7 +16603,7 @@
         <v>0.01113584610178152</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1206077943626458</v>
+        <v>0.1206077943626459</v>
       </c>
     </row>
     <row r="9">
@@ -16640,7 +16640,7 @@
         <v>0.01088781240816079</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1040483319506291</v>
+        <v>0.1040483319506292</v>
       </c>
     </row>
     <row r="10">
@@ -16671,13 +16671,13 @@
         <v>117.7215621558109</v>
       </c>
       <c r="I10" t="n">
-        <v>16132768.8351746</v>
+        <v>16132768.83517459</v>
       </c>
       <c r="J10" t="n">
         <v>0.01067431523357295</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0912703755029113</v>
+        <v>0.09127037550291132</v>
       </c>
     </row>
     <row r="11">
@@ -16708,13 +16708,13 @@
         <v>143.8094429659629</v>
       </c>
       <c r="I11" t="n">
-        <v>17830955.02835087</v>
+        <v>17830955.02835086</v>
       </c>
       <c r="J11" t="n">
         <v>0.01048754992900408</v>
       </c>
       <c r="K11" t="n">
-        <v>0.08113311691453197</v>
+        <v>0.08113311691453198</v>
       </c>
     </row>
   </sheetData>

--- a/data/PV_complete_parameters_definition.xlsx
+++ b/data/PV_complete_parameters_definition.xlsx
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>86.34</v>
+        <v>98.13</v>
       </c>
       <c r="J2" t="n">
-        <v>43.92</v>
+        <v>49.92</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -867,10 +867,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>42.42</v>
+        <v>48.21</v>
       </c>
       <c r="J3" t="n">
-        <v>-43.92</v>
+        <v>-49.92</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>18.73</v>
+        <v>21.28</v>
       </c>
       <c r="J4" t="n">
-        <v>-59.72</v>
+        <v>-67.87</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -977,10 +977,10 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>78.44</v>
+        <v>89.15000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>59.72</v>
+        <v>67.87</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>43.47</v>
+        <v>49.41</v>
       </c>
       <c r="J6" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>42.12</v>
+        <v>47.87</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.35</v>
+        <v>-1.54</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5.34</v>
+        <v>6.07</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.93</v>
+        <v>-3.33</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1197,10 +1197,10 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>8.27</v>
+        <v>9.4</v>
       </c>
       <c r="J9" t="n">
-        <v>2.93</v>
+        <v>3.33</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>93.41</v>
+        <v>106.16</v>
       </c>
       <c r="J10" t="n">
-        <v>53.62</v>
+        <v>60.95</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>39.79</v>
+        <v>45.22</v>
       </c>
       <c r="J11" t="n">
-        <v>-53.62</v>
+        <v>-60.95</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>32.27</v>
+        <v>36.67</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.63</v>
+        <v>-2.99</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>34.9</v>
+        <v>39.66</v>
       </c>
       <c r="J13" t="n">
-        <v>2.63</v>
+        <v>2.99</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>97.55</v>
+        <v>110.86</v>
       </c>
       <c r="J14" t="n">
-        <v>-10.3</v>
+        <v>-11.71</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>107.85</v>
+        <v>122.57</v>
       </c>
       <c r="J15" t="n">
-        <v>10.3</v>
+        <v>11.71</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>38.88</v>
+        <v>44.19</v>
       </c>
       <c r="J16" t="n">
-        <v>15.72</v>
+        <v>17.86</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>23.16</v>
+        <v>26.33</v>
       </c>
       <c r="J17" t="n">
-        <v>-15.72</v>
+        <v>-17.86</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>13.31</v>
+        <v>15.13</v>
       </c>
       <c r="J18" t="n">
-        <v>5.72</v>
+        <v>6.5</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1747,10 +1747,10 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>7.6</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-5.72</v>
+        <v>-6.5</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>74.01000000000001</v>
+        <v>84.11</v>
       </c>
       <c r="J22" t="n">
-        <v>-11.58</v>
+        <v>-13.16</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>85.59</v>
+        <v>97.27</v>
       </c>
       <c r="J23" t="n">
-        <v>11.58</v>
+        <v>13.16</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>60.54</v>
+        <v>68.81</v>
       </c>
       <c r="J24" t="n">
-        <v>39.71</v>
+        <v>45.13</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>20.83</v>
+        <v>23.68</v>
       </c>
       <c r="J25" t="n">
-        <v>-39.71</v>
+        <v>-45.13</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>49.11</v>
+        <v>55.82</v>
       </c>
       <c r="J26" t="n">
-        <v>-85.44</v>
+        <v>-97.09999999999999</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>134.55</v>
+        <v>152.92</v>
       </c>
       <c r="J27" t="n">
-        <v>85.44</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2242,10 +2242,10 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>17.3</v>
+        <v>19.66</v>
       </c>
       <c r="J28" t="n">
-        <v>-8.42</v>
+        <v>-9.57</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>25.72</v>
+        <v>29.23</v>
       </c>
       <c r="J29" t="n">
-        <v>8.42</v>
+        <v>9.57</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>47.46</v>
+        <v>53.94</v>
       </c>
       <c r="J32" t="n">
-        <v>-19.4</v>
+        <v>-22.05</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>66.86</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>19.4</v>
+        <v>22.05</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>40.46</v>
+        <v>45.99</v>
       </c>
       <c r="J36" t="n">
-        <v>-10.08</v>
+        <v>-11.45</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>50.54</v>
+        <v>57.44</v>
       </c>
       <c r="J37" t="n">
-        <v>10.08</v>
+        <v>11.45</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>48.13</v>
+        <v>54.71</v>
       </c>
       <c r="J38" t="n">
-        <v>-45.8</v>
+        <v>-52.06</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2847,10 +2847,10 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>93.94</v>
+        <v>106.76</v>
       </c>
       <c r="J39" t="n">
-        <v>45.8</v>
+        <v>52.06</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>45.88</v>
+        <v>52.14</v>
       </c>
       <c r="J40" t="n">
-        <v>-18.58</v>
+        <v>-21.11</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>64.45999999999999</v>
+        <v>73.25</v>
       </c>
       <c r="J41" t="n">
-        <v>18.58</v>
+        <v>21.11</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>143.35</v>
+        <v>162.92</v>
       </c>
       <c r="J42" t="n">
-        <v>2.03</v>
+        <v>2.31</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>141.32</v>
+        <v>160.61</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.03</v>
+        <v>-2.31</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3122,10 +3122,10 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>34.45</v>
+        <v>39.15</v>
       </c>
       <c r="J44" t="n">
-        <v>34.45</v>
+        <v>39.15</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>-34.45</v>
+        <v>-39.15</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>56.03</v>
+        <v>63.68</v>
       </c>
       <c r="J46" t="n">
-        <v>15.94</v>
+        <v>18.12</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>40.09</v>
+        <v>45.56</v>
       </c>
       <c r="J47" t="n">
-        <v>-15.94</v>
+        <v>-18.12</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -3342,10 +3342,10 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>51.22</v>
+        <v>58.21</v>
       </c>
       <c r="J48" t="n">
-        <v>22.86</v>
+        <v>25.99</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>28.35</v>
+        <v>32.22</v>
       </c>
       <c r="J49" t="n">
-        <v>-22.86</v>
+        <v>-25.99</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>23.99</v>
+        <v>27.27</v>
       </c>
       <c r="J50" t="n">
-        <v>6.99</v>
+        <v>7.95</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>17</v>
+        <v>19.32</v>
       </c>
       <c r="J51" t="n">
-        <v>-6.99</v>
+        <v>-7.95</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -3562,10 +3562,10 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>167.49</v>
+        <v>190.36</v>
       </c>
       <c r="J52" t="n">
-        <v>77.02</v>
+        <v>87.53</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>90.48</v>
+        <v>102.83</v>
       </c>
       <c r="J53" t="n">
-        <v>-77.02</v>
+        <v>-87.53</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>105.75</v>
+        <v>120.18</v>
       </c>
       <c r="J54" t="n">
-        <v>41.59</v>
+        <v>47.27</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>64.15000000000001</v>
+        <v>72.91</v>
       </c>
       <c r="J55" t="n">
-        <v>-41.59</v>
+        <v>-47.27</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>45.28</v>
+        <v>51.46</v>
       </c>
       <c r="J56" t="n">
-        <v>-2.33</v>
+        <v>-2.65</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>47.61</v>
+        <v>54.11</v>
       </c>
       <c r="J57" t="n">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>15.64</v>
+        <v>17.78</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.88</v>
+        <v>-2.14</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>17.52</v>
+        <v>19.92</v>
       </c>
       <c r="J59" t="n">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>-25.57</v>
+        <v>-29.06</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -4057,10 +4057,10 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>25.57</v>
+        <v>29.06</v>
       </c>
       <c r="J61" t="n">
-        <v>25.57</v>
+        <v>29.06</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -4112,10 +4112,10 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>44.75</v>
+        <v>50.86</v>
       </c>
       <c r="J62" t="n">
-        <v>-63.93</v>
+        <v>-72.66</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>108.68</v>
+        <v>123.51</v>
       </c>
       <c r="J63" t="n">
-        <v>63.93</v>
+        <v>72.66</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>76.04000000000001</v>
+        <v>86.42</v>
       </c>
       <c r="J64" t="n">
-        <v>-44.3</v>
+        <v>-50.35</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>120.34</v>
+        <v>136.76</v>
       </c>
       <c r="J65" t="n">
-        <v>44.3</v>
+        <v>50.35</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -4442,10 +4442,10 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>43.02</v>
+        <v>48.89</v>
       </c>
       <c r="J68" t="n">
-        <v>-85.44</v>
+        <v>-97.09999999999999</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -4497,10 +4497,10 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>128.46</v>
+        <v>146</v>
       </c>
       <c r="J69" t="n">
-        <v>85.44</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -4552,10 +4552,10 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>19.25</v>
+        <v>21.88</v>
       </c>
       <c r="J70" t="n">
-        <v>-4.14</v>
+        <v>-4.7</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>23.39</v>
+        <v>26.58</v>
       </c>
       <c r="J71" t="n">
-        <v>4.14</v>
+        <v>4.7</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -4662,10 +4662,10 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>49.79</v>
+        <v>56.59</v>
       </c>
       <c r="J72" t="n">
-        <v>-18.35</v>
+        <v>-20.86</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>68.14</v>
+        <v>77.44</v>
       </c>
       <c r="J73" t="n">
-        <v>18.35</v>
+        <v>20.86</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>95.06999999999999</v>
+        <v>108.04</v>
       </c>
       <c r="J74" t="n">
-        <v>78.37</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>16.7</v>
+        <v>18.98</v>
       </c>
       <c r="J75" t="n">
-        <v>-78.37</v>
+        <v>-89.06999999999999</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>102.06</v>
+        <v>115.99</v>
       </c>
       <c r="J78" t="n">
-        <v>17.07</v>
+        <v>19.4</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -5047,10 +5047,10 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>84.98999999999999</v>
+        <v>96.59</v>
       </c>
       <c r="J79" t="n">
-        <v>-17.07</v>
+        <v>-19.4</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>10</v>
+        <v>11.37</v>
       </c>
       <c r="J80" t="n">
-        <v>8.869999999999999</v>
+        <v>10.09</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -5157,10 +5157,10 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.869999999999999</v>
+        <v>-10.09</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -5212,10 +5212,10 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>34.9</v>
+        <v>39.66</v>
       </c>
       <c r="J82" t="n">
-        <v>17.15</v>
+        <v>19.49</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>17.75</v>
+        <v>20.17</v>
       </c>
       <c r="J83" t="n">
-        <v>-17.15</v>
+        <v>-19.49</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -5322,10 +5322,10 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>39.79</v>
+        <v>45.22</v>
       </c>
       <c r="J84" t="n">
-        <v>-57.99</v>
+        <v>-65.90000000000001</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -5377,10 +5377,10 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>97.77</v>
+        <v>111.12</v>
       </c>
       <c r="J85" t="n">
-        <v>57.99</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>66.56</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="J86" t="n">
-        <v>41.59</v>
+        <v>47.27</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>24.97</v>
+        <v>28.38</v>
       </c>
       <c r="J87" t="n">
-        <v>-41.59</v>
+        <v>-47.27</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -5542,10 +5542,10 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>61.15</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="J88" t="n">
-        <v>17.3</v>
+        <v>19.66</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>43.85</v>
+        <v>49.83</v>
       </c>
       <c r="J89" t="n">
-        <v>-17.3</v>
+        <v>-19.66</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -5652,10 +5652,10 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>71.83</v>
+        <v>81.63</v>
       </c>
       <c r="J90" t="n">
-        <v>43.55</v>
+        <v>49.49</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -5707,10 +5707,10 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>28.28</v>
+        <v>32.14</v>
       </c>
       <c r="J91" t="n">
-        <v>-43.55</v>
+        <v>-49.49</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -5762,10 +5762,10 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>33.92</v>
+        <v>38.55</v>
       </c>
       <c r="J92" t="n">
-        <v>-1.43</v>
+        <v>-1.62</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>35.35</v>
+        <v>40.17</v>
       </c>
       <c r="J93" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>72.73</v>
+        <v>82.66</v>
       </c>
       <c r="J94" t="n">
-        <v>30.01</v>
+        <v>34.11</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>42.72</v>
+        <v>48.55</v>
       </c>
       <c r="J95" t="n">
-        <v>-30.01</v>
+        <v>-34.11</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -5982,10 +5982,10 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>49.19</v>
+        <v>55.9</v>
       </c>
       <c r="J96" t="n">
-        <v>-4.29</v>
+        <v>-4.87</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -6037,10 +6037,10 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>53.47</v>
+        <v>60.77</v>
       </c>
       <c r="J97" t="n">
-        <v>4.29</v>
+        <v>4.87</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -6092,10 +6092,10 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>106.05</v>
+        <v>120.52</v>
       </c>
       <c r="J98" t="n">
-        <v>44.52</v>
+        <v>50.6</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>61.52</v>
+        <v>69.92</v>
       </c>
       <c r="J99" t="n">
-        <v>-44.52</v>
+        <v>-50.6</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -6202,10 +6202,10 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>71.22</v>
+        <v>80.95</v>
       </c>
       <c r="J100" t="n">
-        <v>-18.73</v>
+        <v>-21.28</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>89.95</v>
+        <v>102.23</v>
       </c>
       <c r="J101" t="n">
-        <v>18.73</v>
+        <v>21.28</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -6312,10 +6312,10 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>40.39</v>
+        <v>45.9</v>
       </c>
       <c r="J102" t="n">
-        <v>-8.42</v>
+        <v>-9.57</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>48.81</v>
+        <v>55.47</v>
       </c>
       <c r="J103" t="n">
-        <v>8.42</v>
+        <v>9.57</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -6422,10 +6422,10 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>79.27</v>
+        <v>90.09</v>
       </c>
       <c r="J104" t="n">
-        <v>-25.72</v>
+        <v>-29.23</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -6477,10 +6477,10 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>104.99</v>
+        <v>119.33</v>
       </c>
       <c r="J105" t="n">
-        <v>25.72</v>
+        <v>29.23</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -6532,10 +6532,10 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>92.06</v>
+        <v>104.62</v>
       </c>
       <c r="J106" t="n">
-        <v>13.91</v>
+        <v>15.81</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>78.14</v>
+        <v>88.81</v>
       </c>
       <c r="J107" t="n">
-        <v>-13.91</v>
+        <v>-15.81</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -6814,52 +6814,52 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(249.85, 349.96)</t>
+          <t>(194.15, 271.94)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(134.89, 188.94)</t>
+          <t>(104.82, 146.81)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>(90.15, 126.26)</t>
+          <t>(70.04, 98.11)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>(66.81, 93.58)</t>
+          <t>(51.91, 72.71)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(52.64, 73.73)</t>
+          <t>(40.9, 57.28)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>(43.18, 60.49)</t>
+          <t>(33.55, 47.0)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>(36.46, 51.07)</t>
+          <t>(28.33, 39.68)</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>(31.46, 44.06)</t>
+          <t>(24.44, 34.23)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>(27.59, 38.65)</t>
+          <t>(21.44, 30.03)</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>(24.53, 34.36)</t>
+          <t>(19.06, 26.69)</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -6882,52 +6882,52 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>(100.1, 349.96)</t>
+          <t>(77.79, 271.94)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>(54.05, 188.94)</t>
+          <t>(41.99, 146.81)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>(36.12, 126.26)</t>
+          <t>(28.06, 98.11)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>(26.77, 93.58)</t>
+          <t>(20.8, 72.71)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(21.09, 73.73)</t>
+          <t>(16.39, 57.28)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>(17.3, 60.49)</t>
+          <t>(13.44, 47.0)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>(14.61, 51.07)</t>
+          <t>(11.35, 39.68)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>(12.6, 44.06)</t>
+          <t>(9.79, 34.23)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>(11.06, 38.65)</t>
+          <t>(8.59, 30.03)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>(9.83, 34.36)</t>
+          <t>(7.64, 26.69)</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -6950,52 +6950,52 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(289.42, 406.02)</t>
+          <t>(224.9, 315.51)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>(156.26, 219.21)</t>
+          <t>(121.41, 170.33)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>(104.42, 146.49)</t>
+          <t>(81.14, 113.82)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>(77.39, 108.57)</t>
+          <t>(60.13, 84.35)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(60.97, 85.54)</t>
+          <t>(47.37, 66.46)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>(50.02, 70.18)</t>
+          <t>(38.87, 54.52)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>(42.24, 59.25)</t>
+          <t>(32.82, 46.04)</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>(36.44, 51.12)</t>
+          <t>(28.31, 39.72)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>(31.96, 44.84)</t>
+          <t>(24.83, 34.84)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>(28.41, 39.86)</t>
+          <t>(22.08, 30.97)</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -7018,52 +7018,52 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(115.77, 406.02)</t>
+          <t>(89.96, 315.51)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>(62.5, 219.21)</t>
+          <t>(48.56, 170.33)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>(41.77, 146.49)</t>
+          <t>(32.45, 113.82)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>(30.95, 108.57)</t>
+          <t>(24.05, 84.35)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(24.39, 85.54)</t>
+          <t>(18.95, 66.46)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>(20.01, 70.18)</t>
+          <t>(15.55, 54.52)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>(16.89, 59.25)</t>
+          <t>(13.13, 46.04)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>(14.58, 51.12)</t>
+          <t>(11.32, 39.72)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>(12.79, 44.84)</t>
+          <t>(9.93, 34.84)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>(11.37, 39.86)</t>
+          <t>(8.83, 30.97)</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -7086,52 +7086,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>(99.25, 370.92)</t>
+          <t>(77.12, 288.23)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(53.58, 200.26)</t>
+          <t>(41.63, 155.61)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>(35.81, 133.83)</t>
+          <t>(27.82, 103.98)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>(26.54, 99.18)</t>
+          <t>(20.62, 77.06)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(20.91, 78.14)</t>
+          <t>(16.24, 60.71)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>(17.15, 64.11)</t>
+          <t>(13.33, 49.81)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>(14.48, 54.13)</t>
+          <t>(11.25, 42.06)</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>(12.5, 46.7)</t>
+          <t>(9.71, 36.28)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>(10.96, 40.96)</t>
+          <t>(8.52, 31.83)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>(9.74, 36.41)</t>
+          <t>(7.57, 28.29)</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -7154,52 +7154,52 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>(271.68, 370.92)</t>
+          <t>(211.11, 288.23)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>(146.68, 200.26)</t>
+          <t>(113.97, 155.61)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>(98.02, 133.83)</t>
+          <t>(76.16, 103.98)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>(72.64, 99.18)</t>
+          <t>(56.44, 77.06)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(57.23, 78.14)</t>
+          <t>(44.47, 60.71)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>(46.96, 64.11)</t>
+          <t>(36.48, 49.81)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>(39.65, 54.13)</t>
+          <t>(30.81, 42.06)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>(34.2, 46.7)</t>
+          <t>(26.58, 36.28)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>(30.0, 40.96)</t>
+          <t>(23.31, 31.83)</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>(26.67, 36.41)</t>
+          <t>(20.72, 28.29)</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -7222,52 +7222,52 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>(9.14, 56.9)</t>
+          <t>(7.1, 44.21)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(4.93, 30.72)</t>
+          <t>(3.83, 23.87)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>(3.3, 20.53)</t>
+          <t>(2.56, 15.95)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>(2.44, 15.21)</t>
+          <t>(1.9, 11.82)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(1.93, 11.99)</t>
+          <t>(1.5, 9.31)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>(1.58, 9.83)</t>
+          <t>(1.23, 7.64)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>(1.33, 8.3)</t>
+          <t>(1.04, 6.45)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>(1.15, 7.16)</t>
+          <t>(0.89, 5.57)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>(1.01, 6.28)</t>
+          <t>(0.78, 4.88)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>(0.9, 5.59)</t>
+          <t>(0.7, 4.34)</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -7290,52 +7290,52 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>(47.76, 56.9)</t>
+          <t>(37.11, 44.21)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>(25.78, 30.72)</t>
+          <t>(20.04, 23.87)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>(17.23, 20.53)</t>
+          <t>(13.39, 15.95)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>(12.77, 15.21)</t>
+          <t>(9.92, 11.82)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(10.06, 11.99)</t>
+          <t>(7.82, 9.31)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>(8.25, 9.83)</t>
+          <t>(6.41, 7.64)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>(6.97, 8.3)</t>
+          <t>(5.42, 6.45)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>(6.01, 7.16)</t>
+          <t>(4.67, 5.57)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>(5.27, 6.28)</t>
+          <t>(4.1, 4.88)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>(4.69, 5.59)</t>
+          <t>(3.64, 4.34)</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -7358,52 +7358,52 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>(82.42, 125.08)</t>
+          <t>(64.05, 97.2)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>(44.5, 67.53)</t>
+          <t>(34.58, 52.47)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>(29.74, 45.13)</t>
+          <t>(23.11, 35.06)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>(22.04, 33.44)</t>
+          <t>(17.12, 25.99)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(17.36, 26.35)</t>
+          <t>(13.49, 20.47)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>(14.25, 21.62)</t>
+          <t>(11.07, 16.8)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>(12.03, 18.25)</t>
+          <t>(9.35, 14.18)</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>(10.38, 15.75)</t>
+          <t>(8.06, 12.24)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>(9.1, 13.81)</t>
+          <t>(7.07, 10.73)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>(8.09, 12.28)</t>
+          <t>(6.29, 9.54)</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -7426,52 +7426,52 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>(42.66, 125.08)</t>
+          <t>(33.15, 97.2)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>(23.03, 67.53)</t>
+          <t>(17.9, 52.47)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>(15.39, 45.13)</t>
+          <t>(11.96, 35.06)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>(11.41, 33.44)</t>
+          <t>(8.86, 25.99)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(8.99, 26.35)</t>
+          <t>(6.98, 20.47)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>(7.37, 21.62)</t>
+          <t>(5.73, 16.8)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>(6.23, 18.25)</t>
+          <t>(4.84, 14.18)</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>(5.37, 15.75)</t>
+          <t>(4.17, 12.24)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>(4.71, 13.81)</t>
+          <t>(3.66, 10.73)</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>(4.19, 12.28)</t>
+          <t>(3.25, 9.54)</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -7494,52 +7494,52 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>(54.29, 66.3)</t>
+          <t>(42.19, 51.52)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>(29.31, 35.8)</t>
+          <t>(22.77, 27.82)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>(19.59, 23.92)</t>
+          <t>(15.22, 18.59)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>(14.52, 17.73)</t>
+          <t>(11.28, 13.78)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(11.44, 13.97)</t>
+          <t>(8.89, 10.85)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>(9.38, 11.46)</t>
+          <t>(7.29, 8.9)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>(7.92, 9.68)</t>
+          <t>(6.16, 7.52)</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>(6.83, 8.35)</t>
+          <t>(5.31, 6.49)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>(6.0, 7.32)</t>
+          <t>(4.66, 5.69)</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>(5.33, 6.51)</t>
+          <t>(4.14, 5.06)</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -7562,52 +7562,52 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>(12.02, 66.3)</t>
+          <t>(9.34, 51.52)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(6.49, 35.8)</t>
+          <t>(5.04, 27.82)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>(4.34, 23.92)</t>
+          <t>(3.37, 18.59)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>(3.21, 17.73)</t>
+          <t>(2.5, 13.78)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(2.53, 13.97)</t>
+          <t>(1.97, 10.85)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>(2.08, 11.46)</t>
+          <t>(1.61, 8.9)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>(1.75, 9.68)</t>
+          <t>(1.36, 7.52)</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>(1.51, 8.35)</t>
+          <t>(1.18, 6.49)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>(1.33, 7.32)</t>
+          <t>(1.03, 5.69)</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>(1.18, 6.51)</t>
+          <t>(0.92, 5.06)</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -7630,52 +7630,52 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>(290.11, 428.14)</t>
+          <t>(225.43, 332.69)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>(156.63, 231.15)</t>
+          <t>(121.7, 179.61)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>(104.67, 154.47)</t>
+          <t>(81.33, 120.02)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>(77.57, 114.48)</t>
+          <t>(60.27, 88.95)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(61.12, 90.2)</t>
+          <t>(47.49, 70.08)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>(50.14, 74.0)</t>
+          <t>(38.96, 57.49)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>(42.34, 62.48)</t>
+          <t>(32.89, 48.55)</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>(36.53, 53.9)</t>
+          <t>(28.38, 41.88)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>(32.04, 47.28)</t>
+          <t>(24.89, 36.74)</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>(28.48, 42.03)</t>
+          <t>(22.13, 32.66)</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -7698,52 +7698,52 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>(138.03, 428.14)</t>
+          <t>(107.26, 332.69)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>(74.52, 231.15)</t>
+          <t>(57.9, 179.61)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>(49.8, 154.47)</t>
+          <t>(38.7, 120.02)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>(36.91, 114.48)</t>
+          <t>(28.68, 88.95)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(29.08, 90.2)</t>
+          <t>(22.59, 70.08)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>(23.86, 74.0)</t>
+          <t>(18.54, 57.49)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>(20.14, 62.48)</t>
+          <t>(15.65, 48.55)</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>(17.38, 53.9)</t>
+          <t>(13.5, 41.88)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>(15.24, 47.28)</t>
+          <t>(11.84, 36.74)</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>(13.55, 42.03)</t>
+          <t>(10.53, 32.66)</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -7766,52 +7766,52 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>(398.57, 400.63)</t>
+          <t>(309.72, 311.32)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>(215.18, 216.3)</t>
+          <t>(167.2, 168.07)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>(143.8, 144.55)</t>
+          <t>(111.73, 112.31)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>(106.57, 107.13)</t>
+          <t>(82.8, 83.23)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(83.97, 84.4)</t>
+          <t>(65.24, 65.58)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>(68.89, 69.25)</t>
+          <t>(53.52, 53.8)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>(58.17, 58.47)</t>
+          <t>(45.19, 45.43)</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>(50.18, 50.44)</t>
+          <t>(38.99, 39.19)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>(44.02, 44.25)</t>
+          <t>(34.2, 34.38)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>(39.13, 39.33)</t>
+          <t>(30.4, 30.56)</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -7834,52 +7834,52 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>(2.07, 400.63)</t>
+          <t>(1.61, 311.32)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>(1.12, 216.3)</t>
+          <t>(0.87, 168.07)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>(0.75, 144.55)</t>
+          <t>(0.58, 112.31)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>(0.55, 107.13)</t>
+          <t>(0.43, 83.23)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(0.44, 84.4)</t>
+          <t>(0.34, 65.58)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>(0.36, 69.25)</t>
+          <t>(0.28, 53.8)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>(0.3, 58.47)</t>
+          <t>(0.23, 45.43)</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>(0.26, 50.44)</t>
+          <t>(0.2, 39.19)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>(0.23, 44.25)</t>
+          <t>(0.18, 34.38)</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>(0.2, 39.33)</t>
+          <t>(0.16, 30.56)</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -7902,52 +7902,52 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>(7.45, 117.13)</t>
+          <t>(5.79, 91.02)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>(4.02, 63.24)</t>
+          <t>(3.12, 49.14)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>(2.69, 42.26)</t>
+          <t>(2.09, 32.84)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>(1.99, 31.32)</t>
+          <t>(1.55, 24.33)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(1.57, 24.68)</t>
+          <t>(1.22, 19.17)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>(1.29, 20.24)</t>
+          <t>(1.0, 15.73)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>(1.09, 17.09)</t>
+          <t>(0.84, 13.28)</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>(0.94, 14.75)</t>
+          <t>(0.73, 11.46)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>(0.82, 12.94)</t>
+          <t>(0.64, 10.05)</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>(0.73, 11.5)</t>
+          <t>(0.57, 8.93)</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -7970,52 +7970,52 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>(109.67, 117.13)</t>
+          <t>(85.23, 91.02)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>(59.21, 63.24)</t>
+          <t>(46.01, 49.14)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>(39.57, 42.26)</t>
+          <t>(30.75, 32.84)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>(29.33, 31.32)</t>
+          <t>(22.79, 24.33)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(23.11, 24.68)</t>
+          <t>(17.95, 19.17)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>(18.96, 20.24)</t>
+          <t>(14.73, 15.73)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>(16.01, 17.09)</t>
+          <t>(12.44, 13.28)</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>(13.81, 14.75)</t>
+          <t>(10.73, 11.46)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>(12.11, 12.94)</t>
+          <t>(9.41, 10.05)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>(10.77, 11.5)</t>
+          <t>(8.37, 8.93)</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -8038,52 +8038,52 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>(0.0, 20.34)</t>
+          <t>(0.0, 15.8)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>(0.0, 10.98)</t>
+          <t>(0.0, 8.53)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>(0.0, 7.34)</t>
+          <t>(0.0, 5.7)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>(0.0, 5.44)</t>
+          <t>(0.0, 4.23)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(0.0, 4.28)</t>
+          <t>(0.0, 3.33)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>(0.0, 3.52)</t>
+          <t>(0.0, 2.73)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>(0.0, 2.97)</t>
+          <t>(0.0, 2.31)</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>(0.0, 2.56)</t>
+          <t>(0.0, 1.99)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>(0.0, 2.25)</t>
+          <t>(0.0, 1.75)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>(0.0, 2.0)</t>
+          <t>(0.0, 1.55)</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -8106,52 +8106,52 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>(0.0, 20.34)</t>
+          <t>(0.0, 15.8)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>(0.0, 10.98)</t>
+          <t>(0.0, 8.53)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>(0.0, 7.34)</t>
+          <t>(0.0, 5.7)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>(0.0, 5.44)</t>
+          <t>(0.0, 4.23)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(0.0, 4.28)</t>
+          <t>(0.0, 3.33)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>(0.0, 3.52)</t>
+          <t>(0.0, 2.73)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>(0.0, 2.97)</t>
+          <t>(0.0, 2.31)</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>(0.0, 2.56)</t>
+          <t>(0.0, 1.99)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>(0.0, 2.25)</t>
+          <t>(0.0, 1.75)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>(0.0, 2.0)</t>
+          <t>(0.0, 1.55)</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -8174,52 +8174,52 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>(132.82, 284.27)</t>
+          <t>(103.21, 220.89)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>(71.71, 153.47)</t>
+          <t>(55.72, 119.25)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>(47.92, 102.56)</t>
+          <t>(37.24, 79.69)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>(35.52, 76.01)</t>
+          <t>(27.59, 59.06)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(27.98, 59.89)</t>
+          <t>(21.74, 46.53)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>(22.96, 49.13)</t>
+          <t>(17.84, 38.17)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>(19.38, 41.49)</t>
+          <t>(15.06, 32.23)</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>(16.72, 35.79)</t>
+          <t>(12.99, 27.81)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>(14.67, 31.39)</t>
+          <t>(11.4, 24.39)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>(13.04, 27.91)</t>
+          <t>(10.13, 21.68)</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -8242,52 +8242,52 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>(151.44, 284.27)</t>
+          <t>(117.68, 220.89)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>(81.76, 153.47)</t>
+          <t>(63.53, 119.25)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>(54.64, 102.56)</t>
+          <t>(42.46, 79.69)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>(40.49, 76.01)</t>
+          <t>(31.46, 59.06)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(31.9, 59.89)</t>
+          <t>(24.79, 46.53)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>(26.18, 49.13)</t>
+          <t>(20.34, 38.17)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>(22.1, 41.49)</t>
+          <t>(17.17, 32.23)</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>(19.07, 35.79)</t>
+          <t>(14.81, 27.81)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>(16.73, 31.39)</t>
+          <t>(12.99, 24.39)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>(14.87, 27.91)</t>
+          <t>(11.55, 21.68)</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -8310,52 +8310,52 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>(121.51, 183.51)</t>
+          <t>(94.42, 142.6)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>(65.6, 99.07)</t>
+          <t>(50.97, 76.98)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>(43.84, 66.21)</t>
+          <t>(34.06, 51.44)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>(32.49, 49.07)</t>
+          <t>(25.24, 38.12)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(25.6, 38.66)</t>
+          <t>(19.89, 30.04)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>(21.0, 31.72)</t>
+          <t>(16.32, 24.64)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>(17.73, 26.78)</t>
+          <t>(13.78, 20.81)</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>(15.3, 23.1)</t>
+          <t>(11.89, 17.95)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>(13.42, 20.27)</t>
+          <t>(10.43, 15.75)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>(11.93, 18.02)</t>
+          <t>(9.27, 14.0)</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -8378,52 +8378,52 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>(62.0, 183.51)</t>
+          <t>(48.18, 142.6)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>(33.47, 99.07)</t>
+          <t>(26.01, 76.98)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>(22.37, 66.21)</t>
+          <t>(17.38, 51.44)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>(16.58, 49.07)</t>
+          <t>(12.88, 38.12)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(13.06, 38.66)</t>
+          <t>(10.15, 30.04)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>(10.72, 31.72)</t>
+          <t>(8.33, 24.64)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>(9.05, 26.78)</t>
+          <t>(7.03, 20.81)</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>(7.81, 23.1)</t>
+          <t>(6.06, 17.95)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>(6.85, 20.27)</t>
+          <t>(5.32, 15.75)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>(6.09, 18.02)</t>
+          <t>(4.73, 14.0)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -8446,52 +8446,52 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>(25.21, 459.28)</t>
+          <t>(19.59, 356.89)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>(13.61, 247.96)</t>
+          <t>(10.58, 192.67)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>(9.1, 165.71)</t>
+          <t>(7.07, 128.75)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>(6.74, 122.81)</t>
+          <t>(5.24, 95.42)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(5.31, 96.76)</t>
+          <t>(4.13, 75.18)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>(4.36, 79.38)</t>
+          <t>(3.39, 61.68)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>(3.68, 67.03)</t>
+          <t>(2.86, 52.08)</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>(3.17, 57.82)</t>
+          <t>(2.47, 44.93)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>(2.78, 50.72)</t>
+          <t>(2.16, 39.41)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>(2.48, 45.09)</t>
+          <t>(1.92, 35.03)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -8514,52 +8514,52 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>(433.23, 459.28)</t>
+          <t>(336.65, 356.89)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>(233.9, 247.96)</t>
+          <t>(181.74, 192.67)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>(156.31, 165.71)</t>
+          <t>(121.45, 128.75)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>(115.84, 122.81)</t>
+          <t>(90.01, 95.42)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(91.27, 96.76)</t>
+          <t>(70.91, 75.18)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>(74.88, 79.38)</t>
+          <t>(58.18, 61.68)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>(63.23, 67.03)</t>
+          <t>(49.12, 52.08)</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>(54.54, 57.82)</t>
+          <t>(42.38, 44.93)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>(47.85, 50.72)</t>
+          <t>(37.17, 39.41)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>(42.53, 45.09)</t>
+          <t>(33.04, 35.03)</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -8582,52 +8582,52 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>(244.15, 278.08)</t>
+          <t>(189.72, 216.09)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>(131.82, 150.14)</t>
+          <t>(102.42, 116.66)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>(88.09, 100.33)</t>
+          <t>(68.44, 77.96)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>(65.28, 74.36)</t>
+          <t>(50.72, 57.77)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(51.44, 58.58)</t>
+          <t>(39.96, 45.52)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>(42.2, 48.06)</t>
+          <t>(32.79, 37.34)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>(35.63, 40.58)</t>
+          <t>(27.68, 31.53)</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>(30.74, 35.01)</t>
+          <t>(23.88, 27.2)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>(26.96, 30.71)</t>
+          <t>(20.95, 23.86)</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>(23.97, 27.3)</t>
+          <t>(18.62, 21.21)</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -8650,52 +8650,52 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>(33.52, 278.08)</t>
+          <t>(26.05, 216.09)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>(18.1, 150.14)</t>
+          <t>(14.06, 116.66)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>(12.09, 100.33)</t>
+          <t>(9.4, 77.96)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>(8.96, 74.36)</t>
+          <t>(6.96, 57.77)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(7.06, 58.58)</t>
+          <t>(5.49, 45.52)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>(5.79, 48.06)</t>
+          <t>(4.5, 37.34)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>(4.89, 40.58)</t>
+          <t>(3.8, 31.53)</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>(4.22, 35.01)</t>
+          <t>(3.28, 27.2)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>(3.7, 30.71)</t>
+          <t>(2.88, 23.86)</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>(3.29, 27.3)</t>
+          <t>(2.56, 21.21)</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -8718,52 +8718,52 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>(0.0, 111.84)</t>
+          <t>(0.0, 86.91)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>(0.0, 60.38)</t>
+          <t>(0.0, 46.92)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>(0.0, 40.35)</t>
+          <t>(0.0, 31.35)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>(0.0, 29.9)</t>
+          <t>(0.0, 23.24)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(0.0, 23.56)</t>
+          <t>(0.0, 18.31)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>(0.0, 19.33)</t>
+          <t>(0.0, 15.02)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>(0.0, 16.32)</t>
+          <t>(0.0, 12.68)</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>(0.0, 14.08)</t>
+          <t>(0.0, 10.94)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>(0.0, 12.35)</t>
+          <t>(0.0, 9.6)</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>(0.0, 10.98)</t>
+          <t>(0.0, 8.53)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -8786,52 +8786,52 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>(0.0, 111.84)</t>
+          <t>(0.0, 86.91)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>(0.0, 60.38)</t>
+          <t>(0.0, 46.92)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>(0.0, 40.35)</t>
+          <t>(0.0, 31.35)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>(0.0, 29.9)</t>
+          <t>(0.0, 23.24)</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(0.0, 23.56)</t>
+          <t>(0.0, 18.31)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>(0.0, 19.33)</t>
+          <t>(0.0, 15.02)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>(0.0, 16.32)</t>
+          <t>(0.0, 12.68)</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>(0.0, 14.08)</t>
+          <t>(0.0, 10.94)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>(0.0, 12.35)</t>
+          <t>(0.0, 9.6)</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>(0.0, 10.98)</t>
+          <t>(0.0, 8.53)</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -8854,52 +8854,52 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>(45.52, 108.01)</t>
+          <t>(35.37, 83.93)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>(24.58, 58.32)</t>
+          <t>(19.1, 45.31)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>(16.42, 38.97)</t>
+          <t>(12.76, 30.28)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>(12.17, 28.88)</t>
+          <t>(9.46, 22.44)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(9.59, 22.76)</t>
+          <t>(7.45, 17.68)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>(7.87, 18.67)</t>
+          <t>(6.11, 14.51)</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>(6.64, 15.76)</t>
+          <t>(5.16, 12.25)</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>(5.73, 13.6)</t>
+          <t>(4.45, 10.57)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>(5.03, 11.93)</t>
+          <t>(3.91, 9.27)</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>(4.47, 10.6)</t>
+          <t>(3.47, 8.24)</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -8922,52 +8922,52 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>(62.49, 108.01)</t>
+          <t>(48.56, 83.93)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>(33.74, 58.32)</t>
+          <t>(26.21, 45.31)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>(22.54, 38.97)</t>
+          <t>(17.52, 30.28)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>(16.71, 28.88)</t>
+          <t>(12.98, 22.44)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(13.16, 22.76)</t>
+          <t>(10.23, 17.68)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>(10.8, 18.67)</t>
+          <t>(8.39, 14.51)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>(9.12, 15.76)</t>
+          <t>(7.09, 12.25)</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>(7.87, 13.6)</t>
+          <t>(6.11, 10.57)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>(6.9, 11.93)</t>
+          <t>(5.36, 9.27)</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>(6.13, 10.6)</t>
+          <t>(4.77, 8.24)</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -8990,52 +8990,52 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>(0.0, 21.01)</t>
+          <t>(0.0, 16.32)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>(0.0, 11.34)</t>
+          <t>(0.0, 8.81)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>(0.0, 7.58)</t>
+          <t>(0.0, 5.89)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>(0.0, 5.62)</t>
+          <t>(0.0, 4.36)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(0.0, 4.43)</t>
+          <t>(0.0, 3.44)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>(0.0, 3.63)</t>
+          <t>(0.0, 2.82)</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>(0.0, 3.07)</t>
+          <t>(0.0, 2.38)</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>(0.0, 2.64)</t>
+          <t>(0.0, 2.05)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>(0.0, 2.32)</t>
+          <t>(0.0, 1.8)</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>(0.0, 2.06)</t>
+          <t>(0.0, 1.6)</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -9058,52 +9058,52 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>(0.0, 21.01)</t>
+          <t>(0.0, 16.32)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>(0.0, 11.34)</t>
+          <t>(0.0, 8.81)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>(0.0, 7.58)</t>
+          <t>(0.0, 5.89)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>(0.0, 5.62)</t>
+          <t>(0.0, 4.36)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(0.0, 4.43)</t>
+          <t>(0.0, 3.44)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>(0.0, 3.63)</t>
+          <t>(0.0, 2.82)</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>(0.0, 3.07)</t>
+          <t>(0.0, 2.38)</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>(0.0, 2.64)</t>
+          <t>(0.0, 2.05)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>(0.0, 2.32)</t>
+          <t>(0.0, 1.8)</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>(0.0, 2.06)</t>
+          <t>(0.0, 1.6)</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -9126,52 +9126,52 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>(31.49, 148.32)</t>
+          <t>(24.47, 115.25)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>(17.0, 80.08)</t>
+          <t>(13.21, 62.22)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>(11.36, 53.51)</t>
+          <t>(8.83, 41.58)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>(8.42, 39.66)</t>
+          <t>(6.54, 30.81)</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(6.63, 31.25)</t>
+          <t>(5.15, 24.28)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>(5.44, 25.64)</t>
+          <t>(4.23, 19.92)</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>(4.6, 21.65)</t>
+          <t>(3.57, 16.82)</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>(3.96, 18.67)</t>
+          <t>(3.08, 14.51)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>(3.48, 16.38)</t>
+          <t>(2.7, 12.73)</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>(3.09, 14.56)</t>
+          <t>(2.4, 11.31)</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -9194,52 +9194,52 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>(116.83, 148.32)</t>
+          <t>(90.79, 115.25)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>(63.08, 80.08)</t>
+          <t>(49.01, 62.22)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>(42.15, 53.51)</t>
+          <t>(32.75, 41.58)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>(31.24, 39.66)</t>
+          <t>(24.27, 30.81)</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(24.61, 31.25)</t>
+          <t>(19.12, 24.28)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>(20.19, 25.64)</t>
+          <t>(15.69, 19.92)</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>(17.05, 21.65)</t>
+          <t>(13.25, 16.82)</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>(14.71, 18.67)</t>
+          <t>(11.43, 14.51)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>(12.9, 16.38)</t>
+          <t>(10.02, 12.73)</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>(11.47, 14.56)</t>
+          <t>(8.91, 11.31)</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -9262,52 +9262,52 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>(153.76, 245.51)</t>
+          <t>(119.48, 190.78)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>(83.01, 132.55)</t>
+          <t>(64.5, 103.0)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>(55.48, 88.58)</t>
+          <t>(43.1, 68.83)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>(41.11, 65.65)</t>
+          <t>(31.94, 51.01)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(32.39, 51.72)</t>
+          <t>(25.17, 40.19)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>(26.58, 42.43)</t>
+          <t>(20.65, 32.97)</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>(22.44, 35.83)</t>
+          <t>(17.43, 27.84)</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>(19.36, 30.91)</t>
+          <t>(15.04, 24.02)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>(16.98, 27.11)</t>
+          <t>(13.19, 21.07)</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>(15.09, 24.1)</t>
+          <t>(11.73, 18.73)</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -9330,52 +9330,52 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>(90.52, 245.51)</t>
+          <t>(70.34, 190.78)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>(48.87, 132.55)</t>
+          <t>(37.97, 103.0)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>(32.66, 88.58)</t>
+          <t>(25.38, 68.83)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>(24.2, 65.65)</t>
+          <t>(18.81, 51.01)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(19.07, 51.72)</t>
+          <t>(14.82, 40.19)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>(15.65, 42.43)</t>
+          <t>(12.16, 32.97)</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>(13.21, 35.83)</t>
+          <t>(10.26, 27.84)</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>(11.4, 30.91)</t>
+          <t>(8.85, 24.02)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>(10.0, 27.11)</t>
+          <t>(7.77, 21.07)</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>(8.89, 24.1)</t>
+          <t>(6.9, 18.73)</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -9398,52 +9398,52 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>(106.77, 218.1)</t>
+          <t>(82.97, 169.48)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>(57.65, 117.75)</t>
+          <t>(44.79, 91.5)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>(38.52, 78.69)</t>
+          <t>(29.93, 61.14)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>(28.55, 58.32)</t>
+          <t>(22.18, 45.31)</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(22.49, 45.95)</t>
+          <t>(17.48, 35.7)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>(18.45, 37.7)</t>
+          <t>(14.34, 29.29)</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>(15.58, 31.83)</t>
+          <t>(12.11, 24.73)</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>(13.44, 27.46)</t>
+          <t>(10.44, 21.33)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>(11.79, 24.09)</t>
+          <t>(9.16, 18.71)</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>(10.48, 21.41)</t>
+          <t>(8.14, 16.64)</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -9466,52 +9466,52 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>(111.33, 218.1)</t>
+          <t>(86.51, 169.48)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>(60.11, 117.75)</t>
+          <t>(46.7, 91.5)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>(40.17, 78.69)</t>
+          <t>(31.21, 61.14)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>(29.77, 58.32)</t>
+          <t>(23.13, 45.31)</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(23.45, 45.95)</t>
+          <t>(18.22, 35.7)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>(19.24, 37.7)</t>
+          <t>(14.95, 29.29)</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>(16.25, 31.83)</t>
+          <t>(12.62, 24.73)</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>(14.02, 27.46)</t>
+          <t>(10.89, 21.33)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>(12.3, 24.09)</t>
+          <t>(9.55, 18.71)</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>(10.93, 21.41)</t>
+          <t>(8.49, 16.64)</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -9534,52 +9534,52 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>(171.54, 410.04)</t>
+          <t>(133.3, 318.63)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>(92.61, 221.38)</t>
+          <t>(71.96, 172.01)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>(61.89, 147.94)</t>
+          <t>(48.09, 114.95)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>(45.87, 109.64)</t>
+          <t>(35.64, 85.19)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(36.14, 86.38)</t>
+          <t>(28.08, 67.12)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>(29.65, 70.87)</t>
+          <t>(23.04, 55.06)</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>(25.03, 59.84)</t>
+          <t>(19.45, 46.49)</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>(21.6, 51.62)</t>
+          <t>(16.78, 40.11)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>(18.94, 45.28)</t>
+          <t>(14.72, 35.18)</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>(16.84, 40.26)</t>
+          <t>(13.08, 31.28)</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -9602,52 +9602,52 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>(238.5, 410.04)</t>
+          <t>(185.33, 318.63)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>(128.76, 221.38)</t>
+          <t>(100.05, 172.01)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>(86.05, 147.94)</t>
+          <t>(66.86, 114.95)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>(63.77, 109.64)</t>
+          <t>(49.55, 85.19)</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(50.24, 86.38)</t>
+          <t>(39.04, 67.12)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>(41.22, 70.87)</t>
+          <t>(32.03, 55.06)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>(34.81, 59.84)</t>
+          <t>(27.04, 46.49)</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>(30.03, 51.62)</t>
+          <t>(23.33, 40.11)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>(26.34, 45.28)</t>
+          <t>(20.46, 35.18)</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>(23.41, 40.26)</t>
+          <t>(18.19, 31.28)</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -9670,52 +9670,52 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>(64.56, 64.56)</t>
+          <t>(50.17, 50.17)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>(34.86, 34.86)</t>
+          <t>(27.08, 27.08)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>(23.29, 23.29)</t>
+          <t>(18.1, 18.1)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>(17.26, 17.26)</t>
+          <t>(13.41, 13.41)</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(13.6, 13.6)</t>
+          <t>(10.57, 10.57)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>(11.16, 11.16)</t>
+          <t>(8.67, 8.67)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>(9.42, 9.42)</t>
+          <t>(7.32, 7.32)</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>(8.13, 8.13)</t>
+          <t>(6.32, 6.32)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>(7.13, 7.13)</t>
+          <t>(5.54, 5.54)</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>(6.34, 6.34)</t>
+          <t>(4.92, 4.92)</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -9738,52 +9738,52 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>(0.0, 64.56)</t>
+          <t>(0.0, 50.17)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>(0.0, 34.86)</t>
+          <t>(0.0, 27.08)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>(0.0, 23.29)</t>
+          <t>(0.0, 18.1)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>(0.0, 17.26)</t>
+          <t>(0.0, 13.41)</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(0.0, 13.6)</t>
+          <t>(0.0, 10.57)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>(0.0, 11.16)</t>
+          <t>(0.0, 8.67)</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>(0.0, 9.42)</t>
+          <t>(0.0, 7.32)</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>(0.0, 8.13)</t>
+          <t>(0.0, 6.32)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>(0.0, 7.13)</t>
+          <t>(0.0, 5.54)</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>(0.0, 6.34)</t>
+          <t>(0.0, 4.92)</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -9806,52 +9806,52 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>(36.37, 200.89)</t>
+          <t>(28.26, 156.1)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>(19.64, 108.46)</t>
+          <t>(15.26, 84.27)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>(13.12, 72.48)</t>
+          <t>(10.2, 56.32)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>(9.73, 53.72)</t>
+          <t>(7.56, 41.74)</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(7.66, 42.32)</t>
+          <t>(5.95, 32.88)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>(6.29, 34.72)</t>
+          <t>(4.88, 26.98)</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>(5.31, 29.32)</t>
+          <t>(4.12, 22.78)</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>(4.58, 25.29)</t>
+          <t>(3.56, 19.65)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>(4.02, 22.19)</t>
+          <t>(3.12, 17.24)</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>(3.57, 19.72)</t>
+          <t>(2.77, 15.32)</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -9874,52 +9874,52 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>(164.51, 200.89)</t>
+          <t>(127.83, 156.1)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>(88.82, 108.46)</t>
+          <t>(69.01, 84.27)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>(59.35, 72.48)</t>
+          <t>(46.12, 56.32)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>(43.99, 53.72)</t>
+          <t>(34.18, 41.74)</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(34.66, 42.32)</t>
+          <t>(26.93, 32.88)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>(28.43, 34.72)</t>
+          <t>(22.09, 26.98)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>(24.01, 29.32)</t>
+          <t>(18.65, 22.78)</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>(20.71, 25.29)</t>
+          <t>(16.09, 19.65)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>(18.17, 22.19)</t>
+          <t>(14.12, 17.24)</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>(16.15, 19.72)</t>
+          <t>(12.55, 15.32)</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -9942,52 +9942,52 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>(70.81, 188.82)</t>
+          <t>(55.02, 146.73)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>(38.23, 101.94)</t>
+          <t>(29.7, 79.21)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>(25.55, 68.13)</t>
+          <t>(19.85, 52.93)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>(18.93, 50.49)</t>
+          <t>(14.71, 39.23)</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(14.92, 39.78)</t>
+          <t>(11.59, 30.91)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>(12.24, 32.64)</t>
+          <t>(9.51, 25.36)</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>(10.33, 27.56)</t>
+          <t>(8.03, 21.41)</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>(8.91, 23.77)</t>
+          <t>(6.93, 18.47)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>(7.82, 20.85)</t>
+          <t>(6.08, 16.2)</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>(6.95, 18.54)</t>
+          <t>(5.4, 14.4)</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -10010,52 +10010,52 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>(118.01, 188.82)</t>
+          <t>(91.7, 146.73)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>(63.71, 101.94)</t>
+          <t>(49.51, 79.21)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>(42.58, 68.13)</t>
+          <t>(33.08, 52.93)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>(31.56, 50.49)</t>
+          <t>(24.52, 39.23)</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(24.86, 39.78)</t>
+          <t>(19.32, 30.91)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>(20.4, 32.64)</t>
+          <t>(15.85, 25.36)</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>(17.22, 27.56)</t>
+          <t>(13.38, 21.41)</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>(14.86, 23.77)</t>
+          <t>(11.54, 18.47)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>(13.03, 20.85)</t>
+          <t>(10.13, 16.2)</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>(11.59, 18.54)</t>
+          <t>(9.0, 14.4)</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -10078,52 +10078,52 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>(250.95, 285.27)</t>
+          <t>(195.01, 221.67)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>(135.49, 154.01)</t>
+          <t>(105.28, 119.67)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>(90.54, 102.92)</t>
+          <t>(70.35, 79.97)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>(67.1, 76.28)</t>
+          <t>(52.14, 59.27)</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(52.87, 60.1)</t>
+          <t>(41.08, 46.69)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>(43.37, 49.31)</t>
+          <t>(33.7, 38.31)</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>(36.62, 41.63)</t>
+          <t>(28.45, 32.35)</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>(31.6, 35.92)</t>
+          <t>(24.55, 27.9)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>(27.72, 31.5)</t>
+          <t>(21.53, 24.48)</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>(24.64, 28.01)</t>
+          <t>(19.14, 21.76)</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -10146,52 +10146,52 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>(34.31, 285.27)</t>
+          <t>(26.66, 221.67)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>(18.53, 154.01)</t>
+          <t>(14.39, 119.67)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>(12.38, 102.92)</t>
+          <t>(9.62, 79.97)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>(9.17, 76.28)</t>
+          <t>(7.13, 59.27)</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(7.23, 60.1)</t>
+          <t>(5.62, 46.69)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>(5.93, 49.31)</t>
+          <t>(4.61, 38.31)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>(5.01, 41.63)</t>
+          <t>(3.89, 32.35)</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>(4.32, 35.92)</t>
+          <t>(3.36, 27.9)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>(3.79, 31.5)</t>
+          <t>(2.94, 24.48)</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>(3.37, 28.01)</t>
+          <t>(2.62, 21.76)</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -10214,52 +10214,52 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>(292.26, 457.61)</t>
+          <t>(227.1, 355.59)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>(157.79, 247.06)</t>
+          <t>(122.6, 191.97)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>(105.45, 165.11)</t>
+          <t>(81.93, 128.29)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>(78.15, 122.36)</t>
+          <t>(60.72, 95.07)</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(61.57, 96.4)</t>
+          <t>(47.84, 74.9)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>(50.51, 79.09)</t>
+          <t>(39.25, 61.45)</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>(42.65, 66.78)</t>
+          <t>(33.14, 51.89)</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>(36.8, 57.61)</t>
+          <t>(28.59, 44.76)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>(32.28, 50.54)</t>
+          <t>(25.08, 39.27)</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>(28.69, 44.93)</t>
+          <t>(22.29, 34.9)</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -10282,52 +10282,52 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>(165.35, 457.61)</t>
+          <t>(128.49, 355.59)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>(89.27, 247.06)</t>
+          <t>(69.37, 191.97)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>(59.66, 165.11)</t>
+          <t>(46.35, 128.29)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>(44.21, 122.36)</t>
+          <t>(34.35, 95.07)</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(34.83, 96.4)</t>
+          <t>(27.07, 74.9)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>(28.58, 79.09)</t>
+          <t>(22.2, 61.45)</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>(24.13, 66.78)</t>
+          <t>(18.75, 51.89)</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>(20.82, 57.61)</t>
+          <t>(16.17, 44.76)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>(18.26, 50.54)</t>
+          <t>(14.19, 39.27)</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>(16.23, 44.93)</t>
+          <t>(12.61, 34.9)</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -10350,52 +10350,52 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>(63.7, 269.27)</t>
+          <t>(49.5, 209.24)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>(34.39, 145.38)</t>
+          <t>(26.72, 112.96)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>(22.98, 97.15)</t>
+          <t>(17.86, 75.49)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>(17.03, 72.0)</t>
+          <t>(13.23, 55.94)</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(13.42, 56.73)</t>
+          <t>(10.43, 44.08)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>(11.01, 46.54)</t>
+          <t>(8.55, 36.16)</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>(9.3, 39.3)</t>
+          <t>(7.22, 30.53)</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>(8.02, 33.9)</t>
+          <t>(6.23, 26.34)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>(7.04, 29.74)</t>
+          <t>(5.47, 23.11)</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>(6.25, 26.44)</t>
+          <t>(4.86, 20.54)</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -10418,52 +10418,52 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>(205.57, 269.27)</t>
+          <t>(159.74, 209.24)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>(110.99, 145.38)</t>
+          <t>(86.24, 112.96)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>(74.17, 97.15)</t>
+          <t>(57.63, 75.49)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>(54.97, 72.0)</t>
+          <t>(42.71, 55.94)</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(43.31, 56.73)</t>
+          <t>(33.65, 44.08)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>(35.53, 46.54)</t>
+          <t>(27.61, 36.16)</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>(30.0, 39.3)</t>
+          <t>(23.31, 30.53)</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>(25.88, 33.9)</t>
+          <t>(20.11, 26.34)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>(22.7, 29.74)</t>
+          <t>(17.64, 23.11)</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>(20.18, 26.44)</t>
+          <t>(15.68, 20.54)</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -10486,52 +10486,52 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>(215.76, 287.27)</t>
+          <t>(167.66, 223.23)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>(116.49, 155.1)</t>
+          <t>(90.51, 120.51)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>(77.85, 103.65)</t>
+          <t>(60.49, 80.53)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>(57.69, 76.81)</t>
+          <t>(44.83, 59.68)</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(45.45, 60.52)</t>
+          <t>(35.32, 47.02)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>(37.29, 49.65)</t>
+          <t>(28.97, 38.58)</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>(31.49, 41.92)</t>
+          <t>(24.46, 32.57)</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>(27.16, 36.17)</t>
+          <t>(21.11, 28.1)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>(23.83, 31.73)</t>
+          <t>(18.51, 24.65)</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>(21.18, 28.2)</t>
+          <t>(16.46, 21.91)</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -10554,52 +10554,52 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>(71.51, 287.27)</t>
+          <t>(55.57, 223.23)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>(38.61, 155.1)</t>
+          <t>(30.0, 120.51)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>(25.8, 103.65)</t>
+          <t>(20.05, 80.53)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>(19.12, 76.81)</t>
+          <t>(14.86, 59.68)</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(15.07, 60.52)</t>
+          <t>(11.71, 47.02)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>(12.36, 49.65)</t>
+          <t>(9.6, 38.58)</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>(10.44, 41.92)</t>
+          <t>(8.11, 32.57)</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>(9.0, 36.17)</t>
+          <t>(7.0, 28.1)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>(7.9, 31.73)</t>
+          <t>(6.14, 24.65)</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>(7.02, 28.2)</t>
+          <t>(5.45, 21.91)</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -10622,52 +10622,52 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>(96.4, 269.76)</t>
+          <t>(74.91, 209.62)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>(52.05, 145.64)</t>
+          <t>(40.44, 113.17)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>(34.78, 97.33)</t>
+          <t>(27.03, 75.62)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>(25.78, 72.13)</t>
+          <t>(20.03, 56.04)</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(20.31, 56.83)</t>
+          <t>(15.78, 44.16)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>(16.66, 46.63)</t>
+          <t>(12.95, 36.23)</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>(14.07, 39.37)</t>
+          <t>(10.93, 30.59)</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>(12.14, 33.96)</t>
+          <t>(9.43, 26.39)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>(10.65, 29.79)</t>
+          <t>(8.27, 23.15)</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>(9.46, 26.48)</t>
+          <t>(7.35, 20.58)</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -10690,52 +10690,52 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>(173.36, 269.76)</t>
+          <t>(134.71, 209.62)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>(93.6, 145.64)</t>
+          <t>(72.73, 113.17)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>(62.55, 97.33)</t>
+          <t>(48.6, 75.62)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>(46.35, 72.13)</t>
+          <t>(36.02, 56.04)</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(36.52, 56.83)</t>
+          <t>(28.38, 44.16)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>(29.96, 46.63)</t>
+          <t>(23.28, 36.23)</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>(25.3, 39.37)</t>
+          <t>(19.66, 30.59)</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>(21.83, 33.96)</t>
+          <t>(16.96, 26.39)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>(19.15, 29.79)</t>
+          <t>(14.88, 23.15)</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>(17.02, 26.48)</t>
+          <t>(13.22, 20.58)</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -10758,52 +10758,52 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>(0.0, 83.14)</t>
+          <t>(0.0, 64.6)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>(0.0, 44.89)</t>
+          <t>(0.0, 34.88)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>(0.0, 30.0)</t>
+          <t>(0.0, 23.31)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>(0.0, 22.23)</t>
+          <t>(0.0, 17.27)</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(0.0, 17.51)</t>
+          <t>(0.0, 13.61)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>(0.0, 14.37)</t>
+          <t>(0.0, 11.16)</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>(0.0, 12.13)</t>
+          <t>(0.0, 9.43)</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>(0.0, 10.47)</t>
+          <t>(0.0, 8.13)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>(0.0, 9.18)</t>
+          <t>(0.0, 7.13)</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>(0.0, 8.16)</t>
+          <t>(0.0, 6.34)</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -10826,52 +10826,52 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>(83.14, 83.14)</t>
+          <t>(64.6, 64.6)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>(44.89, 44.89)</t>
+          <t>(34.88, 34.88)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>(30.0, 30.0)</t>
+          <t>(23.31, 23.31)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>(22.23, 22.23)</t>
+          <t>(17.27, 17.27)</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(17.51, 17.51)</t>
+          <t>(13.61, 13.61)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>(14.37, 14.37)</t>
+          <t>(11.16, 11.16)</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>(12.13, 12.13)</t>
+          <t>(9.43, 9.43)</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>(10.47, 10.47)</t>
+          <t>(8.13, 8.13)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>(9.18, 9.18)</t>
+          <t>(7.13, 7.13)</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>(8.16, 8.16)</t>
+          <t>(6.34, 6.34)</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -10894,52 +10894,52 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>(122.79, 305.93)</t>
+          <t>(95.42, 237.73)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>(66.29, 165.17)</t>
+          <t>(51.51, 128.34)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>(44.3, 110.38)</t>
+          <t>(34.42, 85.77)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>(32.83, 81.8)</t>
+          <t>(25.51, 63.56)</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(25.87, 64.45)</t>
+          <t>(20.1, 50.08)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>(21.22, 52.88)</t>
+          <t>(16.49, 41.08)</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>(17.92, 44.65)</t>
+          <t>(13.92, 34.69)</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>(15.46, 38.52)</t>
+          <t>(12.01, 29.93)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>(13.56, 33.79)</t>
+          <t>(10.54, 26.25)</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>(12.05, 30.03)</t>
+          <t>(9.37, 23.34)</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -10962,52 +10962,52 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>(183.15, 305.93)</t>
+          <t>(142.32, 237.73)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>(98.88, 165.17)</t>
+          <t>(76.83, 128.34)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>(66.08, 110.38)</t>
+          <t>(51.34, 85.77)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>(48.97, 81.8)</t>
+          <t>(38.05, 63.56)</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(38.58, 64.45)</t>
+          <t>(29.98, 50.08)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>(31.66, 52.88)</t>
+          <t>(24.6, 41.08)</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>(26.73, 44.65)</t>
+          <t>(20.77, 34.69)</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>(23.06, 38.52)</t>
+          <t>(17.92, 29.93)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>(20.23, 33.79)</t>
+          <t>(15.72, 26.25)</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>(17.98, 30.03)</t>
+          <t>(13.97, 23.34)</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -11030,52 +11030,52 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>(74.87, 288.32)</t>
+          <t>(58.18, 224.04)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>(40.42, 155.66)</t>
+          <t>(31.41, 120.95)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>(27.01, 104.02)</t>
+          <t>(20.99, 80.83)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>(20.02, 77.09)</t>
+          <t>(15.56, 59.9)</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(15.77, 60.74)</t>
+          <t>(12.26, 47.19)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>(12.94, 49.83)</t>
+          <t>(10.05, 38.72)</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>(10.93, 42.08)</t>
+          <t>(8.49, 32.69)</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>(9.43, 36.3)</t>
+          <t>(7.32, 28.2)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>(8.27, 31.84)</t>
+          <t>(6.42, 24.74)</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>(7.35, 28.3)</t>
+          <t>(5.71, 21.99)</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -11098,52 +11098,52 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>(213.44, 288.32)</t>
+          <t>(165.86, 224.04)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>(115.24, 155.66)</t>
+          <t>(89.54, 120.95)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>(77.01, 104.02)</t>
+          <t>(59.84, 80.83)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>(57.07, 77.09)</t>
+          <t>(44.34, 59.9)</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(44.97, 60.74)</t>
+          <t>(34.94, 47.19)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>(36.89, 49.83)</t>
+          <t>(28.66, 38.72)</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>(31.15, 42.08)</t>
+          <t>(24.2, 32.69)</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>(26.87, 36.3)</t>
+          <t>(20.88, 28.2)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>(23.57, 31.84)</t>
+          <t>(18.31, 24.74)</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>(20.95, 28.3)</t>
+          <t>(16.28, 21.99)</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -11166,52 +11166,52 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>(0.0, 133.71)</t>
+          <t>(0.0, 103.9)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>(0.0, 72.19)</t>
+          <t>(0.0, 56.09)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>(0.0, 48.24)</t>
+          <t>(0.0, 37.48)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>(0.0, 35.75)</t>
+          <t>(0.0, 27.78)</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(0.0, 28.17)</t>
+          <t>(0.0, 21.89)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>(0.0, 23.11)</t>
+          <t>(0.0, 17.96)</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>(0.0, 19.51)</t>
+          <t>(0.0, 15.16)</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>(0.0, 16.83)</t>
+          <t>(0.0, 13.08)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>(0.0, 14.77)</t>
+          <t>(0.0, 11.47)</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>(0.0, 13.13)</t>
+          <t>(0.0, 10.2)</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -11234,52 +11234,52 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>(0.0, 133.71)</t>
+          <t>(0.0, 103.9)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>(0.0, 72.19)</t>
+          <t>(0.0, 56.09)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>(0.0, 48.24)</t>
+          <t>(0.0, 37.48)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>(0.0, 35.75)</t>
+          <t>(0.0, 27.78)</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(0.0, 28.17)</t>
+          <t>(0.0, 21.89)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>(0.0, 23.11)</t>
+          <t>(0.0, 17.96)</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>(0.0, 19.51)</t>
+          <t>(0.0, 15.16)</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>(0.0, 16.83)</t>
+          <t>(0.0, 13.08)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>(0.0, 14.77)</t>
+          <t>(0.0, 11.47)</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>(0.0, 13.13)</t>
+          <t>(0.0, 10.2)</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -11302,52 +11302,52 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>(26.04, 464.97)</t>
+          <t>(20.24, 361.32)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>(14.06, 251.04)</t>
+          <t>(10.92, 195.06)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>(9.4, 167.76)</t>
+          <t>(7.3, 130.35)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>(6.96, 124.33)</t>
+          <t>(5.41, 96.6)</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(5.49, 97.96)</t>
+          <t>(4.26, 76.11)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>(4.5, 80.37)</t>
+          <t>(3.5, 62.44)</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>(3.8, 67.86)</t>
+          <t>(2.95, 52.72)</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>(3.28, 58.54)</t>
+          <t>(2.55, 45.48)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>(2.88, 51.35)</t>
+          <t>(2.23, 39.9)</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>(2.56, 45.65)</t>
+          <t>(1.99, 35.47)</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -11370,52 +11370,52 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>(438.52, 464.97)</t>
+          <t>(340.76, 361.32)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>(236.75, 251.04)</t>
+          <t>(183.96, 195.06)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>(158.22, 167.76)</t>
+          <t>(122.93, 130.35)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>(117.26, 124.33)</t>
+          <t>(91.1, 96.6)</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(92.38, 97.96)</t>
+          <t>(71.78, 76.11)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>(75.79, 80.37)</t>
+          <t>(58.89, 62.44)</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>(64.0, 67.86)</t>
+          <t>(49.72, 52.72)</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>(55.21, 58.54)</t>
+          <t>(42.9, 45.48)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>(48.43, 51.35)</t>
+          <t>(37.63, 39.9)</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>(43.05, 45.65)</t>
+          <t>(33.45, 35.47)</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -11438,52 +11438,52 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>(136.8, 249.63)</t>
+          <t>(106.3, 193.98)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>(73.86, 134.77)</t>
+          <t>(57.39, 104.72)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>(49.36, 90.07)</t>
+          <t>(38.35, 69.98)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>(36.58, 66.75)</t>
+          <t>(28.42, 51.86)</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(28.82, 52.59)</t>
+          <t>(22.39, 40.86)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>(23.64, 43.15)</t>
+          <t>(18.37, 33.52)</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>(19.96, 36.43)</t>
+          <t>(15.51, 28.31)</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>(17.22, 31.43)</t>
+          <t>(13.38, 24.42)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>(15.11, 27.57)</t>
+          <t>(11.74, 21.42)</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>(13.43, 24.51)</t>
+          <t>(10.43, 19.04)</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -11506,52 +11506,52 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>(40.09, 249.63)</t>
+          <t>(31.15, 193.98)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>(21.64, 134.77)</t>
+          <t>(16.82, 104.72)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>(14.46, 90.07)</t>
+          <t>(11.24, 69.98)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>(10.72, 66.75)</t>
+          <t>(8.33, 51.86)</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(8.45, 52.59)</t>
+          <t>(6.56, 40.86)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>(6.93, 43.15)</t>
+          <t>(5.38, 33.52)</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>(5.85, 36.43)</t>
+          <t>(4.55, 28.31)</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>(5.05, 31.43)</t>
+          <t>(3.92, 24.42)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>(4.43, 27.57)</t>
+          <t>(3.44, 21.42)</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>(3.94, 24.51)</t>
+          <t>(3.06, 19.04)</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -11574,52 +11574,52 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>(189.25, 464.05)</t>
+          <t>(147.06, 360.6)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>(102.18, 250.54)</t>
+          <t>(79.39, 194.67)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>(68.28, 167.43)</t>
+          <t>(53.05, 130.09)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>(50.6, 124.08)</t>
+          <t>(39.32, 96.41)</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(39.87, 97.76)</t>
+          <t>(30.98, 75.96)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>(32.71, 80.21)</t>
+          <t>(25.41, 62.32)</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>(27.62, 67.72)</t>
+          <t>(21.46, 52.62)</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>(23.83, 58.42)</t>
+          <t>(18.51, 45.39)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>(20.9, 51.25)</t>
+          <t>(16.24, 39.82)</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>(18.58, 45.56)</t>
+          <t>(14.44, 35.4)</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -11642,52 +11642,52 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>(274.79, 464.05)</t>
+          <t>(213.53, 360.6)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>(148.36, 250.54)</t>
+          <t>(115.27, 194.67)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>(99.14, 167.43)</t>
+          <t>(77.03, 130.09)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>(73.47, 124.08)</t>
+          <t>(57.09, 96.41)</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(57.89, 97.76)</t>
+          <t>(44.98, 75.96)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>(47.49, 80.21)</t>
+          <t>(36.9, 62.32)</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>(40.1, 67.72)</t>
+          <t>(31.16, 52.62)</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>(34.6, 58.42)</t>
+          <t>(26.88, 45.39)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>(30.35, 51.25)</t>
+          <t>(23.58, 39.82)</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>(26.98, 45.56)</t>
+          <t>(20.96, 35.4)</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -11710,52 +11710,52 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>(239.87, 382.97)</t>
+          <t>(186.4, 297.59)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>(129.5, 206.76)</t>
+          <t>(100.63, 160.66)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>(86.55, 138.17)</t>
+          <t>(67.24, 107.36)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>(64.14, 102.4)</t>
+          <t>(49.83, 79.56)</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(50.53, 80.68)</t>
+          <t>(39.26, 62.69)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>(41.46, 66.19)</t>
+          <t>(32.21, 51.43)</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>(35.01, 55.89)</t>
+          <t>(27.2, 43.42)</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>(30.2, 48.22)</t>
+          <t>(23.46, 37.46)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>(26.49, 42.29)</t>
+          <t>(20.58, 32.86)</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>(23.55, 37.6)</t>
+          <t>(18.3, 29.21)</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -11778,52 +11778,52 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>(143.1, 382.97)</t>
+          <t>(111.2, 297.59)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>(77.26, 206.76)</t>
+          <t>(60.03, 160.66)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>(51.63, 138.17)</t>
+          <t>(40.12, 107.36)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>(38.26, 102.4)</t>
+          <t>(29.73, 79.56)</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(30.15, 80.68)</t>
+          <t>(23.42, 62.69)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>(24.73, 66.19)</t>
+          <t>(19.22, 51.43)</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>(20.88, 55.89)</t>
+          <t>(16.23, 43.42)</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>(18.02, 48.22)</t>
+          <t>(14.0, 37.46)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>(15.8, 42.29)</t>
+          <t>(12.28, 32.86)</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>(14.05, 37.6)</t>
+          <t>(10.91, 29.21)</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -11846,52 +11846,52 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>(0.0, 21.26)</t>
+          <t>(0.0, 16.52)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>(0.0, 11.48)</t>
+          <t>(0.0, 8.92)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>(0.0, 7.67)</t>
+          <t>(0.0, 5.96)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>(0.0, 5.69)</t>
+          <t>(0.0, 4.42)</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(0.0, 4.48)</t>
+          <t>(0.0, 3.48)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>(0.0, 3.68)</t>
+          <t>(0.0, 2.86)</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>(0.0, 3.1)</t>
+          <t>(0.0, 2.41)</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>(0.0, 2.68)</t>
+          <t>(0.0, 2.08)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>(0.0, 2.35)</t>
+          <t>(0.0, 1.82)</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>(0.0, 2.09)</t>
+          <t>(0.0, 1.62)</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -11914,52 +11914,52 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>(0.0, 21.26)</t>
+          <t>(0.0, 16.52)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>(0.0, 11.48)</t>
+          <t>(0.0, 8.92)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>(0.0, 7.67)</t>
+          <t>(0.0, 5.96)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>(0.0, 5.69)</t>
+          <t>(0.0, 4.42)</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(0.0, 4.48)</t>
+          <t>(0.0, 3.48)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>(0.0, 3.68)</t>
+          <t>(0.0, 2.86)</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>(0.0, 3.1)</t>
+          <t>(0.0, 2.41)</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>(0.0, 2.68)</t>
+          <t>(0.0, 2.08)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>(0.0, 2.35)</t>
+          <t>(0.0, 1.82)</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>(0.0, 2.09)</t>
+          <t>(0.0, 1.62)</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -11982,52 +11982,52 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>(280.48, 306.95)</t>
+          <t>(217.95, 238.52)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>(151.43, 165.72)</t>
+          <t>(117.66, 128.77)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>(101.2, 110.75)</t>
+          <t>(78.63, 86.05)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>(75.0, 82.08)</t>
+          <t>(58.27, 63.77)</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(59.09, 64.67)</t>
+          <t>(45.91, 50.24)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>(48.48, 53.05)</t>
+          <t>(37.67, 41.22)</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>(40.93, 44.8)</t>
+          <t>(31.8, 34.8)</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>(35.31, 38.65)</t>
+          <t>(27.44, 30.03)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>(30.98, 33.9)</t>
+          <t>(24.07, 26.34)</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>(27.54, 30.13)</t>
+          <t>(21.39, 23.41)</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -12050,52 +12050,52 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>(26.48, 306.95)</t>
+          <t>(20.58, 238.52)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>(14.3, 165.72)</t>
+          <t>(11.11, 128.77)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>(9.55, 110.75)</t>
+          <t>(7.42, 86.05)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>(7.08, 82.08)</t>
+          <t>(5.5, 63.77)</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(5.58, 64.67)</t>
+          <t>(4.33, 50.24)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>(4.58, 53.05)</t>
+          <t>(3.56, 41.22)</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>(3.86, 44.8)</t>
+          <t>(3.0, 34.8)</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>(3.33, 38.65)</t>
+          <t>(2.59, 30.03)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>(2.92, 33.9)</t>
+          <t>(2.27, 26.34)</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>(2.6, 30.13)</t>
+          <t>(2.02, 23.41)</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -12118,52 +12118,52 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>(30.77, 37.42)</t>
+          <t>(23.91, 29.08)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>(16.61, 20.2)</t>
+          <t>(12.91, 15.7)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>(11.1, 13.5)</t>
+          <t>(8.63, 10.49)</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>(8.23, 10.01)</t>
+          <t>(6.39, 7.77)</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(6.48, 7.88)</t>
+          <t>(5.04, 6.13)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>(5.32, 6.47)</t>
+          <t>(4.13, 5.03)</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>(4.49, 5.46)</t>
+          <t>(3.49, 4.24)</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>(3.87, 4.71)</t>
+          <t>(3.01, 3.66)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>(3.4, 4.13)</t>
+          <t>(2.64, 3.21)</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>(3.02, 3.67)</t>
+          <t>(2.35, 2.85)</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -12186,52 +12186,52 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>(6.65, 37.42)</t>
+          <t>(5.17, 29.08)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>(3.59, 20.2)</t>
+          <t>(2.79, 15.7)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>(2.4, 13.5)</t>
+          <t>(1.87, 10.49)</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>(1.78, 10.01)</t>
+          <t>(1.38, 7.77)</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(1.4, 7.88)</t>
+          <t>(1.09, 6.13)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>(1.15, 6.47)</t>
+          <t>(0.89, 5.03)</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>(0.97, 5.46)</t>
+          <t>(0.75, 4.24)</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>(0.84, 4.71)</t>
+          <t>(0.65, 3.66)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>(0.73, 4.13)</t>
+          <t>(0.57, 3.21)</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>(0.65, 3.67)</t>
+          <t>(0.51, 2.85)</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -12254,52 +12254,52 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>(33.92, 218.04)</t>
+          <t>(26.36, 169.43)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>(18.32, 117.72)</t>
+          <t>(14.23, 91.47)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>(12.24, 78.67)</t>
+          <t>(9.51, 61.12)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>(9.07, 58.3)</t>
+          <t>(7.05, 45.3)</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(7.15, 45.93)</t>
+          <t>(5.55, 35.69)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>(5.86, 37.69)</t>
+          <t>(4.56, 29.28)</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>(4.95, 31.82)</t>
+          <t>(3.85, 24.72)</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>(4.27, 27.45)</t>
+          <t>(3.32, 21.33)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>(3.75, 24.08)</t>
+          <t>(2.91, 18.71)</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>(3.33, 21.41)</t>
+          <t>(2.59, 16.63)</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -12322,52 +12322,52 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>(184.11, 218.04)</t>
+          <t>(143.07, 169.43)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>(99.4, 117.72)</t>
+          <t>(77.24, 91.47)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>(66.43, 78.67)</t>
+          <t>(51.61, 61.12)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>(49.23, 58.3)</t>
+          <t>(38.25, 45.3)</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(38.79, 45.93)</t>
+          <t>(30.14, 35.69)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>(31.82, 37.69)</t>
+          <t>(24.72, 29.28)</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>(26.87, 31.82)</t>
+          <t>(20.88, 24.72)</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>(23.18, 27.45)</t>
+          <t>(18.01, 21.33)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>(20.33, 24.08)</t>
+          <t>(15.8, 18.71)</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>(18.07, 21.41)</t>
+          <t>(14.04, 16.63)</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -12390,52 +12390,52 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>(66.2, 137.38)</t>
+          <t>(51.45, 106.75)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>(35.74, 74.17)</t>
+          <t>(27.77, 57.63)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>(23.89, 49.57)</t>
+          <t>(18.56, 38.51)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>(17.7, 36.73)</t>
+          <t>(13.75, 28.54)</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(13.95, 28.94)</t>
+          <t>(10.84, 22.49)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>(11.44, 23.74)</t>
+          <t>(8.89, 18.45)</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>(9.66, 20.05)</t>
+          <t>(7.51, 15.58)</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>(8.34, 17.3)</t>
+          <t>(6.48, 13.44)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>(7.31, 15.17)</t>
+          <t>(5.68, 11.79)</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>(6.5, 13.49)</t>
+          <t>(5.05, 10.48)</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -12458,52 +12458,52 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>(70.35, 137.38)</t>
+          <t>(54.66, 106.75)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>(37.98, 74.17)</t>
+          <t>(29.51, 57.63)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>(25.38, 49.57)</t>
+          <t>(19.72, 38.51)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>(18.81, 36.73)</t>
+          <t>(14.61, 28.54)</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(14.82, 28.94)</t>
+          <t>(11.51, 22.49)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>(12.16, 23.74)</t>
+          <t>(9.45, 18.45)</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>(10.27, 20.05)</t>
+          <t>(7.98, 15.58)</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>(8.86, 17.3)</t>
+          <t>(6.88, 13.44)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>(7.77, 15.17)</t>
+          <t>(6.04, 11.79)</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>(6.91, 13.49)</t>
+          <t>(5.37, 10.48)</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -12526,52 +12526,52 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>(136.06, 156.74)</t>
+          <t>(105.73, 121.8)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>(73.46, 84.62)</t>
+          <t>(57.08, 65.75)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>(49.09, 56.55)</t>
+          <t>(38.14, 43.94)</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>(36.38, 41.91)</t>
+          <t>(28.27, 32.56)</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(28.66, 33.02)</t>
+          <t>(22.27, 25.66)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>(23.52, 27.09)</t>
+          <t>(18.27, 21.05)</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>(19.86, 22.87)</t>
+          <t>(15.43, 17.77)</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>(17.13, 19.73)</t>
+          <t>(13.31, 15.33)</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>(15.03, 17.31)</t>
+          <t>(11.68, 13.45)</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>(13.36, 15.39)</t>
+          <t>(10.38, 11.96)</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -12594,52 +12594,52 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>(20.68, 156.74)</t>
+          <t>(16.07, 121.8)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>(11.16, 84.62)</t>
+          <t>(8.67, 65.75)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>(7.46, 56.55)</t>
+          <t>(5.8, 43.94)</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>(5.53, 41.91)</t>
+          <t>(4.3, 32.56)</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(4.36, 33.02)</t>
+          <t>(3.38, 25.66)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>(3.57, 27.09)</t>
+          <t>(2.78, 21.05)</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>(3.02, 22.87)</t>
+          <t>(2.34, 17.77)</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>(2.6, 19.73)</t>
+          <t>(2.02, 15.33)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>(2.28, 17.31)</t>
+          <t>(1.77, 13.45)</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>(2.03, 15.39)</t>
+          <t>(1.58, 11.96)</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -12662,52 +12662,52 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>(166.54, 294.24)</t>
+          <t>(129.41, 228.65)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>(89.91, 158.86)</t>
+          <t>(69.87, 123.44)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>(60.09, 106.16)</t>
+          <t>(46.69, 82.49)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>(44.53, 78.68)</t>
+          <t>(34.6, 61.13)</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(35.09, 61.99)</t>
+          <t>(27.26, 48.16)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>(28.78, 50.86)</t>
+          <t>(22.36, 39.51)</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>(24.3, 42.94)</t>
+          <t>(18.88, 33.36)</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>(20.97, 37.05)</t>
+          <t>(16.29, 28.78)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>(18.39, 32.5)</t>
+          <t>(14.29, 25.25)</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>(16.35, 28.89)</t>
+          <t>(12.7, 22.44)</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -12730,52 +12730,52 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>(127.7, 294.24)</t>
+          <t>(99.23, 228.65)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>(68.94, 158.86)</t>
+          <t>(53.57, 123.44)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>(46.07, 106.16)</t>
+          <t>(35.8, 82.49)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>(34.15, 78.68)</t>
+          <t>(26.53, 61.13)</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(26.9, 61.99)</t>
+          <t>(20.9, 48.16)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>(22.07, 50.86)</t>
+          <t>(17.15, 39.51)</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>(18.64, 42.94)</t>
+          <t>(14.48, 33.36)</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>(16.08, 37.05)</t>
+          <t>(12.49, 28.78)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>(14.1, 32.5)</t>
+          <t>(10.96, 25.25)</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>(12.54, 28.89)</t>
+          <t>(9.74, 22.44)</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -12798,52 +12798,52 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>(69.89, 105.04)</t>
+          <t>(54.31, 81.62)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>(37.73, 56.71)</t>
+          <t>(29.32, 44.06)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>(25.22, 37.9)</t>
+          <t>(19.59, 29.45)</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>(18.69, 28.09)</t>
+          <t>(14.52, 21.82)</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(14.72, 22.13)</t>
+          <t>(11.44, 17.19)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>(12.08, 18.15)</t>
+          <t>(9.39, 14.11)</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>(10.2, 15.33)</t>
+          <t>(7.92, 11.91)</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>(8.8, 13.22)</t>
+          <t>(6.84, 10.27)</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>(7.72, 11.6)</t>
+          <t>(6.0, 9.01)</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>(6.86, 10.31)</t>
+          <t>(5.33, 8.01)</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -12866,52 +12866,52 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>(35.15, 105.04)</t>
+          <t>(27.31, 81.62)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>(18.98, 56.71)</t>
+          <t>(14.74, 44.06)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>(12.68, 37.9)</t>
+          <t>(9.85, 29.45)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>(9.4, 28.09)</t>
+          <t>(7.3, 21.82)</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(7.4, 22.13)</t>
+          <t>(5.75, 17.19)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>(6.07, 18.15)</t>
+          <t>(4.72, 14.11)</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>(5.13, 15.33)</t>
+          <t>(3.99, 11.91)</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>(4.43, 13.22)</t>
+          <t>(3.44, 10.27)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>(3.88, 11.6)</t>
+          <t>(3.02, 9.01)</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>(3.45, 10.31)</t>
+          <t>(2.68, 8.01)</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -12934,52 +12934,52 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>(189.68, 192.99)</t>
+          <t>(147.4, 149.96)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>(102.41, 104.19)</t>
+          <t>(79.57, 80.96)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>(68.44, 69.63)</t>
+          <t>(53.17, 54.1)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>(50.72, 51.6)</t>
+          <t>(39.41, 40.09)</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(39.96, 40.66)</t>
+          <t>(31.05, 31.59)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>(32.78, 33.36)</t>
+          <t>(25.47, 25.92)</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>(27.68, 28.16)</t>
+          <t>(21.51, 21.88)</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>(23.88, 24.3)</t>
+          <t>(18.55, 18.88)</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>(20.95, 21.31)</t>
+          <t>(16.28, 16.56)</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>(18.62, 18.95)</t>
+          <t>(14.47, 14.72)</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -13002,52 +13002,52 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>(3.31, 192.99)</t>
+          <t>(2.57, 149.96)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>(1.78, 104.19)</t>
+          <t>(1.39, 80.96)</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>(1.19, 69.63)</t>
+          <t>(0.93, 54.1)</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>(0.88, 51.6)</t>
+          <t>(0.69, 40.09)</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(0.7, 40.66)</t>
+          <t>(0.54, 31.59)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>(0.57, 33.36)</t>
+          <t>(0.44, 25.92)</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>(0.48, 28.16)</t>
+          <t>(0.37, 21.88)</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>(0.42, 24.3)</t>
+          <t>(0.32, 18.88)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>(0.37, 21.31)</t>
+          <t>(0.28, 16.56)</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>(0.32, 18.95)</t>
+          <t>(0.25, 14.72)</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -13070,52 +13070,52 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>(70.86, 121.82)</t>
+          <t>(55.06, 94.67)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>(38.26, 65.77)</t>
+          <t>(29.73, 51.11)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>(25.57, 43.95)</t>
+          <t>(19.86, 34.15)</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>(18.95, 32.57)</t>
+          <t>(14.72, 25.31)</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(14.93, 25.66)</t>
+          <t>(11.6, 19.94)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>(12.25, 21.06)</t>
+          <t>(9.52, 16.36)</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>(10.34, 17.78)</t>
+          <t>(8.03, 13.81)</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>(8.92, 15.34)</t>
+          <t>(6.93, 11.92)</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>(7.83, 13.45)</t>
+          <t>(6.08, 10.45)</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>(6.96, 11.96)</t>
+          <t>(5.4, 9.29)</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -13138,52 +13138,52 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>(50.97, 121.82)</t>
+          <t>(39.6, 94.67)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>(27.52, 65.77)</t>
+          <t>(21.38, 51.11)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>(18.39, 43.95)</t>
+          <t>(14.29, 34.15)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>(13.63, 32.57)</t>
+          <t>(10.59, 25.31)</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(10.74, 25.66)</t>
+          <t>(8.34, 19.94)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>(8.81, 21.06)</t>
+          <t>(6.84, 16.36)</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>(7.44, 17.78)</t>
+          <t>(5.78, 13.81)</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>(6.42, 15.34)</t>
+          <t>(4.99, 11.92)</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>(5.63, 13.45)</t>
+          <t>(4.37, 10.45)</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>(5.0, 11.96)</t>
+          <t>(3.89, 9.29)</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -13206,52 +13206,52 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>(258.89, 370.15)</t>
+          <t>(201.18, 287.63)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>(139.78, 199.84)</t>
+          <t>(108.61, 155.28)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>(93.41, 133.55)</t>
+          <t>(72.58, 103.77)</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>(69.23, 98.97)</t>
+          <t>(53.79, 76.9)</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(54.54, 77.98)</t>
+          <t>(42.38, 60.59)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>(44.75, 63.98)</t>
+          <t>(34.77, 49.71)</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>(37.78, 54.02)</t>
+          <t>(29.36, 41.97)</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>(32.6, 46.6)</t>
+          <t>(25.32, 36.21)</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>(28.59, 40.88)</t>
+          <t>(22.21, 31.76)</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>(25.42, 36.34)</t>
+          <t>(19.75, 28.23)</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -13274,52 +13274,52 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>(111.25, 370.15)</t>
+          <t>(86.45, 287.63)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>(60.07, 199.84)</t>
+          <t>(46.67, 155.28)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>(40.14, 133.55)</t>
+          <t>(31.19, 103.77)</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>(29.75, 98.97)</t>
+          <t>(23.11, 76.9)</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(23.44, 77.98)</t>
+          <t>(18.21, 60.59)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>(19.23, 63.98)</t>
+          <t>(14.94, 49.71)</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>(16.24, 54.02)</t>
+          <t>(12.61, 41.97)</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>(14.01, 46.6)</t>
+          <t>(10.88, 36.21)</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>(12.29, 40.88)</t>
+          <t>(9.55, 31.76)</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>(10.92, 36.34)</t>
+          <t>(8.49, 28.23)</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -13342,52 +13342,52 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>(183.51, 202.52)</t>
+          <t>(142.6, 157.38)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>(99.07, 109.34)</t>
+          <t>(76.98, 84.96)</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>(66.21, 73.07)</t>
+          <t>(51.44, 56.78)</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>(49.07, 54.15)</t>
+          <t>(38.12, 42.08)</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(38.66, 42.67)</t>
+          <t>(30.04, 33.15)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>(31.72, 35.0)</t>
+          <t>(24.64, 27.2)</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>(26.78, 29.56)</t>
+          <t>(20.81, 22.96)</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>(23.1, 25.5)</t>
+          <t>(17.95, 19.81)</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>(20.27, 22.37)</t>
+          <t>(15.75, 17.38)</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>(18.02, 19.88)</t>
+          <t>(14.0, 15.45)</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -13410,52 +13410,52 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>(19.02, 202.52)</t>
+          <t>(14.78, 157.38)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>(10.27, 109.34)</t>
+          <t>(7.98, 84.96)</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>(6.86, 73.07)</t>
+          <t>(5.33, 56.78)</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>(5.08, 54.15)</t>
+          <t>(3.95, 42.08)</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(4.01, 42.67)</t>
+          <t>(3.11, 33.15)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>(3.29, 35.0)</t>
+          <t>(2.55, 27.2)</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>(2.78, 29.56)</t>
+          <t>(2.16, 22.96)</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>(2.39, 25.5)</t>
+          <t>(1.86, 19.81)</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>(2.1, 22.37)</t>
+          <t>(1.63, 17.38)</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>(1.87, 19.88)</t>
+          <t>(1.45, 15.45)</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -13478,52 +13478,52 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>(222.13, 299.07)</t>
+          <t>(172.61, 232.4)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>(119.93, 161.46)</t>
+          <t>(93.19, 125.46)</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>(80.15, 107.9)</t>
+          <t>(62.27, 83.84)</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>(59.4, 79.97)</t>
+          <t>(46.15, 62.13)</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(46.8, 63.0)</t>
+          <t>(36.36, 48.95)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>(38.39, 51.69)</t>
+          <t>(29.83, 40.16)</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>(32.42, 43.65)</t>
+          <t>(25.19, 33.91)</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>(27.97, 37.65)</t>
+          <t>(21.73, 29.25)</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>(24.53, 33.03)</t>
+          <t>(19.06, 25.66)</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>(21.81, 29.36)</t>
+          <t>(16.94, 22.81)</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -13546,52 +13546,52 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>(76.94, 299.07)</t>
+          <t>(59.79, 232.4)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>(41.54, 161.46)</t>
+          <t>(32.28, 125.46)</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>(27.76, 107.9)</t>
+          <t>(21.57, 83.84)</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>(20.57, 79.97)</t>
+          <t>(15.98, 62.13)</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(16.21, 63.0)</t>
+          <t>(12.59, 48.95)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>(13.3, 51.69)</t>
+          <t>(10.33, 40.16)</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>(11.23, 43.65)</t>
+          <t>(8.72, 33.91)</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>(9.69, 37.65)</t>
+          <t>(7.53, 29.25)</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>(8.5, 33.03)</t>
+          <t>(6.6, 25.66)</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>(7.55, 29.36)</t>
+          <t>(5.87, 22.81)</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -13614,52 +13614,52 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>(9.96, 91.27)</t>
+          <t>(7.74, 70.92)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>(5.38, 49.28)</t>
+          <t>(4.18, 38.29)</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>(3.59, 32.93)</t>
+          <t>(2.79, 25.59)</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>(2.66, 24.4)</t>
+          <t>(2.07, 18.96)</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(2.1, 19.23)</t>
+          <t>(1.63, 14.94)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>(1.72, 15.78)</t>
+          <t>(1.34, 12.26)</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>(1.45, 13.32)</t>
+          <t>(1.13, 10.35)</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>(1.25, 11.49)</t>
+          <t>(0.97, 8.93)</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>(1.1, 10.08)</t>
+          <t>(0.85, 7.83)</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>(0.98, 8.96)</t>
+          <t>(0.76, 6.96)</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -13682,52 +13682,52 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>(70.53, 91.27)</t>
+          <t>(54.8, 70.92)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>(38.08, 49.28)</t>
+          <t>(29.59, 38.29)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>(25.45, 32.93)</t>
+          <t>(19.77, 25.59)</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>(18.86, 24.4)</t>
+          <t>(14.65, 18.96)</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(14.86, 19.23)</t>
+          <t>(11.54, 14.94)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>(12.19, 15.78)</t>
+          <t>(9.47, 12.26)</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>(10.29, 13.32)</t>
+          <t>(8.0, 10.35)</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>(8.88, 11.49)</t>
+          <t>(6.9, 8.93)</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>(7.79, 10.08)</t>
+          <t>(6.05, 7.83)</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>(6.92, 8.96)</t>
+          <t>(5.38, 6.96)</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -13750,52 +13750,52 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>(23.99, 156.76)</t>
+          <t>(18.64, 121.82)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>(12.95, 84.64)</t>
+          <t>(10.06, 65.76)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>(8.66, 56.56)</t>
+          <t>(6.73, 43.95)</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>(6.41, 41.92)</t>
+          <t>(4.98, 32.57)</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(5.05, 33.03)</t>
+          <t>(3.93, 25.66)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>(4.15, 27.1)</t>
+          <t>(3.22, 21.05)</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>(3.5, 22.88)</t>
+          <t>(2.72, 17.78)</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>(3.02, 19.74)</t>
+          <t>(2.35, 15.33)</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>(2.65, 17.31)</t>
+          <t>(2.06, 13.45)</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>(2.36, 15.39)</t>
+          <t>(1.83, 11.96)</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -13818,52 +13818,52 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>(132.77, 156.76)</t>
+          <t>(103.17, 121.82)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>(71.68, 84.64)</t>
+          <t>(55.7, 65.76)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>(47.9, 56.56)</t>
+          <t>(37.22, 43.95)</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>(35.5, 41.92)</t>
+          <t>(27.58, 32.57)</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(27.97, 33.03)</t>
+          <t>(21.73, 25.66)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>(22.95, 27.1)</t>
+          <t>(17.83, 21.05)</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>(19.38, 22.88)</t>
+          <t>(15.05, 17.78)</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>(16.72, 19.74)</t>
+          <t>(12.99, 15.33)</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>(14.66, 17.31)</t>
+          <t>(11.39, 13.45)</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>(13.03, 15.39)</t>
+          <t>(10.13, 11.96)</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -13886,52 +13886,52 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>(52.96, 305.33)</t>
+          <t>(41.15, 237.26)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>(28.59, 164.85)</t>
+          <t>(22.22, 128.09)</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>(19.11, 110.16)</t>
+          <t>(14.85, 85.6)</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>(14.16, 81.64)</t>
+          <t>(11.0, 63.43)</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(11.16, 64.32)</t>
+          <t>(8.67, 49.98)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>(9.15, 52.77)</t>
+          <t>(7.11, 41.0)</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>(7.73, 44.56)</t>
+          <t>(6.0, 34.62)</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>(6.67, 38.44)</t>
+          <t>(5.18, 29.87)</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>(5.85, 33.72)</t>
+          <t>(4.54, 26.2)</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>(5.2, 29.98)</t>
+          <t>(4.04, 23.29)</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -13954,52 +13954,52 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>(252.37, 305.33)</t>
+          <t>(196.11, 237.26)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>(136.26, 164.85)</t>
+          <t>(105.87, 128.09)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>(91.06, 110.16)</t>
+          <t>(70.75, 85.6)</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>(67.48, 81.64)</t>
+          <t>(52.43, 63.43)</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(53.17, 64.32)</t>
+          <t>(41.31, 49.98)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>(43.62, 52.77)</t>
+          <t>(33.89, 41.0)</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>(36.83, 44.56)</t>
+          <t>(28.62, 34.62)</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>(31.77, 38.44)</t>
+          <t>(24.69, 29.87)</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>(27.87, 33.72)</t>
+          <t>(21.66, 26.2)</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>(24.78, 29.98)</t>
+          <t>(19.25, 23.29)</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -14022,52 +14022,52 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>(0.0, 158.74)</t>
+          <t>(0.0, 123.35)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>(0.0, 85.7)</t>
+          <t>(0.0, 66.59)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>(0.0, 57.27)</t>
+          <t>(0.0, 44.5)</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>(0.0, 42.45)</t>
+          <t>(0.0, 32.98)</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(0.0, 33.44)</t>
+          <t>(0.0, 25.98)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>(0.0, 27.44)</t>
+          <t>(0.0, 21.32)</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>(0.0, 23.17)</t>
+          <t>(0.0, 18.0)</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>(0.0, 19.99)</t>
+          <t>(0.0, 15.53)</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>(0.0, 17.53)</t>
+          <t>(0.0, 13.62)</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>(0.0, 15.58)</t>
+          <t>(0.0, 12.11)</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -14090,52 +14090,52 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>(0.0, 158.74)</t>
+          <t>(0.0, 123.35)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>(0.0, 85.7)</t>
+          <t>(0.0, 66.59)</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>(0.0, 57.27)</t>
+          <t>(0.0, 44.5)</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>(0.0, 42.45)</t>
+          <t>(0.0, 32.98)</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(0.0, 33.44)</t>
+          <t>(0.0, 25.98)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>(0.0, 27.44)</t>
+          <t>(0.0, 21.32)</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>(0.0, 23.17)</t>
+          <t>(0.0, 18.0)</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>(0.0, 19.99)</t>
+          <t>(0.0, 15.53)</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>(0.0, 17.53)</t>
+          <t>(0.0, 13.62)</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>(0.0, 15.58)</t>
+          <t>(0.0, 12.11)</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -16363,25 +16363,25 @@
         <v>0.01824146924750992</v>
       </c>
       <c r="E2" t="n">
-        <v>31.02154776701865</v>
+        <v>31.02154776701866</v>
       </c>
       <c r="F2" t="n">
-        <v>2680.261727070411</v>
+        <v>2680.261727070412</v>
       </c>
       <c r="G2" t="n">
-        <v>1.457662084409439</v>
+        <v>1.200427598925421</v>
       </c>
       <c r="H2" t="n">
         <v>2.9348865911421</v>
       </c>
       <c r="I2" t="n">
-        <v>2547279.289764409</v>
+        <v>1824676.826353009</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01526095200714532</v>
+        <v>0.01538535729238877</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8264256458975006</v>
+        <v>0.6421900859217268</v>
       </c>
     </row>
     <row r="3">
@@ -16400,25 +16400,25 @@
         <v>0.05067074790974978</v>
       </c>
       <c r="E3" t="n">
-        <v>86.17096601949626</v>
+        <v>86.17096601949629</v>
       </c>
       <c r="F3" t="n">
-        <v>7445.171464084477</v>
+        <v>7445.17146408448</v>
       </c>
       <c r="G3" t="n">
-        <v>1.457662084409439</v>
+        <v>1.200427598925421</v>
       </c>
       <c r="H3" t="n">
-        <v>8.152462753172502</v>
+        <v>8.152462753172506</v>
       </c>
       <c r="I3" t="n">
-        <v>4245465.482940682</v>
+        <v>3041128.043921682</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01373215657536467</v>
+        <v>0.01384316824346184</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4461821134899511</v>
+        <v>0.3466911519082727</v>
       </c>
     </row>
     <row r="4">
@@ -16437,25 +16437,25 @@
         <v>0.09931466590310954</v>
       </c>
       <c r="E4" t="n">
-        <v>168.8950933982126</v>
+        <v>168.8950933982127</v>
       </c>
       <c r="F4" t="n">
-        <v>14592.53606960557</v>
+        <v>14592.53606960558</v>
       </c>
       <c r="G4" t="n">
-        <v>1.457662084409439</v>
+        <v>1.200427598925421</v>
       </c>
       <c r="H4" t="n">
-        <v>15.9788269962181</v>
+        <v>15.97882699621811</v>
       </c>
       <c r="I4" t="n">
-        <v>5943651.676116955</v>
+        <v>4257579.261490354</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0128476948598514</v>
+        <v>0.01295112329939843</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2981745601793407</v>
+        <v>0.2316789963626576</v>
       </c>
     </row>
     <row r="5">
@@ -16480,19 +16480,19 @@
         <v>24122.35554363371</v>
       </c>
       <c r="G5" t="n">
-        <v>1.457662084409439</v>
+        <v>1.200427598925421</v>
       </c>
       <c r="H5" t="n">
         <v>26.41397932027891</v>
       </c>
       <c r="I5" t="n">
-        <v>7641837.869293228</v>
+        <v>5474030.479059028</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01224184464939308</v>
+        <v>0.01234015035010719</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2209773537634847</v>
+        <v>0.171694034854443</v>
       </c>
     </row>
     <row r="6">
@@ -16511,25 +16511,25 @@
         <v>0.2452464198831888</v>
       </c>
       <c r="E6" t="n">
-        <v>417.0674755343618</v>
+        <v>417.067475534362</v>
       </c>
       <c r="F6" t="n">
-        <v>36034.62988616886</v>
+        <v>36034.62988616887</v>
       </c>
       <c r="G6" t="n">
-        <v>1.457662084409439</v>
+        <v>1.200427598925421</v>
       </c>
       <c r="H6" t="n">
-        <v>39.45791972535491</v>
+        <v>39.45791972535492</v>
       </c>
       <c r="I6" t="n">
-        <v>9340024.062469501</v>
+        <v>6690481.6966277</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01178843874176854</v>
+        <v>0.0118829494532778</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1741033068053998</v>
+        <v>0.1352722861220867</v>
       </c>
     </row>
     <row r="7">
@@ -16548,25 +16548,25 @@
         <v>0.3425342558699084</v>
       </c>
       <c r="E7" t="n">
-        <v>582.5157302917946</v>
+        <v>582.5157302917949</v>
       </c>
       <c r="F7" t="n">
-        <v>50329.35909721105</v>
+        <v>50329.35909721108</v>
       </c>
       <c r="G7" t="n">
-        <v>1.457662084409439</v>
+        <v>1.200427598925421</v>
       </c>
       <c r="H7" t="n">
-        <v>55.1106482114461</v>
+        <v>55.11064821144612</v>
       </c>
       <c r="I7" t="n">
-        <v>11038210.25564577</v>
+        <v>7906932.914196372</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01142999900920052</v>
+        <v>0.01152153335738611</v>
       </c>
       <c r="K7" t="n">
-        <v>0.142838820218025</v>
+        <v>0.1109798655573259</v>
       </c>
     </row>
     <row r="8">
@@ -16585,25 +16585,25 @@
         <v>0.456036731187748</v>
       </c>
       <c r="E8" t="n">
-        <v>775.5386941754664</v>
+        <v>775.5386941754667</v>
       </c>
       <c r="F8" t="n">
-        <v>67006.5431767603</v>
+        <v>67006.54317676033</v>
       </c>
       <c r="G8" t="n">
-        <v>1.457662084409439</v>
+        <v>1.200427598925421</v>
       </c>
       <c r="H8" t="n">
-        <v>73.37216477855253</v>
+        <v>73.37216477855256</v>
       </c>
       <c r="I8" t="n">
-        <v>12736396.44882205</v>
+        <v>9123384.131765045</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01113584610178152</v>
+        <v>0.01122495372138249</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1206077943626459</v>
+        <v>0.09370668302085056</v>
       </c>
     </row>
     <row r="9">
@@ -16622,25 +16622,25 @@
         <v>0.5857538458367073</v>
       </c>
       <c r="E9" t="n">
-        <v>996.1363671853766</v>
+        <v>996.1363671853769</v>
       </c>
       <c r="F9" t="n">
-        <v>86066.18212481654</v>
+        <v>86066.18212481657</v>
       </c>
       <c r="G9" t="n">
-        <v>1.457662084409439</v>
+        <v>1.200427598925421</v>
       </c>
       <c r="H9" t="n">
-        <v>94.24246942667411</v>
+        <v>94.24246942667413</v>
       </c>
       <c r="I9" t="n">
-        <v>14434582.64199832</v>
+        <v>10339835.34933372</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01088781240816079</v>
+        <v>0.01097488494094747</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1040483319506292</v>
+        <v>0.08084037503130398</v>
       </c>
     </row>
     <row r="10">
@@ -16662,22 +16662,22 @@
         <v>1244.308749321526</v>
       </c>
       <c r="F10" t="n">
-        <v>107508.2759413798</v>
+        <v>107508.2759413799</v>
       </c>
       <c r="G10" t="n">
-        <v>1.457662084409439</v>
+        <v>1.200427598925421</v>
       </c>
       <c r="H10" t="n">
-        <v>117.7215621558109</v>
+        <v>117.721562155811</v>
       </c>
       <c r="I10" t="n">
-        <v>16132768.83517459</v>
+        <v>11556286.56690239</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01067431523357295</v>
+        <v>0.01075964427718696</v>
       </c>
       <c r="K10" t="n">
-        <v>0.09127037550291132</v>
+        <v>0.07091230096464102</v>
       </c>
     </row>
     <row r="11">
@@ -16702,19 +16702,19 @@
         <v>131332.8246264502</v>
       </c>
       <c r="G11" t="n">
-        <v>1.457662084409439</v>
+        <v>1.200427598925421</v>
       </c>
       <c r="H11" t="n">
         <v>143.8094429659629</v>
       </c>
       <c r="I11" t="n">
-        <v>17830955.02835086</v>
+        <v>12772737.78447106</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01048754992900408</v>
+        <v>0.01057136006073237</v>
       </c>
       <c r="K11" t="n">
-        <v>0.08113311691453198</v>
+        <v>0.06303602738903012</v>
       </c>
     </row>
   </sheetData>

--- a/data/PV_complete_parameters_definition.xlsx
+++ b/data/PV_complete_parameters_definition.xlsx
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>98.13</v>
+        <v>86.34</v>
       </c>
       <c r="J2" t="n">
-        <v>49.92</v>
+        <v>43.92</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -867,10 +867,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>48.21</v>
+        <v>42.42</v>
       </c>
       <c r="J3" t="n">
-        <v>-49.92</v>
+        <v>-43.92</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>21.28</v>
+        <v>18.73</v>
       </c>
       <c r="J4" t="n">
-        <v>-67.87</v>
+        <v>-59.72</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -977,10 +977,10 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>89.15000000000001</v>
+        <v>78.44</v>
       </c>
       <c r="J5" t="n">
-        <v>67.87</v>
+        <v>59.72</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>49.41</v>
+        <v>43.47</v>
       </c>
       <c r="J6" t="n">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>47.87</v>
+        <v>42.12</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.54</v>
+        <v>-1.35</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>6.07</v>
+        <v>5.34</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.33</v>
+        <v>-2.93</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1197,10 +1197,10 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>9.4</v>
+        <v>8.27</v>
       </c>
       <c r="J9" t="n">
-        <v>3.33</v>
+        <v>2.93</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>106.16</v>
+        <v>93.41</v>
       </c>
       <c r="J10" t="n">
-        <v>60.95</v>
+        <v>53.62</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>45.22</v>
+        <v>39.79</v>
       </c>
       <c r="J11" t="n">
-        <v>-60.95</v>
+        <v>-53.62</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>36.67</v>
+        <v>32.27</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.99</v>
+        <v>-2.63</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>39.66</v>
+        <v>34.9</v>
       </c>
       <c r="J13" t="n">
-        <v>2.99</v>
+        <v>2.63</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>110.86</v>
+        <v>97.55</v>
       </c>
       <c r="J14" t="n">
-        <v>-11.71</v>
+        <v>-10.3</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>122.57</v>
+        <v>107.85</v>
       </c>
       <c r="J15" t="n">
-        <v>11.71</v>
+        <v>10.3</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>44.19</v>
+        <v>38.88</v>
       </c>
       <c r="J16" t="n">
-        <v>17.86</v>
+        <v>15.72</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>26.33</v>
+        <v>23.16</v>
       </c>
       <c r="J17" t="n">
-        <v>-17.86</v>
+        <v>-15.72</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>15.13</v>
+        <v>13.31</v>
       </c>
       <c r="J18" t="n">
-        <v>6.5</v>
+        <v>5.72</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1747,10 +1747,10 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>8.630000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="J19" t="n">
-        <v>-6.5</v>
+        <v>-5.72</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>84.11</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>-13.16</v>
+        <v>-11.58</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>97.27</v>
+        <v>85.59</v>
       </c>
       <c r="J23" t="n">
-        <v>13.16</v>
+        <v>11.58</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>68.81</v>
+        <v>60.54</v>
       </c>
       <c r="J24" t="n">
-        <v>45.13</v>
+        <v>39.71</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>23.68</v>
+        <v>20.83</v>
       </c>
       <c r="J25" t="n">
-        <v>-45.13</v>
+        <v>-39.71</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>55.82</v>
+        <v>49.11</v>
       </c>
       <c r="J26" t="n">
-        <v>-97.09999999999999</v>
+        <v>-85.44</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>152.92</v>
+        <v>134.55</v>
       </c>
       <c r="J27" t="n">
-        <v>97.09999999999999</v>
+        <v>85.44</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2242,10 +2242,10 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>19.66</v>
+        <v>17.3</v>
       </c>
       <c r="J28" t="n">
-        <v>-9.57</v>
+        <v>-8.42</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>29.23</v>
+        <v>25.72</v>
       </c>
       <c r="J29" t="n">
-        <v>9.57</v>
+        <v>8.42</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>53.94</v>
+        <v>47.46</v>
       </c>
       <c r="J32" t="n">
-        <v>-22.05</v>
+        <v>-19.4</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>75.98999999999999</v>
+        <v>66.86</v>
       </c>
       <c r="J33" t="n">
-        <v>22.05</v>
+        <v>19.4</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>45.99</v>
+        <v>40.46</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.45</v>
+        <v>-10.08</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>57.44</v>
+        <v>50.54</v>
       </c>
       <c r="J37" t="n">
-        <v>11.45</v>
+        <v>10.08</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>54.71</v>
+        <v>48.13</v>
       </c>
       <c r="J38" t="n">
-        <v>-52.06</v>
+        <v>-45.8</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2847,10 +2847,10 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>106.76</v>
+        <v>93.94</v>
       </c>
       <c r="J39" t="n">
-        <v>52.06</v>
+        <v>45.8</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>52.14</v>
+        <v>45.88</v>
       </c>
       <c r="J40" t="n">
-        <v>-21.11</v>
+        <v>-18.58</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>73.25</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>21.11</v>
+        <v>18.58</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>162.92</v>
+        <v>143.35</v>
       </c>
       <c r="J42" t="n">
-        <v>2.31</v>
+        <v>2.03</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>160.61</v>
+        <v>141.32</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.31</v>
+        <v>-2.03</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3122,10 +3122,10 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>39.15</v>
+        <v>34.45</v>
       </c>
       <c r="J44" t="n">
-        <v>39.15</v>
+        <v>34.45</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>-39.15</v>
+        <v>-34.45</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>63.68</v>
+        <v>56.03</v>
       </c>
       <c r="J46" t="n">
-        <v>18.12</v>
+        <v>15.94</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>45.56</v>
+        <v>40.09</v>
       </c>
       <c r="J47" t="n">
-        <v>-18.12</v>
+        <v>-15.94</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -3342,10 +3342,10 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>58.21</v>
+        <v>51.22</v>
       </c>
       <c r="J48" t="n">
-        <v>25.99</v>
+        <v>22.86</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>32.22</v>
+        <v>28.35</v>
       </c>
       <c r="J49" t="n">
-        <v>-25.99</v>
+        <v>-22.86</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>27.27</v>
+        <v>23.99</v>
       </c>
       <c r="J50" t="n">
-        <v>7.95</v>
+        <v>6.99</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>19.32</v>
+        <v>17</v>
       </c>
       <c r="J51" t="n">
-        <v>-7.95</v>
+        <v>-6.99</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -3562,10 +3562,10 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>190.36</v>
+        <v>167.49</v>
       </c>
       <c r="J52" t="n">
-        <v>87.53</v>
+        <v>77.02</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>102.83</v>
+        <v>90.48</v>
       </c>
       <c r="J53" t="n">
-        <v>-87.53</v>
+        <v>-77.02</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>120.18</v>
+        <v>105.75</v>
       </c>
       <c r="J54" t="n">
-        <v>47.27</v>
+        <v>41.59</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>72.91</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="J55" t="n">
-        <v>-47.27</v>
+        <v>-41.59</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>51.46</v>
+        <v>45.28</v>
       </c>
       <c r="J56" t="n">
-        <v>-2.65</v>
+        <v>-2.33</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>54.11</v>
+        <v>47.61</v>
       </c>
       <c r="J57" t="n">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>17.78</v>
+        <v>15.64</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.14</v>
+        <v>-1.88</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>19.92</v>
+        <v>17.52</v>
       </c>
       <c r="J59" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>-29.06</v>
+        <v>-25.57</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -4057,10 +4057,10 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>29.06</v>
+        <v>25.57</v>
       </c>
       <c r="J61" t="n">
-        <v>29.06</v>
+        <v>25.57</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -4112,10 +4112,10 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>50.86</v>
+        <v>44.75</v>
       </c>
       <c r="J62" t="n">
-        <v>-72.66</v>
+        <v>-63.93</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>123.51</v>
+        <v>108.68</v>
       </c>
       <c r="J63" t="n">
-        <v>72.66</v>
+        <v>63.93</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>86.42</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="J64" t="n">
-        <v>-50.35</v>
+        <v>-44.3</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>136.76</v>
+        <v>120.34</v>
       </c>
       <c r="J65" t="n">
-        <v>50.35</v>
+        <v>44.3</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -4442,10 +4442,10 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>48.89</v>
+        <v>43.02</v>
       </c>
       <c r="J68" t="n">
-        <v>-97.09999999999999</v>
+        <v>-85.44</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -4497,10 +4497,10 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>146</v>
+        <v>128.46</v>
       </c>
       <c r="J69" t="n">
-        <v>97.09999999999999</v>
+        <v>85.44</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -4552,10 +4552,10 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>21.88</v>
+        <v>19.25</v>
       </c>
       <c r="J70" t="n">
-        <v>-4.7</v>
+        <v>-4.14</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>26.58</v>
+        <v>23.39</v>
       </c>
       <c r="J71" t="n">
-        <v>4.7</v>
+        <v>4.14</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -4662,10 +4662,10 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>56.59</v>
+        <v>49.79</v>
       </c>
       <c r="J72" t="n">
-        <v>-20.86</v>
+        <v>-18.35</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>77.44</v>
+        <v>68.14</v>
       </c>
       <c r="J73" t="n">
-        <v>20.86</v>
+        <v>18.35</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>108.04</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="J74" t="n">
-        <v>89.06999999999999</v>
+        <v>78.37</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>18.98</v>
+        <v>16.7</v>
       </c>
       <c r="J75" t="n">
-        <v>-89.06999999999999</v>
+        <v>-78.37</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>115.99</v>
+        <v>102.06</v>
       </c>
       <c r="J78" t="n">
-        <v>19.4</v>
+        <v>17.07</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -5047,10 +5047,10 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>96.59</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="J79" t="n">
-        <v>-19.4</v>
+        <v>-17.07</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>11.37</v>
+        <v>10</v>
       </c>
       <c r="J80" t="n">
-        <v>10.09</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -5157,10 +5157,10 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.09</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -5212,10 +5212,10 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>39.66</v>
+        <v>34.9</v>
       </c>
       <c r="J82" t="n">
-        <v>19.49</v>
+        <v>17.15</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>20.17</v>
+        <v>17.75</v>
       </c>
       <c r="J83" t="n">
-        <v>-19.49</v>
+        <v>-17.15</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -5322,10 +5322,10 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>45.22</v>
+        <v>39.79</v>
       </c>
       <c r="J84" t="n">
-        <v>-65.90000000000001</v>
+        <v>-57.99</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -5377,10 +5377,10 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>111.12</v>
+        <v>97.77</v>
       </c>
       <c r="J85" t="n">
-        <v>65.90000000000001</v>
+        <v>57.99</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>75.65000000000001</v>
+        <v>66.56</v>
       </c>
       <c r="J86" t="n">
-        <v>47.27</v>
+        <v>41.59</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>28.38</v>
+        <v>24.97</v>
       </c>
       <c r="J87" t="n">
-        <v>-47.27</v>
+        <v>-41.59</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -5542,10 +5542,10 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>69.48999999999999</v>
+        <v>61.15</v>
       </c>
       <c r="J88" t="n">
-        <v>19.66</v>
+        <v>17.3</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>49.83</v>
+        <v>43.85</v>
       </c>
       <c r="J89" t="n">
-        <v>-19.66</v>
+        <v>-17.3</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -5652,10 +5652,10 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>81.63</v>
+        <v>71.83</v>
       </c>
       <c r="J90" t="n">
-        <v>49.49</v>
+        <v>43.55</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -5707,10 +5707,10 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>32.14</v>
+        <v>28.28</v>
       </c>
       <c r="J91" t="n">
-        <v>-49.49</v>
+        <v>-43.55</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -5762,10 +5762,10 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>38.55</v>
+        <v>33.92</v>
       </c>
       <c r="J92" t="n">
-        <v>-1.62</v>
+        <v>-1.43</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>40.17</v>
+        <v>35.35</v>
       </c>
       <c r="J93" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>82.66</v>
+        <v>72.73</v>
       </c>
       <c r="J94" t="n">
-        <v>34.11</v>
+        <v>30.01</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>48.55</v>
+        <v>42.72</v>
       </c>
       <c r="J95" t="n">
-        <v>-34.11</v>
+        <v>-30.01</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -5982,10 +5982,10 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>55.9</v>
+        <v>49.19</v>
       </c>
       <c r="J96" t="n">
-        <v>-4.87</v>
+        <v>-4.29</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -6037,10 +6037,10 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>60.77</v>
+        <v>53.47</v>
       </c>
       <c r="J97" t="n">
-        <v>4.87</v>
+        <v>4.29</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -6092,10 +6092,10 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>120.52</v>
+        <v>106.05</v>
       </c>
       <c r="J98" t="n">
-        <v>50.6</v>
+        <v>44.52</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>69.92</v>
+        <v>61.52</v>
       </c>
       <c r="J99" t="n">
-        <v>-50.6</v>
+        <v>-44.52</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -6202,10 +6202,10 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>80.95</v>
+        <v>71.22</v>
       </c>
       <c r="J100" t="n">
-        <v>-21.28</v>
+        <v>-18.73</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>102.23</v>
+        <v>89.95</v>
       </c>
       <c r="J101" t="n">
-        <v>21.28</v>
+        <v>18.73</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -6312,10 +6312,10 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>45.9</v>
+        <v>40.39</v>
       </c>
       <c r="J102" t="n">
-        <v>-9.57</v>
+        <v>-8.42</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>55.47</v>
+        <v>48.81</v>
       </c>
       <c r="J103" t="n">
-        <v>9.57</v>
+        <v>8.42</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -6422,10 +6422,10 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>90.09</v>
+        <v>79.27</v>
       </c>
       <c r="J104" t="n">
-        <v>-29.23</v>
+        <v>-25.72</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -6477,10 +6477,10 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>119.33</v>
+        <v>104.99</v>
       </c>
       <c r="J105" t="n">
-        <v>29.23</v>
+        <v>25.72</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -6532,10 +6532,10 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>104.62</v>
+        <v>92.06</v>
       </c>
       <c r="J106" t="n">
-        <v>15.81</v>
+        <v>13.91</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>88.81</v>
+        <v>78.14</v>
       </c>
       <c r="J107" t="n">
-        <v>-15.81</v>
+        <v>-13.91</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -6814,52 +6814,52 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(194.15, 271.94)</t>
+          <t>(249.85, 349.96)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(104.82, 146.81)</t>
+          <t>(134.89, 188.94)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>(70.04, 98.11)</t>
+          <t>(90.15, 126.26)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>(51.91, 72.71)</t>
+          <t>(66.81, 93.58)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(40.9, 57.28)</t>
+          <t>(52.64, 73.73)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>(33.55, 47.0)</t>
+          <t>(43.18, 60.49)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>(28.33, 39.68)</t>
+          <t>(36.46, 51.07)</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>(24.44, 34.23)</t>
+          <t>(31.46, 44.06)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>(21.44, 30.03)</t>
+          <t>(27.59, 38.65)</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>(19.06, 26.69)</t>
+          <t>(24.53, 34.36)</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -6882,52 +6882,52 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>(77.79, 271.94)</t>
+          <t>(100.1, 349.96)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>(41.99, 146.81)</t>
+          <t>(54.05, 188.94)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>(28.06, 98.11)</t>
+          <t>(36.12, 126.26)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>(20.8, 72.71)</t>
+          <t>(26.77, 93.58)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(16.39, 57.28)</t>
+          <t>(21.09, 73.73)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>(13.44, 47.0)</t>
+          <t>(17.3, 60.49)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>(11.35, 39.68)</t>
+          <t>(14.61, 51.07)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>(9.79, 34.23)</t>
+          <t>(12.6, 44.06)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>(8.59, 30.03)</t>
+          <t>(11.06, 38.65)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>(7.64, 26.69)</t>
+          <t>(9.83, 34.36)</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -6950,52 +6950,52 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(224.9, 315.51)</t>
+          <t>(289.42, 406.02)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>(121.41, 170.33)</t>
+          <t>(156.26, 219.21)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>(81.14, 113.82)</t>
+          <t>(104.42, 146.49)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>(60.13, 84.35)</t>
+          <t>(77.39, 108.57)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(47.37, 66.46)</t>
+          <t>(60.97, 85.54)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>(38.87, 54.52)</t>
+          <t>(50.02, 70.18)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>(32.82, 46.04)</t>
+          <t>(42.24, 59.25)</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>(28.31, 39.72)</t>
+          <t>(36.44, 51.12)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>(24.83, 34.84)</t>
+          <t>(31.96, 44.84)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>(22.08, 30.97)</t>
+          <t>(28.41, 39.86)</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -7018,52 +7018,52 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(89.96, 315.51)</t>
+          <t>(115.77, 406.02)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>(48.56, 170.33)</t>
+          <t>(62.5, 219.21)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>(32.45, 113.82)</t>
+          <t>(41.77, 146.49)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>(24.05, 84.35)</t>
+          <t>(30.95, 108.57)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(18.95, 66.46)</t>
+          <t>(24.39, 85.54)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>(15.55, 54.52)</t>
+          <t>(20.01, 70.18)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>(13.13, 46.04)</t>
+          <t>(16.89, 59.25)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>(11.32, 39.72)</t>
+          <t>(14.58, 51.12)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>(9.93, 34.84)</t>
+          <t>(12.79, 44.84)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>(8.83, 30.97)</t>
+          <t>(11.37, 39.86)</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -7086,52 +7086,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>(77.12, 288.23)</t>
+          <t>(99.25, 370.92)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(41.63, 155.61)</t>
+          <t>(53.58, 200.26)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>(27.82, 103.98)</t>
+          <t>(35.81, 133.83)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>(20.62, 77.06)</t>
+          <t>(26.54, 99.18)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(16.24, 60.71)</t>
+          <t>(20.91, 78.14)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>(13.33, 49.81)</t>
+          <t>(17.15, 64.11)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>(11.25, 42.06)</t>
+          <t>(14.48, 54.13)</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>(9.71, 36.28)</t>
+          <t>(12.5, 46.7)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>(8.52, 31.83)</t>
+          <t>(10.96, 40.96)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>(7.57, 28.29)</t>
+          <t>(9.74, 36.41)</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -7154,52 +7154,52 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>(211.11, 288.23)</t>
+          <t>(271.68, 370.92)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>(113.97, 155.61)</t>
+          <t>(146.68, 200.26)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>(76.16, 103.98)</t>
+          <t>(98.02, 133.83)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>(56.44, 77.06)</t>
+          <t>(72.64, 99.18)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(44.47, 60.71)</t>
+          <t>(57.23, 78.14)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>(36.48, 49.81)</t>
+          <t>(46.96, 64.11)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>(30.81, 42.06)</t>
+          <t>(39.65, 54.13)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>(26.58, 36.28)</t>
+          <t>(34.2, 46.7)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>(23.31, 31.83)</t>
+          <t>(30.0, 40.96)</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>(20.72, 28.29)</t>
+          <t>(26.67, 36.41)</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -7222,52 +7222,52 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>(7.1, 44.21)</t>
+          <t>(9.14, 56.9)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(3.83, 23.87)</t>
+          <t>(4.93, 30.72)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>(2.56, 15.95)</t>
+          <t>(3.3, 20.53)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>(1.9, 11.82)</t>
+          <t>(2.44, 15.21)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(1.5, 9.31)</t>
+          <t>(1.93, 11.99)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>(1.23, 7.64)</t>
+          <t>(1.58, 9.83)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>(1.04, 6.45)</t>
+          <t>(1.33, 8.3)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>(0.89, 5.57)</t>
+          <t>(1.15, 7.16)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>(0.78, 4.88)</t>
+          <t>(1.01, 6.28)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>(0.7, 4.34)</t>
+          <t>(0.9, 5.59)</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -7290,52 +7290,52 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>(37.11, 44.21)</t>
+          <t>(47.76, 56.9)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>(20.04, 23.87)</t>
+          <t>(25.78, 30.72)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>(13.39, 15.95)</t>
+          <t>(17.23, 20.53)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>(9.92, 11.82)</t>
+          <t>(12.77, 15.21)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(7.82, 9.31)</t>
+          <t>(10.06, 11.99)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>(6.41, 7.64)</t>
+          <t>(8.25, 9.83)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>(5.42, 6.45)</t>
+          <t>(6.97, 8.3)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>(4.67, 5.57)</t>
+          <t>(6.01, 7.16)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>(4.1, 4.88)</t>
+          <t>(5.27, 6.28)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>(3.64, 4.34)</t>
+          <t>(4.69, 5.59)</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -7358,52 +7358,52 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>(64.05, 97.2)</t>
+          <t>(82.42, 125.08)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>(34.58, 52.47)</t>
+          <t>(44.5, 67.53)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>(23.11, 35.06)</t>
+          <t>(29.74, 45.13)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>(17.12, 25.99)</t>
+          <t>(22.04, 33.44)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(13.49, 20.47)</t>
+          <t>(17.36, 26.35)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>(11.07, 16.8)</t>
+          <t>(14.25, 21.62)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>(9.35, 14.18)</t>
+          <t>(12.03, 18.25)</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>(8.06, 12.24)</t>
+          <t>(10.38, 15.75)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>(7.07, 10.73)</t>
+          <t>(9.1, 13.81)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>(6.29, 9.54)</t>
+          <t>(8.09, 12.28)</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -7426,52 +7426,52 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>(33.15, 97.2)</t>
+          <t>(42.66, 125.08)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>(17.9, 52.47)</t>
+          <t>(23.03, 67.53)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>(11.96, 35.06)</t>
+          <t>(15.39, 45.13)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>(8.86, 25.99)</t>
+          <t>(11.41, 33.44)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(6.98, 20.47)</t>
+          <t>(8.99, 26.35)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>(5.73, 16.8)</t>
+          <t>(7.37, 21.62)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>(4.84, 14.18)</t>
+          <t>(6.23, 18.25)</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>(4.17, 12.24)</t>
+          <t>(5.37, 15.75)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>(3.66, 10.73)</t>
+          <t>(4.71, 13.81)</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>(3.25, 9.54)</t>
+          <t>(4.19, 12.28)</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -7494,52 +7494,52 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>(42.19, 51.52)</t>
+          <t>(54.29, 66.3)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>(22.77, 27.82)</t>
+          <t>(29.31, 35.8)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>(15.22, 18.59)</t>
+          <t>(19.59, 23.92)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>(11.28, 13.78)</t>
+          <t>(14.52, 17.73)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(8.89, 10.85)</t>
+          <t>(11.44, 13.97)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>(7.29, 8.9)</t>
+          <t>(9.38, 11.46)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>(6.16, 7.52)</t>
+          <t>(7.92, 9.68)</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>(5.31, 6.49)</t>
+          <t>(6.83, 8.35)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>(4.66, 5.69)</t>
+          <t>(6.0, 7.32)</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>(4.14, 5.06)</t>
+          <t>(5.33, 6.51)</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -7562,52 +7562,52 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>(9.34, 51.52)</t>
+          <t>(12.02, 66.3)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(5.04, 27.82)</t>
+          <t>(6.49, 35.8)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>(3.37, 18.59)</t>
+          <t>(4.34, 23.92)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>(2.5, 13.78)</t>
+          <t>(3.21, 17.73)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(1.97, 10.85)</t>
+          <t>(2.53, 13.97)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>(1.61, 8.9)</t>
+          <t>(2.08, 11.46)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>(1.36, 7.52)</t>
+          <t>(1.75, 9.68)</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>(1.18, 6.49)</t>
+          <t>(1.51, 8.35)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>(1.03, 5.69)</t>
+          <t>(1.33, 7.32)</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>(0.92, 5.06)</t>
+          <t>(1.18, 6.51)</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -7630,52 +7630,52 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>(225.43, 332.69)</t>
+          <t>(290.11, 428.14)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>(121.7, 179.61)</t>
+          <t>(156.63, 231.15)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>(81.33, 120.02)</t>
+          <t>(104.67, 154.47)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>(60.27, 88.95)</t>
+          <t>(77.57, 114.48)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(47.49, 70.08)</t>
+          <t>(61.12, 90.2)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>(38.96, 57.49)</t>
+          <t>(50.14, 74.0)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>(32.89, 48.55)</t>
+          <t>(42.34, 62.48)</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>(28.38, 41.88)</t>
+          <t>(36.53, 53.9)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>(24.89, 36.74)</t>
+          <t>(32.04, 47.28)</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>(22.13, 32.66)</t>
+          <t>(28.48, 42.03)</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -7698,52 +7698,52 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>(107.26, 332.69)</t>
+          <t>(138.03, 428.14)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>(57.9, 179.61)</t>
+          <t>(74.52, 231.15)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>(38.7, 120.02)</t>
+          <t>(49.8, 154.47)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>(28.68, 88.95)</t>
+          <t>(36.91, 114.48)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(22.59, 70.08)</t>
+          <t>(29.08, 90.2)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>(18.54, 57.49)</t>
+          <t>(23.86, 74.0)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>(15.65, 48.55)</t>
+          <t>(20.14, 62.48)</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>(13.5, 41.88)</t>
+          <t>(17.38, 53.9)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>(11.84, 36.74)</t>
+          <t>(15.24, 47.28)</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>(10.53, 32.66)</t>
+          <t>(13.55, 42.03)</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -7766,52 +7766,52 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>(309.72, 311.32)</t>
+          <t>(398.57, 400.63)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>(167.2, 168.07)</t>
+          <t>(215.18, 216.3)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>(111.73, 112.31)</t>
+          <t>(143.8, 144.55)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>(82.8, 83.23)</t>
+          <t>(106.57, 107.13)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(65.24, 65.58)</t>
+          <t>(83.97, 84.4)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>(53.52, 53.8)</t>
+          <t>(68.89, 69.25)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>(45.19, 45.43)</t>
+          <t>(58.17, 58.47)</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>(38.99, 39.19)</t>
+          <t>(50.18, 50.44)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>(34.2, 34.38)</t>
+          <t>(44.02, 44.25)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>(30.4, 30.56)</t>
+          <t>(39.13, 39.33)</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -7834,52 +7834,52 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>(1.61, 311.32)</t>
+          <t>(2.07, 400.63)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>(0.87, 168.07)</t>
+          <t>(1.12, 216.3)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>(0.58, 112.31)</t>
+          <t>(0.75, 144.55)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>(0.43, 83.23)</t>
+          <t>(0.55, 107.13)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(0.34, 65.58)</t>
+          <t>(0.44, 84.4)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>(0.28, 53.8)</t>
+          <t>(0.36, 69.25)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>(0.23, 45.43)</t>
+          <t>(0.3, 58.47)</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>(0.2, 39.19)</t>
+          <t>(0.26, 50.44)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>(0.18, 34.38)</t>
+          <t>(0.23, 44.25)</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>(0.16, 30.56)</t>
+          <t>(0.2, 39.33)</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -7902,52 +7902,52 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>(5.79, 91.02)</t>
+          <t>(7.45, 117.13)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>(3.12, 49.14)</t>
+          <t>(4.02, 63.24)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>(2.09, 32.84)</t>
+          <t>(2.69, 42.26)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>(1.55, 24.33)</t>
+          <t>(1.99, 31.32)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(1.22, 19.17)</t>
+          <t>(1.57, 24.68)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>(1.0, 15.73)</t>
+          <t>(1.29, 20.24)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>(0.84, 13.28)</t>
+          <t>(1.09, 17.09)</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>(0.73, 11.46)</t>
+          <t>(0.94, 14.75)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>(0.64, 10.05)</t>
+          <t>(0.82, 12.94)</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>(0.57, 8.93)</t>
+          <t>(0.73, 11.5)</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -7970,52 +7970,52 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>(85.23, 91.02)</t>
+          <t>(109.67, 117.13)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>(46.01, 49.14)</t>
+          <t>(59.21, 63.24)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>(30.75, 32.84)</t>
+          <t>(39.57, 42.26)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>(22.79, 24.33)</t>
+          <t>(29.33, 31.32)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(17.95, 19.17)</t>
+          <t>(23.11, 24.68)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>(14.73, 15.73)</t>
+          <t>(18.96, 20.24)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>(12.44, 13.28)</t>
+          <t>(16.01, 17.09)</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>(10.73, 11.46)</t>
+          <t>(13.81, 14.75)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>(9.41, 10.05)</t>
+          <t>(12.11, 12.94)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>(8.37, 8.93)</t>
+          <t>(10.77, 11.5)</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -8038,52 +8038,52 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>(0.0, 15.8)</t>
+          <t>(0.0, 20.34)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>(0.0, 8.53)</t>
+          <t>(0.0, 10.98)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>(0.0, 5.7)</t>
+          <t>(0.0, 7.34)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>(0.0, 4.23)</t>
+          <t>(0.0, 5.44)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(0.0, 3.33)</t>
+          <t>(0.0, 4.28)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>(0.0, 2.73)</t>
+          <t>(0.0, 3.52)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>(0.0, 2.31)</t>
+          <t>(0.0, 2.97)</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>(0.0, 1.99)</t>
+          <t>(0.0, 2.56)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>(0.0, 1.75)</t>
+          <t>(0.0, 2.25)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>(0.0, 1.55)</t>
+          <t>(0.0, 2.0)</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -8106,52 +8106,52 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>(0.0, 15.8)</t>
+          <t>(0.0, 20.34)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>(0.0, 8.53)</t>
+          <t>(0.0, 10.98)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>(0.0, 5.7)</t>
+          <t>(0.0, 7.34)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>(0.0, 4.23)</t>
+          <t>(0.0, 5.44)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(0.0, 3.33)</t>
+          <t>(0.0, 4.28)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>(0.0, 2.73)</t>
+          <t>(0.0, 3.52)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>(0.0, 2.31)</t>
+          <t>(0.0, 2.97)</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>(0.0, 1.99)</t>
+          <t>(0.0, 2.56)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>(0.0, 1.75)</t>
+          <t>(0.0, 2.25)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>(0.0, 1.55)</t>
+          <t>(0.0, 2.0)</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -8174,52 +8174,52 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>(103.21, 220.89)</t>
+          <t>(132.82, 284.27)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>(55.72, 119.25)</t>
+          <t>(71.71, 153.47)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>(37.24, 79.69)</t>
+          <t>(47.92, 102.56)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>(27.59, 59.06)</t>
+          <t>(35.52, 76.01)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(21.74, 46.53)</t>
+          <t>(27.98, 59.89)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>(17.84, 38.17)</t>
+          <t>(22.96, 49.13)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>(15.06, 32.23)</t>
+          <t>(19.38, 41.49)</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>(12.99, 27.81)</t>
+          <t>(16.72, 35.79)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>(11.4, 24.39)</t>
+          <t>(14.67, 31.39)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>(10.13, 21.68)</t>
+          <t>(13.04, 27.91)</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -8242,52 +8242,52 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>(117.68, 220.89)</t>
+          <t>(151.44, 284.27)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>(63.53, 119.25)</t>
+          <t>(81.76, 153.47)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>(42.46, 79.69)</t>
+          <t>(54.64, 102.56)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>(31.46, 59.06)</t>
+          <t>(40.49, 76.01)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(24.79, 46.53)</t>
+          <t>(31.9, 59.89)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>(20.34, 38.17)</t>
+          <t>(26.18, 49.13)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>(17.17, 32.23)</t>
+          <t>(22.1, 41.49)</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>(14.81, 27.81)</t>
+          <t>(19.07, 35.79)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>(12.99, 24.39)</t>
+          <t>(16.73, 31.39)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>(11.55, 21.68)</t>
+          <t>(14.87, 27.91)</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -8310,52 +8310,52 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>(94.42, 142.6)</t>
+          <t>(121.51, 183.51)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>(50.97, 76.98)</t>
+          <t>(65.6, 99.07)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>(34.06, 51.44)</t>
+          <t>(43.84, 66.21)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>(25.24, 38.12)</t>
+          <t>(32.49, 49.07)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(19.89, 30.04)</t>
+          <t>(25.6, 38.66)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>(16.32, 24.64)</t>
+          <t>(21.0, 31.72)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>(13.78, 20.81)</t>
+          <t>(17.73, 26.78)</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>(11.89, 17.95)</t>
+          <t>(15.3, 23.1)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>(10.43, 15.75)</t>
+          <t>(13.42, 20.27)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>(9.27, 14.0)</t>
+          <t>(11.93, 18.02)</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -8378,52 +8378,52 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>(48.18, 142.6)</t>
+          <t>(62.0, 183.51)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>(26.01, 76.98)</t>
+          <t>(33.47, 99.07)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>(17.38, 51.44)</t>
+          <t>(22.37, 66.21)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>(12.88, 38.12)</t>
+          <t>(16.58, 49.07)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(10.15, 30.04)</t>
+          <t>(13.06, 38.66)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>(8.33, 24.64)</t>
+          <t>(10.72, 31.72)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>(7.03, 20.81)</t>
+          <t>(9.05, 26.78)</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>(6.06, 17.95)</t>
+          <t>(7.81, 23.1)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>(5.32, 15.75)</t>
+          <t>(6.85, 20.27)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>(4.73, 14.0)</t>
+          <t>(6.09, 18.02)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -8446,52 +8446,52 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>(19.59, 356.89)</t>
+          <t>(25.21, 459.28)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>(10.58, 192.67)</t>
+          <t>(13.61, 247.96)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>(7.07, 128.75)</t>
+          <t>(9.1, 165.71)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>(5.24, 95.42)</t>
+          <t>(6.74, 122.81)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(4.13, 75.18)</t>
+          <t>(5.31, 96.76)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>(3.39, 61.68)</t>
+          <t>(4.36, 79.38)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>(2.86, 52.08)</t>
+          <t>(3.68, 67.03)</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>(2.47, 44.93)</t>
+          <t>(3.17, 57.82)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>(2.16, 39.41)</t>
+          <t>(2.78, 50.72)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>(1.92, 35.03)</t>
+          <t>(2.48, 45.09)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -8514,52 +8514,52 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>(336.65, 356.89)</t>
+          <t>(433.23, 459.28)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>(181.74, 192.67)</t>
+          <t>(233.9, 247.96)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>(121.45, 128.75)</t>
+          <t>(156.31, 165.71)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>(90.01, 95.42)</t>
+          <t>(115.84, 122.81)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(70.91, 75.18)</t>
+          <t>(91.27, 96.76)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>(58.18, 61.68)</t>
+          <t>(74.88, 79.38)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>(49.12, 52.08)</t>
+          <t>(63.23, 67.03)</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>(42.38, 44.93)</t>
+          <t>(54.54, 57.82)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>(37.17, 39.41)</t>
+          <t>(47.85, 50.72)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>(33.04, 35.03)</t>
+          <t>(42.53, 45.09)</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -8582,52 +8582,52 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>(189.72, 216.09)</t>
+          <t>(244.15, 278.08)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>(102.42, 116.66)</t>
+          <t>(131.82, 150.14)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>(68.44, 77.96)</t>
+          <t>(88.09, 100.33)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>(50.72, 57.77)</t>
+          <t>(65.28, 74.36)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(39.96, 45.52)</t>
+          <t>(51.44, 58.58)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>(32.79, 37.34)</t>
+          <t>(42.2, 48.06)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>(27.68, 31.53)</t>
+          <t>(35.63, 40.58)</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>(23.88, 27.2)</t>
+          <t>(30.74, 35.01)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>(20.95, 23.86)</t>
+          <t>(26.96, 30.71)</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>(18.62, 21.21)</t>
+          <t>(23.97, 27.3)</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -8650,52 +8650,52 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>(26.05, 216.09)</t>
+          <t>(33.52, 278.08)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>(14.06, 116.66)</t>
+          <t>(18.1, 150.14)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>(9.4, 77.96)</t>
+          <t>(12.09, 100.33)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>(6.96, 57.77)</t>
+          <t>(8.96, 74.36)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(5.49, 45.52)</t>
+          <t>(7.06, 58.58)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>(4.5, 37.34)</t>
+          <t>(5.79, 48.06)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>(3.8, 31.53)</t>
+          <t>(4.89, 40.58)</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>(3.28, 27.2)</t>
+          <t>(4.22, 35.01)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>(2.88, 23.86)</t>
+          <t>(3.7, 30.71)</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>(2.56, 21.21)</t>
+          <t>(3.29, 27.3)</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -8718,52 +8718,52 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>(0.0, 86.91)</t>
+          <t>(0.0, 111.84)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>(0.0, 46.92)</t>
+          <t>(0.0, 60.38)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>(0.0, 31.35)</t>
+          <t>(0.0, 40.35)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>(0.0, 23.24)</t>
+          <t>(0.0, 29.9)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(0.0, 18.31)</t>
+          <t>(0.0, 23.56)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>(0.0, 15.02)</t>
+          <t>(0.0, 19.33)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>(0.0, 12.68)</t>
+          <t>(0.0, 16.32)</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>(0.0, 10.94)</t>
+          <t>(0.0, 14.08)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>(0.0, 9.6)</t>
+          <t>(0.0, 12.35)</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>(0.0, 8.53)</t>
+          <t>(0.0, 10.98)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -8786,52 +8786,52 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>(0.0, 86.91)</t>
+          <t>(0.0, 111.84)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>(0.0, 46.92)</t>
+          <t>(0.0, 60.38)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>(0.0, 31.35)</t>
+          <t>(0.0, 40.35)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>(0.0, 23.24)</t>
+          <t>(0.0, 29.9)</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(0.0, 18.31)</t>
+          <t>(0.0, 23.56)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>(0.0, 15.02)</t>
+          <t>(0.0, 19.33)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>(0.0, 12.68)</t>
+          <t>(0.0, 16.32)</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>(0.0, 10.94)</t>
+          <t>(0.0, 14.08)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>(0.0, 9.6)</t>
+          <t>(0.0, 12.35)</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>(0.0, 8.53)</t>
+          <t>(0.0, 10.98)</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -8854,52 +8854,52 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>(35.37, 83.93)</t>
+          <t>(45.52, 108.01)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>(19.1, 45.31)</t>
+          <t>(24.58, 58.32)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>(12.76, 30.28)</t>
+          <t>(16.42, 38.97)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>(9.46, 22.44)</t>
+          <t>(12.17, 28.88)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(7.45, 17.68)</t>
+          <t>(9.59, 22.76)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>(6.11, 14.51)</t>
+          <t>(7.87, 18.67)</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>(5.16, 12.25)</t>
+          <t>(6.64, 15.76)</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>(4.45, 10.57)</t>
+          <t>(5.73, 13.6)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>(3.91, 9.27)</t>
+          <t>(5.03, 11.93)</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>(3.47, 8.24)</t>
+          <t>(4.47, 10.6)</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -8922,52 +8922,52 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>(48.56, 83.93)</t>
+          <t>(62.49, 108.01)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>(26.21, 45.31)</t>
+          <t>(33.74, 58.32)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>(17.52, 30.28)</t>
+          <t>(22.54, 38.97)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>(12.98, 22.44)</t>
+          <t>(16.71, 28.88)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(10.23, 17.68)</t>
+          <t>(13.16, 22.76)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>(8.39, 14.51)</t>
+          <t>(10.8, 18.67)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>(7.09, 12.25)</t>
+          <t>(9.12, 15.76)</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>(6.11, 10.57)</t>
+          <t>(7.87, 13.6)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>(5.36, 9.27)</t>
+          <t>(6.9, 11.93)</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>(4.77, 8.24)</t>
+          <t>(6.13, 10.6)</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -8990,52 +8990,52 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>(0.0, 16.32)</t>
+          <t>(0.0, 21.01)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>(0.0, 8.81)</t>
+          <t>(0.0, 11.34)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>(0.0, 5.89)</t>
+          <t>(0.0, 7.58)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>(0.0, 4.36)</t>
+          <t>(0.0, 5.62)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(0.0, 3.44)</t>
+          <t>(0.0, 4.43)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>(0.0, 2.82)</t>
+          <t>(0.0, 3.63)</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>(0.0, 2.38)</t>
+          <t>(0.0, 3.07)</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>(0.0, 2.05)</t>
+          <t>(0.0, 2.64)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>(0.0, 1.8)</t>
+          <t>(0.0, 2.32)</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>(0.0, 1.6)</t>
+          <t>(0.0, 2.06)</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -9058,52 +9058,52 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>(0.0, 16.32)</t>
+          <t>(0.0, 21.01)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>(0.0, 8.81)</t>
+          <t>(0.0, 11.34)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>(0.0, 5.89)</t>
+          <t>(0.0, 7.58)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>(0.0, 4.36)</t>
+          <t>(0.0, 5.62)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(0.0, 3.44)</t>
+          <t>(0.0, 4.43)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>(0.0, 2.82)</t>
+          <t>(0.0, 3.63)</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>(0.0, 2.38)</t>
+          <t>(0.0, 3.07)</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>(0.0, 2.05)</t>
+          <t>(0.0, 2.64)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>(0.0, 1.8)</t>
+          <t>(0.0, 2.32)</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>(0.0, 1.6)</t>
+          <t>(0.0, 2.06)</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -9126,52 +9126,52 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>(24.47, 115.25)</t>
+          <t>(31.49, 148.32)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>(13.21, 62.22)</t>
+          <t>(17.0, 80.08)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>(8.83, 41.58)</t>
+          <t>(11.36, 53.51)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>(6.54, 30.81)</t>
+          <t>(8.42, 39.66)</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(5.15, 24.28)</t>
+          <t>(6.63, 31.25)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>(4.23, 19.92)</t>
+          <t>(5.44, 25.64)</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>(3.57, 16.82)</t>
+          <t>(4.6, 21.65)</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>(3.08, 14.51)</t>
+          <t>(3.96, 18.67)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>(2.7, 12.73)</t>
+          <t>(3.48, 16.38)</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>(2.4, 11.31)</t>
+          <t>(3.09, 14.56)</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -9194,52 +9194,52 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>(90.79, 115.25)</t>
+          <t>(116.83, 148.32)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>(49.01, 62.22)</t>
+          <t>(63.08, 80.08)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>(32.75, 41.58)</t>
+          <t>(42.15, 53.51)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>(24.27, 30.81)</t>
+          <t>(31.24, 39.66)</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(19.12, 24.28)</t>
+          <t>(24.61, 31.25)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>(15.69, 19.92)</t>
+          <t>(20.19, 25.64)</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>(13.25, 16.82)</t>
+          <t>(17.05, 21.65)</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>(11.43, 14.51)</t>
+          <t>(14.71, 18.67)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>(10.02, 12.73)</t>
+          <t>(12.9, 16.38)</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>(8.91, 11.31)</t>
+          <t>(11.47, 14.56)</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -9262,52 +9262,52 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>(119.48, 190.78)</t>
+          <t>(153.76, 245.51)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>(64.5, 103.0)</t>
+          <t>(83.01, 132.55)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>(43.1, 68.83)</t>
+          <t>(55.48, 88.58)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>(31.94, 51.01)</t>
+          <t>(41.11, 65.65)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(25.17, 40.19)</t>
+          <t>(32.39, 51.72)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>(20.65, 32.97)</t>
+          <t>(26.58, 42.43)</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>(17.43, 27.84)</t>
+          <t>(22.44, 35.83)</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>(15.04, 24.02)</t>
+          <t>(19.36, 30.91)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>(13.19, 21.07)</t>
+          <t>(16.98, 27.11)</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>(11.73, 18.73)</t>
+          <t>(15.09, 24.1)</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -9330,52 +9330,52 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>(70.34, 190.78)</t>
+          <t>(90.52, 245.51)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>(37.97, 103.0)</t>
+          <t>(48.87, 132.55)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>(25.38, 68.83)</t>
+          <t>(32.66, 88.58)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>(18.81, 51.01)</t>
+          <t>(24.2, 65.65)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(14.82, 40.19)</t>
+          <t>(19.07, 51.72)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>(12.16, 32.97)</t>
+          <t>(15.65, 42.43)</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>(10.26, 27.84)</t>
+          <t>(13.21, 35.83)</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>(8.85, 24.02)</t>
+          <t>(11.4, 30.91)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>(7.77, 21.07)</t>
+          <t>(10.0, 27.11)</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>(6.9, 18.73)</t>
+          <t>(8.89, 24.1)</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -9398,52 +9398,52 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>(82.97, 169.48)</t>
+          <t>(106.77, 218.1)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>(44.79, 91.5)</t>
+          <t>(57.65, 117.75)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>(29.93, 61.14)</t>
+          <t>(38.52, 78.69)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>(22.18, 45.31)</t>
+          <t>(28.55, 58.32)</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(17.48, 35.7)</t>
+          <t>(22.49, 45.95)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>(14.34, 29.29)</t>
+          <t>(18.45, 37.7)</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>(12.11, 24.73)</t>
+          <t>(15.58, 31.83)</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>(10.44, 21.33)</t>
+          <t>(13.44, 27.46)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>(9.16, 18.71)</t>
+          <t>(11.79, 24.09)</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>(8.14, 16.64)</t>
+          <t>(10.48, 21.41)</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -9466,52 +9466,52 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>(86.51, 169.48)</t>
+          <t>(111.33, 218.1)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>(46.7, 91.5)</t>
+          <t>(60.11, 117.75)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>(31.21, 61.14)</t>
+          <t>(40.17, 78.69)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>(23.13, 45.31)</t>
+          <t>(29.77, 58.32)</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(18.22, 35.7)</t>
+          <t>(23.45, 45.95)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>(14.95, 29.29)</t>
+          <t>(19.24, 37.7)</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>(12.62, 24.73)</t>
+          <t>(16.25, 31.83)</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>(10.89, 21.33)</t>
+          <t>(14.02, 27.46)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>(9.55, 18.71)</t>
+          <t>(12.3, 24.09)</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>(8.49, 16.64)</t>
+          <t>(10.93, 21.41)</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -9534,52 +9534,52 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>(133.3, 318.63)</t>
+          <t>(171.54, 410.04)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>(71.96, 172.01)</t>
+          <t>(92.61, 221.38)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>(48.09, 114.95)</t>
+          <t>(61.89, 147.94)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>(35.64, 85.19)</t>
+          <t>(45.87, 109.64)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(28.08, 67.12)</t>
+          <t>(36.14, 86.38)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>(23.04, 55.06)</t>
+          <t>(29.65, 70.87)</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>(19.45, 46.49)</t>
+          <t>(25.03, 59.84)</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>(16.78, 40.11)</t>
+          <t>(21.6, 51.62)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>(14.72, 35.18)</t>
+          <t>(18.94, 45.28)</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>(13.08, 31.28)</t>
+          <t>(16.84, 40.26)</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -9602,52 +9602,52 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>(185.33, 318.63)</t>
+          <t>(238.5, 410.04)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>(100.05, 172.01)</t>
+          <t>(128.76, 221.38)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>(66.86, 114.95)</t>
+          <t>(86.05, 147.94)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>(49.55, 85.19)</t>
+          <t>(63.77, 109.64)</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(39.04, 67.12)</t>
+          <t>(50.24, 86.38)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>(32.03, 55.06)</t>
+          <t>(41.22, 70.87)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>(27.04, 46.49)</t>
+          <t>(34.81, 59.84)</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>(23.33, 40.11)</t>
+          <t>(30.03, 51.62)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>(20.46, 35.18)</t>
+          <t>(26.34, 45.28)</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>(18.19, 31.28)</t>
+          <t>(23.41, 40.26)</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -9670,52 +9670,52 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>(50.17, 50.17)</t>
+          <t>(64.56, 64.56)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>(27.08, 27.08)</t>
+          <t>(34.86, 34.86)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>(18.1, 18.1)</t>
+          <t>(23.29, 23.29)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>(13.41, 13.41)</t>
+          <t>(17.26, 17.26)</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(10.57, 10.57)</t>
+          <t>(13.6, 13.6)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>(8.67, 8.67)</t>
+          <t>(11.16, 11.16)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>(7.32, 7.32)</t>
+          <t>(9.42, 9.42)</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>(6.32, 6.32)</t>
+          <t>(8.13, 8.13)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>(5.54, 5.54)</t>
+          <t>(7.13, 7.13)</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>(4.92, 4.92)</t>
+          <t>(6.34, 6.34)</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -9738,52 +9738,52 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>(0.0, 50.17)</t>
+          <t>(0.0, 64.56)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>(0.0, 27.08)</t>
+          <t>(0.0, 34.86)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>(0.0, 18.1)</t>
+          <t>(0.0, 23.29)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>(0.0, 13.41)</t>
+          <t>(0.0, 17.26)</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(0.0, 10.57)</t>
+          <t>(0.0, 13.6)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>(0.0, 8.67)</t>
+          <t>(0.0, 11.16)</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>(0.0, 7.32)</t>
+          <t>(0.0, 9.42)</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>(0.0, 6.32)</t>
+          <t>(0.0, 8.13)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>(0.0, 5.54)</t>
+          <t>(0.0, 7.13)</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>(0.0, 4.92)</t>
+          <t>(0.0, 6.34)</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -9806,52 +9806,52 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>(28.26, 156.1)</t>
+          <t>(36.37, 200.89)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>(15.26, 84.27)</t>
+          <t>(19.64, 108.46)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>(10.2, 56.32)</t>
+          <t>(13.12, 72.48)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>(7.56, 41.74)</t>
+          <t>(9.73, 53.72)</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(5.95, 32.88)</t>
+          <t>(7.66, 42.32)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>(4.88, 26.98)</t>
+          <t>(6.29, 34.72)</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>(4.12, 22.78)</t>
+          <t>(5.31, 29.32)</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>(3.56, 19.65)</t>
+          <t>(4.58, 25.29)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>(3.12, 17.24)</t>
+          <t>(4.02, 22.19)</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>(2.77, 15.32)</t>
+          <t>(3.57, 19.72)</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -9874,52 +9874,52 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>(127.83, 156.1)</t>
+          <t>(164.51, 200.89)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>(69.01, 84.27)</t>
+          <t>(88.82, 108.46)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>(46.12, 56.32)</t>
+          <t>(59.35, 72.48)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>(34.18, 41.74)</t>
+          <t>(43.99, 53.72)</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(26.93, 32.88)</t>
+          <t>(34.66, 42.32)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>(22.09, 26.98)</t>
+          <t>(28.43, 34.72)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>(18.65, 22.78)</t>
+          <t>(24.01, 29.32)</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>(16.09, 19.65)</t>
+          <t>(20.71, 25.29)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>(14.12, 17.24)</t>
+          <t>(18.17, 22.19)</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>(12.55, 15.32)</t>
+          <t>(16.15, 19.72)</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -9942,52 +9942,52 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>(55.02, 146.73)</t>
+          <t>(70.81, 188.82)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>(29.7, 79.21)</t>
+          <t>(38.23, 101.94)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>(19.85, 52.93)</t>
+          <t>(25.55, 68.13)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>(14.71, 39.23)</t>
+          <t>(18.93, 50.49)</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(11.59, 30.91)</t>
+          <t>(14.92, 39.78)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>(9.51, 25.36)</t>
+          <t>(12.24, 32.64)</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>(8.03, 21.41)</t>
+          <t>(10.33, 27.56)</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>(6.93, 18.47)</t>
+          <t>(8.91, 23.77)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>(6.08, 16.2)</t>
+          <t>(7.82, 20.85)</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>(5.4, 14.4)</t>
+          <t>(6.95, 18.54)</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -10010,52 +10010,52 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>(91.7, 146.73)</t>
+          <t>(118.01, 188.82)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>(49.51, 79.21)</t>
+          <t>(63.71, 101.94)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>(33.08, 52.93)</t>
+          <t>(42.58, 68.13)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>(24.52, 39.23)</t>
+          <t>(31.56, 50.49)</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(19.32, 30.91)</t>
+          <t>(24.86, 39.78)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>(15.85, 25.36)</t>
+          <t>(20.4, 32.64)</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>(13.38, 21.41)</t>
+          <t>(17.22, 27.56)</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>(11.54, 18.47)</t>
+          <t>(14.86, 23.77)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>(10.13, 16.2)</t>
+          <t>(13.03, 20.85)</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>(9.0, 14.4)</t>
+          <t>(11.59, 18.54)</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -10078,52 +10078,52 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>(195.01, 221.67)</t>
+          <t>(250.95, 285.27)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>(105.28, 119.67)</t>
+          <t>(135.49, 154.01)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>(70.35, 79.97)</t>
+          <t>(90.54, 102.92)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>(52.14, 59.27)</t>
+          <t>(67.1, 76.28)</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(41.08, 46.69)</t>
+          <t>(52.87, 60.1)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>(33.7, 38.31)</t>
+          <t>(43.37, 49.31)</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>(28.45, 32.35)</t>
+          <t>(36.62, 41.63)</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>(24.55, 27.9)</t>
+          <t>(31.6, 35.92)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>(21.53, 24.48)</t>
+          <t>(27.72, 31.5)</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>(19.14, 21.76)</t>
+          <t>(24.64, 28.01)</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -10146,52 +10146,52 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>(26.66, 221.67)</t>
+          <t>(34.31, 285.27)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>(14.39, 119.67)</t>
+          <t>(18.53, 154.01)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>(9.62, 79.97)</t>
+          <t>(12.38, 102.92)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>(7.13, 59.27)</t>
+          <t>(9.17, 76.28)</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(5.62, 46.69)</t>
+          <t>(7.23, 60.1)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>(4.61, 38.31)</t>
+          <t>(5.93, 49.31)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>(3.89, 32.35)</t>
+          <t>(5.01, 41.63)</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>(3.36, 27.9)</t>
+          <t>(4.32, 35.92)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>(2.94, 24.48)</t>
+          <t>(3.79, 31.5)</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>(2.62, 21.76)</t>
+          <t>(3.37, 28.01)</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -10214,52 +10214,52 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>(227.1, 355.59)</t>
+          <t>(292.26, 457.61)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>(122.6, 191.97)</t>
+          <t>(157.79, 247.06)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>(81.93, 128.29)</t>
+          <t>(105.45, 165.11)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>(60.72, 95.07)</t>
+          <t>(78.15, 122.36)</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(47.84, 74.9)</t>
+          <t>(61.57, 96.4)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>(39.25, 61.45)</t>
+          <t>(50.51, 79.09)</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>(33.14, 51.89)</t>
+          <t>(42.65, 66.78)</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>(28.59, 44.76)</t>
+          <t>(36.8, 57.61)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>(25.08, 39.27)</t>
+          <t>(32.28, 50.54)</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>(22.29, 34.9)</t>
+          <t>(28.69, 44.93)</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -10282,52 +10282,52 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>(128.49, 355.59)</t>
+          <t>(165.35, 457.61)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>(69.37, 191.97)</t>
+          <t>(89.27, 247.06)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>(46.35, 128.29)</t>
+          <t>(59.66, 165.11)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>(34.35, 95.07)</t>
+          <t>(44.21, 122.36)</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(27.07, 74.9)</t>
+          <t>(34.83, 96.4)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>(22.2, 61.45)</t>
+          <t>(28.58, 79.09)</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>(18.75, 51.89)</t>
+          <t>(24.13, 66.78)</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>(16.17, 44.76)</t>
+          <t>(20.82, 57.61)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>(14.19, 39.27)</t>
+          <t>(18.26, 50.54)</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>(12.61, 34.9)</t>
+          <t>(16.23, 44.93)</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -10350,52 +10350,52 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>(49.5, 209.24)</t>
+          <t>(63.7, 269.27)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>(26.72, 112.96)</t>
+          <t>(34.39, 145.38)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>(17.86, 75.49)</t>
+          <t>(22.98, 97.15)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>(13.23, 55.94)</t>
+          <t>(17.03, 72.0)</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(10.43, 44.08)</t>
+          <t>(13.42, 56.73)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>(8.55, 36.16)</t>
+          <t>(11.01, 46.54)</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>(7.22, 30.53)</t>
+          <t>(9.3, 39.3)</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>(6.23, 26.34)</t>
+          <t>(8.02, 33.9)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>(5.47, 23.11)</t>
+          <t>(7.04, 29.74)</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>(4.86, 20.54)</t>
+          <t>(6.25, 26.44)</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -10418,52 +10418,52 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>(159.74, 209.24)</t>
+          <t>(205.57, 269.27)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>(86.24, 112.96)</t>
+          <t>(110.99, 145.38)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>(57.63, 75.49)</t>
+          <t>(74.17, 97.15)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>(42.71, 55.94)</t>
+          <t>(54.97, 72.0)</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(33.65, 44.08)</t>
+          <t>(43.31, 56.73)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>(27.61, 36.16)</t>
+          <t>(35.53, 46.54)</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>(23.31, 30.53)</t>
+          <t>(30.0, 39.3)</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>(20.11, 26.34)</t>
+          <t>(25.88, 33.9)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>(17.64, 23.11)</t>
+          <t>(22.7, 29.74)</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>(15.68, 20.54)</t>
+          <t>(20.18, 26.44)</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -10486,52 +10486,52 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>(167.66, 223.23)</t>
+          <t>(215.76, 287.27)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>(90.51, 120.51)</t>
+          <t>(116.49, 155.1)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>(60.49, 80.53)</t>
+          <t>(77.85, 103.65)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>(44.83, 59.68)</t>
+          <t>(57.69, 76.81)</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(35.32, 47.02)</t>
+          <t>(45.45, 60.52)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>(28.97, 38.58)</t>
+          <t>(37.29, 49.65)</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>(24.46, 32.57)</t>
+          <t>(31.49, 41.92)</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>(21.11, 28.1)</t>
+          <t>(27.16, 36.17)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>(18.51, 24.65)</t>
+          <t>(23.83, 31.73)</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>(16.46, 21.91)</t>
+          <t>(21.18, 28.2)</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -10554,52 +10554,52 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>(55.57, 223.23)</t>
+          <t>(71.51, 287.27)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>(30.0, 120.51)</t>
+          <t>(38.61, 155.1)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>(20.05, 80.53)</t>
+          <t>(25.8, 103.65)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>(14.86, 59.68)</t>
+          <t>(19.12, 76.81)</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(11.71, 47.02)</t>
+          <t>(15.07, 60.52)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>(9.6, 38.58)</t>
+          <t>(12.36, 49.65)</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>(8.11, 32.57)</t>
+          <t>(10.44, 41.92)</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>(7.0, 28.1)</t>
+          <t>(9.0, 36.17)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>(6.14, 24.65)</t>
+          <t>(7.9, 31.73)</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>(5.45, 21.91)</t>
+          <t>(7.02, 28.2)</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -10622,52 +10622,52 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>(74.91, 209.62)</t>
+          <t>(96.4, 269.76)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>(40.44, 113.17)</t>
+          <t>(52.05, 145.64)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>(27.03, 75.62)</t>
+          <t>(34.78, 97.33)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>(20.03, 56.04)</t>
+          <t>(25.78, 72.13)</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(15.78, 44.16)</t>
+          <t>(20.31, 56.83)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>(12.95, 36.23)</t>
+          <t>(16.66, 46.63)</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>(10.93, 30.59)</t>
+          <t>(14.07, 39.37)</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>(9.43, 26.39)</t>
+          <t>(12.14, 33.96)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>(8.27, 23.15)</t>
+          <t>(10.65, 29.79)</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>(7.35, 20.58)</t>
+          <t>(9.46, 26.48)</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -10690,52 +10690,52 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>(134.71, 209.62)</t>
+          <t>(173.36, 269.76)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>(72.73, 113.17)</t>
+          <t>(93.6, 145.64)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>(48.6, 75.62)</t>
+          <t>(62.55, 97.33)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>(36.02, 56.04)</t>
+          <t>(46.35, 72.13)</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(28.38, 44.16)</t>
+          <t>(36.52, 56.83)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>(23.28, 36.23)</t>
+          <t>(29.96, 46.63)</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>(19.66, 30.59)</t>
+          <t>(25.3, 39.37)</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>(16.96, 26.39)</t>
+          <t>(21.83, 33.96)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>(14.88, 23.15)</t>
+          <t>(19.15, 29.79)</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>(13.22, 20.58)</t>
+          <t>(17.02, 26.48)</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -10758,52 +10758,52 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>(0.0, 64.6)</t>
+          <t>(0.0, 83.14)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>(0.0, 34.88)</t>
+          <t>(0.0, 44.89)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>(0.0, 23.31)</t>
+          <t>(0.0, 30.0)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>(0.0, 17.27)</t>
+          <t>(0.0, 22.23)</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(0.0, 13.61)</t>
+          <t>(0.0, 17.51)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>(0.0, 11.16)</t>
+          <t>(0.0, 14.37)</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>(0.0, 9.43)</t>
+          <t>(0.0, 12.13)</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>(0.0, 8.13)</t>
+          <t>(0.0, 10.47)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>(0.0, 7.13)</t>
+          <t>(0.0, 9.18)</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>(0.0, 6.34)</t>
+          <t>(0.0, 8.16)</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -10826,52 +10826,52 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>(64.6, 64.6)</t>
+          <t>(83.14, 83.14)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>(34.88, 34.88)</t>
+          <t>(44.89, 44.89)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>(23.31, 23.31)</t>
+          <t>(30.0, 30.0)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>(17.27, 17.27)</t>
+          <t>(22.23, 22.23)</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(13.61, 13.61)</t>
+          <t>(17.51, 17.51)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>(11.16, 11.16)</t>
+          <t>(14.37, 14.37)</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>(9.43, 9.43)</t>
+          <t>(12.13, 12.13)</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>(8.13, 8.13)</t>
+          <t>(10.47, 10.47)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>(7.13, 7.13)</t>
+          <t>(9.18, 9.18)</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>(6.34, 6.34)</t>
+          <t>(8.16, 8.16)</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -10894,52 +10894,52 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>(95.42, 237.73)</t>
+          <t>(122.79, 305.93)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>(51.51, 128.34)</t>
+          <t>(66.29, 165.17)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>(34.42, 85.77)</t>
+          <t>(44.3, 110.38)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>(25.51, 63.56)</t>
+          <t>(32.83, 81.8)</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(20.1, 50.08)</t>
+          <t>(25.87, 64.45)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>(16.49, 41.08)</t>
+          <t>(21.22, 52.88)</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>(13.92, 34.69)</t>
+          <t>(17.92, 44.65)</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>(12.01, 29.93)</t>
+          <t>(15.46, 38.52)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>(10.54, 26.25)</t>
+          <t>(13.56, 33.79)</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>(9.37, 23.34)</t>
+          <t>(12.05, 30.03)</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -10962,52 +10962,52 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>(142.32, 237.73)</t>
+          <t>(183.15, 305.93)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>(76.83, 128.34)</t>
+          <t>(98.88, 165.17)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>(51.34, 85.77)</t>
+          <t>(66.08, 110.38)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>(38.05, 63.56)</t>
+          <t>(48.97, 81.8)</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(29.98, 50.08)</t>
+          <t>(38.58, 64.45)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>(24.6, 41.08)</t>
+          <t>(31.66, 52.88)</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>(20.77, 34.69)</t>
+          <t>(26.73, 44.65)</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>(17.92, 29.93)</t>
+          <t>(23.06, 38.52)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>(15.72, 26.25)</t>
+          <t>(20.23, 33.79)</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>(13.97, 23.34)</t>
+          <t>(17.98, 30.03)</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -11030,52 +11030,52 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>(58.18, 224.04)</t>
+          <t>(74.87, 288.32)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>(31.41, 120.95)</t>
+          <t>(40.42, 155.66)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>(20.99, 80.83)</t>
+          <t>(27.01, 104.02)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>(15.56, 59.9)</t>
+          <t>(20.02, 77.09)</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(12.26, 47.19)</t>
+          <t>(15.77, 60.74)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>(10.05, 38.72)</t>
+          <t>(12.94, 49.83)</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>(8.49, 32.69)</t>
+          <t>(10.93, 42.08)</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>(7.32, 28.2)</t>
+          <t>(9.43, 36.3)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>(6.42, 24.74)</t>
+          <t>(8.27, 31.84)</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>(5.71, 21.99)</t>
+          <t>(7.35, 28.3)</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -11098,52 +11098,52 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>(165.86, 224.04)</t>
+          <t>(213.44, 288.32)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>(89.54, 120.95)</t>
+          <t>(115.24, 155.66)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>(59.84, 80.83)</t>
+          <t>(77.01, 104.02)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>(44.34, 59.9)</t>
+          <t>(57.07, 77.09)</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(34.94, 47.19)</t>
+          <t>(44.97, 60.74)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>(28.66, 38.72)</t>
+          <t>(36.89, 49.83)</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>(24.2, 32.69)</t>
+          <t>(31.15, 42.08)</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>(20.88, 28.2)</t>
+          <t>(26.87, 36.3)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>(18.31, 24.74)</t>
+          <t>(23.57, 31.84)</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>(16.28, 21.99)</t>
+          <t>(20.95, 28.3)</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -11166,52 +11166,52 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>(0.0, 103.9)</t>
+          <t>(0.0, 133.71)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>(0.0, 56.09)</t>
+          <t>(0.0, 72.19)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>(0.0, 37.48)</t>
+          <t>(0.0, 48.24)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>(0.0, 27.78)</t>
+          <t>(0.0, 35.75)</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(0.0, 21.89)</t>
+          <t>(0.0, 28.17)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>(0.0, 17.96)</t>
+          <t>(0.0, 23.11)</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>(0.0, 15.16)</t>
+          <t>(0.0, 19.51)</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>(0.0, 13.08)</t>
+          <t>(0.0, 16.83)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>(0.0, 11.47)</t>
+          <t>(0.0, 14.77)</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>(0.0, 10.2)</t>
+          <t>(0.0, 13.13)</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -11234,52 +11234,52 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>(0.0, 103.9)</t>
+          <t>(0.0, 133.71)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>(0.0, 56.09)</t>
+          <t>(0.0, 72.19)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>(0.0, 37.48)</t>
+          <t>(0.0, 48.24)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>(0.0, 27.78)</t>
+          <t>(0.0, 35.75)</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(0.0, 21.89)</t>
+          <t>(0.0, 28.17)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>(0.0, 17.96)</t>
+          <t>(0.0, 23.11)</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>(0.0, 15.16)</t>
+          <t>(0.0, 19.51)</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>(0.0, 13.08)</t>
+          <t>(0.0, 16.83)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>(0.0, 11.47)</t>
+          <t>(0.0, 14.77)</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>(0.0, 10.2)</t>
+          <t>(0.0, 13.13)</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -11302,52 +11302,52 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>(20.24, 361.32)</t>
+          <t>(26.04, 464.97)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>(10.92, 195.06)</t>
+          <t>(14.06, 251.04)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>(7.3, 130.35)</t>
+          <t>(9.4, 167.76)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>(5.41, 96.6)</t>
+          <t>(6.96, 124.33)</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(4.26, 76.11)</t>
+          <t>(5.49, 97.96)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>(3.5, 62.44)</t>
+          <t>(4.5, 80.37)</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>(2.95, 52.72)</t>
+          <t>(3.8, 67.86)</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>(2.55, 45.48)</t>
+          <t>(3.28, 58.54)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>(2.23, 39.9)</t>
+          <t>(2.88, 51.35)</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>(1.99, 35.47)</t>
+          <t>(2.56, 45.65)</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -11370,52 +11370,52 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>(340.76, 361.32)</t>
+          <t>(438.52, 464.97)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>(183.96, 195.06)</t>
+          <t>(236.75, 251.04)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>(122.93, 130.35)</t>
+          <t>(158.22, 167.76)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>(91.1, 96.6)</t>
+          <t>(117.26, 124.33)</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(71.78, 76.11)</t>
+          <t>(92.38, 97.96)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>(58.89, 62.44)</t>
+          <t>(75.79, 80.37)</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>(49.72, 52.72)</t>
+          <t>(64.0, 67.86)</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>(42.9, 45.48)</t>
+          <t>(55.21, 58.54)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>(37.63, 39.9)</t>
+          <t>(48.43, 51.35)</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>(33.45, 35.47)</t>
+          <t>(43.05, 45.65)</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -11438,52 +11438,52 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>(106.3, 193.98)</t>
+          <t>(136.8, 249.63)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>(57.39, 104.72)</t>
+          <t>(73.86, 134.77)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>(38.35, 69.98)</t>
+          <t>(49.36, 90.07)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>(28.42, 51.86)</t>
+          <t>(36.58, 66.75)</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(22.39, 40.86)</t>
+          <t>(28.82, 52.59)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>(18.37, 33.52)</t>
+          <t>(23.64, 43.15)</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>(15.51, 28.31)</t>
+          <t>(19.96, 36.43)</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>(13.38, 24.42)</t>
+          <t>(17.22, 31.43)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>(11.74, 21.42)</t>
+          <t>(15.11, 27.57)</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>(10.43, 19.04)</t>
+          <t>(13.43, 24.51)</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -11506,52 +11506,52 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>(31.15, 193.98)</t>
+          <t>(40.09, 249.63)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>(16.82, 104.72)</t>
+          <t>(21.64, 134.77)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>(11.24, 69.98)</t>
+          <t>(14.46, 90.07)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>(8.33, 51.86)</t>
+          <t>(10.72, 66.75)</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(6.56, 40.86)</t>
+          <t>(8.45, 52.59)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>(5.38, 33.52)</t>
+          <t>(6.93, 43.15)</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>(4.55, 28.31)</t>
+          <t>(5.85, 36.43)</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>(3.92, 24.42)</t>
+          <t>(5.05, 31.43)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>(3.44, 21.42)</t>
+          <t>(4.43, 27.57)</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>(3.06, 19.04)</t>
+          <t>(3.94, 24.51)</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -11574,52 +11574,52 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>(147.06, 360.6)</t>
+          <t>(189.25, 464.05)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>(79.39, 194.67)</t>
+          <t>(102.18, 250.54)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>(53.05, 130.09)</t>
+          <t>(68.28, 167.43)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>(39.32, 96.41)</t>
+          <t>(50.6, 124.08)</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(30.98, 75.96)</t>
+          <t>(39.87, 97.76)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>(25.41, 62.32)</t>
+          <t>(32.71, 80.21)</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>(21.46, 52.62)</t>
+          <t>(27.62, 67.72)</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>(18.51, 45.39)</t>
+          <t>(23.83, 58.42)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>(16.24, 39.82)</t>
+          <t>(20.9, 51.25)</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>(14.44, 35.4)</t>
+          <t>(18.58, 45.56)</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -11642,52 +11642,52 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>(213.53, 360.6)</t>
+          <t>(274.79, 464.05)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>(115.27, 194.67)</t>
+          <t>(148.36, 250.54)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>(77.03, 130.09)</t>
+          <t>(99.14, 167.43)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>(57.09, 96.41)</t>
+          <t>(73.47, 124.08)</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(44.98, 75.96)</t>
+          <t>(57.89, 97.76)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>(36.9, 62.32)</t>
+          <t>(47.49, 80.21)</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>(31.16, 52.62)</t>
+          <t>(40.1, 67.72)</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>(26.88, 45.39)</t>
+          <t>(34.6, 58.42)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>(23.58, 39.82)</t>
+          <t>(30.35, 51.25)</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>(20.96, 35.4)</t>
+          <t>(26.98, 45.56)</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -11710,52 +11710,52 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>(186.4, 297.59)</t>
+          <t>(239.87, 382.97)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>(100.63, 160.66)</t>
+          <t>(129.5, 206.76)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>(67.24, 107.36)</t>
+          <t>(86.55, 138.17)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>(49.83, 79.56)</t>
+          <t>(64.14, 102.4)</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(39.26, 62.69)</t>
+          <t>(50.53, 80.68)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>(32.21, 51.43)</t>
+          <t>(41.46, 66.19)</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>(27.2, 43.42)</t>
+          <t>(35.01, 55.89)</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>(23.46, 37.46)</t>
+          <t>(30.2, 48.22)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>(20.58, 32.86)</t>
+          <t>(26.49, 42.29)</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>(18.3, 29.21)</t>
+          <t>(23.55, 37.6)</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -11778,52 +11778,52 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>(111.2, 297.59)</t>
+          <t>(143.1, 382.97)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>(60.03, 160.66)</t>
+          <t>(77.26, 206.76)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>(40.12, 107.36)</t>
+          <t>(51.63, 138.17)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>(29.73, 79.56)</t>
+          <t>(38.26, 102.4)</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(23.42, 62.69)</t>
+          <t>(30.15, 80.68)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>(19.22, 51.43)</t>
+          <t>(24.73, 66.19)</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>(16.23, 43.42)</t>
+          <t>(20.88, 55.89)</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>(14.0, 37.46)</t>
+          <t>(18.02, 48.22)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>(12.28, 32.86)</t>
+          <t>(15.8, 42.29)</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>(10.91, 29.21)</t>
+          <t>(14.05, 37.6)</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -11846,52 +11846,52 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>(0.0, 16.52)</t>
+          <t>(0.0, 21.26)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>(0.0, 8.92)</t>
+          <t>(0.0, 11.48)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>(0.0, 5.96)</t>
+          <t>(0.0, 7.67)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>(0.0, 4.42)</t>
+          <t>(0.0, 5.69)</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(0.0, 3.48)</t>
+          <t>(0.0, 4.48)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>(0.0, 2.86)</t>
+          <t>(0.0, 3.68)</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>(0.0, 2.41)</t>
+          <t>(0.0, 3.1)</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>(0.0, 2.08)</t>
+          <t>(0.0, 2.68)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>(0.0, 1.82)</t>
+          <t>(0.0, 2.35)</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>(0.0, 1.62)</t>
+          <t>(0.0, 2.09)</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -11914,52 +11914,52 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>(0.0, 16.52)</t>
+          <t>(0.0, 21.26)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>(0.0, 8.92)</t>
+          <t>(0.0, 11.48)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>(0.0, 5.96)</t>
+          <t>(0.0, 7.67)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>(0.0, 4.42)</t>
+          <t>(0.0, 5.69)</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(0.0, 3.48)</t>
+          <t>(0.0, 4.48)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>(0.0, 2.86)</t>
+          <t>(0.0, 3.68)</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>(0.0, 2.41)</t>
+          <t>(0.0, 3.1)</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>(0.0, 2.08)</t>
+          <t>(0.0, 2.68)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>(0.0, 1.82)</t>
+          <t>(0.0, 2.35)</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>(0.0, 1.62)</t>
+          <t>(0.0, 2.09)</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -11982,52 +11982,52 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>(217.95, 238.52)</t>
+          <t>(280.48, 306.95)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>(117.66, 128.77)</t>
+          <t>(151.43, 165.72)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>(78.63, 86.05)</t>
+          <t>(101.2, 110.75)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>(58.27, 63.77)</t>
+          <t>(75.0, 82.08)</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(45.91, 50.24)</t>
+          <t>(59.09, 64.67)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>(37.67, 41.22)</t>
+          <t>(48.48, 53.05)</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>(31.8, 34.8)</t>
+          <t>(40.93, 44.8)</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>(27.44, 30.03)</t>
+          <t>(35.31, 38.65)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>(24.07, 26.34)</t>
+          <t>(30.98, 33.9)</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>(21.39, 23.41)</t>
+          <t>(27.54, 30.13)</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -12050,52 +12050,52 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>(20.58, 238.52)</t>
+          <t>(26.48, 306.95)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>(11.11, 128.77)</t>
+          <t>(14.3, 165.72)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>(7.42, 86.05)</t>
+          <t>(9.55, 110.75)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>(5.5, 63.77)</t>
+          <t>(7.08, 82.08)</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(4.33, 50.24)</t>
+          <t>(5.58, 64.67)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>(3.56, 41.22)</t>
+          <t>(4.58, 53.05)</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>(3.0, 34.8)</t>
+          <t>(3.86, 44.8)</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>(2.59, 30.03)</t>
+          <t>(3.33, 38.65)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>(2.27, 26.34)</t>
+          <t>(2.92, 33.9)</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>(2.02, 23.41)</t>
+          <t>(2.6, 30.13)</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -12118,52 +12118,52 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>(23.91, 29.08)</t>
+          <t>(30.77, 37.42)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>(12.91, 15.7)</t>
+          <t>(16.61, 20.2)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>(8.63, 10.49)</t>
+          <t>(11.1, 13.5)</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>(6.39, 7.77)</t>
+          <t>(8.23, 10.01)</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(5.04, 6.13)</t>
+          <t>(6.48, 7.88)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>(4.13, 5.03)</t>
+          <t>(5.32, 6.47)</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>(3.49, 4.24)</t>
+          <t>(4.49, 5.46)</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>(3.01, 3.66)</t>
+          <t>(3.87, 4.71)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>(2.64, 3.21)</t>
+          <t>(3.4, 4.13)</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>(2.35, 2.85)</t>
+          <t>(3.02, 3.67)</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -12186,52 +12186,52 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>(5.17, 29.08)</t>
+          <t>(6.65, 37.42)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>(2.79, 15.7)</t>
+          <t>(3.59, 20.2)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>(1.87, 10.49)</t>
+          <t>(2.4, 13.5)</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>(1.38, 7.77)</t>
+          <t>(1.78, 10.01)</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(1.09, 6.13)</t>
+          <t>(1.4, 7.88)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>(0.89, 5.03)</t>
+          <t>(1.15, 6.47)</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>(0.75, 4.24)</t>
+          <t>(0.97, 5.46)</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>(0.65, 3.66)</t>
+          <t>(0.84, 4.71)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>(0.57, 3.21)</t>
+          <t>(0.73, 4.13)</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>(0.51, 2.85)</t>
+          <t>(0.65, 3.67)</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -12254,52 +12254,52 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>(26.36, 169.43)</t>
+          <t>(33.92, 218.04)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>(14.23, 91.47)</t>
+          <t>(18.32, 117.72)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>(9.51, 61.12)</t>
+          <t>(12.24, 78.67)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>(7.05, 45.3)</t>
+          <t>(9.07, 58.3)</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(5.55, 35.69)</t>
+          <t>(7.15, 45.93)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>(4.56, 29.28)</t>
+          <t>(5.86, 37.69)</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>(3.85, 24.72)</t>
+          <t>(4.95, 31.82)</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>(3.32, 21.33)</t>
+          <t>(4.27, 27.45)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>(2.91, 18.71)</t>
+          <t>(3.75, 24.08)</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>(2.59, 16.63)</t>
+          <t>(3.33, 21.41)</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -12322,52 +12322,52 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>(143.07, 169.43)</t>
+          <t>(184.11, 218.04)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>(77.24, 91.47)</t>
+          <t>(99.4, 117.72)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>(51.61, 61.12)</t>
+          <t>(66.43, 78.67)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>(38.25, 45.3)</t>
+          <t>(49.23, 58.3)</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(30.14, 35.69)</t>
+          <t>(38.79, 45.93)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>(24.72, 29.28)</t>
+          <t>(31.82, 37.69)</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>(20.88, 24.72)</t>
+          <t>(26.87, 31.82)</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>(18.01, 21.33)</t>
+          <t>(23.18, 27.45)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>(15.8, 18.71)</t>
+          <t>(20.33, 24.08)</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>(14.04, 16.63)</t>
+          <t>(18.07, 21.41)</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -12390,52 +12390,52 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>(51.45, 106.75)</t>
+          <t>(66.2, 137.38)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>(27.77, 57.63)</t>
+          <t>(35.74, 74.17)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>(18.56, 38.51)</t>
+          <t>(23.89, 49.57)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>(13.75, 28.54)</t>
+          <t>(17.7, 36.73)</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(10.84, 22.49)</t>
+          <t>(13.95, 28.94)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>(8.89, 18.45)</t>
+          <t>(11.44, 23.74)</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>(7.51, 15.58)</t>
+          <t>(9.66, 20.05)</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>(6.48, 13.44)</t>
+          <t>(8.34, 17.3)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>(5.68, 11.79)</t>
+          <t>(7.31, 15.17)</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>(5.05, 10.48)</t>
+          <t>(6.5, 13.49)</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -12458,52 +12458,52 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>(54.66, 106.75)</t>
+          <t>(70.35, 137.38)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>(29.51, 57.63)</t>
+          <t>(37.98, 74.17)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>(19.72, 38.51)</t>
+          <t>(25.38, 49.57)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>(14.61, 28.54)</t>
+          <t>(18.81, 36.73)</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(11.51, 22.49)</t>
+          <t>(14.82, 28.94)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>(9.45, 18.45)</t>
+          <t>(12.16, 23.74)</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>(7.98, 15.58)</t>
+          <t>(10.27, 20.05)</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>(6.88, 13.44)</t>
+          <t>(8.86, 17.3)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>(6.04, 11.79)</t>
+          <t>(7.77, 15.17)</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>(5.37, 10.48)</t>
+          <t>(6.91, 13.49)</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -12526,52 +12526,52 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>(105.73, 121.8)</t>
+          <t>(136.06, 156.74)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>(57.08, 65.75)</t>
+          <t>(73.46, 84.62)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>(38.14, 43.94)</t>
+          <t>(49.09, 56.55)</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>(28.27, 32.56)</t>
+          <t>(36.38, 41.91)</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(22.27, 25.66)</t>
+          <t>(28.66, 33.02)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>(18.27, 21.05)</t>
+          <t>(23.52, 27.09)</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>(15.43, 17.77)</t>
+          <t>(19.86, 22.87)</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>(13.31, 15.33)</t>
+          <t>(17.13, 19.73)</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>(11.68, 13.45)</t>
+          <t>(15.03, 17.31)</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>(10.38, 11.96)</t>
+          <t>(13.36, 15.39)</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -12594,52 +12594,52 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>(16.07, 121.8)</t>
+          <t>(20.68, 156.74)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>(8.67, 65.75)</t>
+          <t>(11.16, 84.62)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>(5.8, 43.94)</t>
+          <t>(7.46, 56.55)</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>(4.3, 32.56)</t>
+          <t>(5.53, 41.91)</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(3.38, 25.66)</t>
+          <t>(4.36, 33.02)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>(2.78, 21.05)</t>
+          <t>(3.57, 27.09)</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>(2.34, 17.77)</t>
+          <t>(3.02, 22.87)</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>(2.02, 15.33)</t>
+          <t>(2.6, 19.73)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>(1.77, 13.45)</t>
+          <t>(2.28, 17.31)</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>(1.58, 11.96)</t>
+          <t>(2.03, 15.39)</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -12662,52 +12662,52 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>(129.41, 228.65)</t>
+          <t>(166.54, 294.24)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>(69.87, 123.44)</t>
+          <t>(89.91, 158.86)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>(46.69, 82.49)</t>
+          <t>(60.09, 106.16)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>(34.6, 61.13)</t>
+          <t>(44.53, 78.68)</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(27.26, 48.16)</t>
+          <t>(35.09, 61.99)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>(22.36, 39.51)</t>
+          <t>(28.78, 50.86)</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>(18.88, 33.36)</t>
+          <t>(24.3, 42.94)</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>(16.29, 28.78)</t>
+          <t>(20.97, 37.05)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>(14.29, 25.25)</t>
+          <t>(18.39, 32.5)</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>(12.7, 22.44)</t>
+          <t>(16.35, 28.89)</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -12730,52 +12730,52 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>(99.23, 228.65)</t>
+          <t>(127.7, 294.24)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>(53.57, 123.44)</t>
+          <t>(68.94, 158.86)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>(35.8, 82.49)</t>
+          <t>(46.07, 106.16)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>(26.53, 61.13)</t>
+          <t>(34.15, 78.68)</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(20.9, 48.16)</t>
+          <t>(26.9, 61.99)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>(17.15, 39.51)</t>
+          <t>(22.07, 50.86)</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>(14.48, 33.36)</t>
+          <t>(18.64, 42.94)</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>(12.49, 28.78)</t>
+          <t>(16.08, 37.05)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>(10.96, 25.25)</t>
+          <t>(14.1, 32.5)</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>(9.74, 22.44)</t>
+          <t>(12.54, 28.89)</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -12798,52 +12798,52 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>(54.31, 81.62)</t>
+          <t>(69.89, 105.04)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>(29.32, 44.06)</t>
+          <t>(37.73, 56.71)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>(19.59, 29.45)</t>
+          <t>(25.22, 37.9)</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>(14.52, 21.82)</t>
+          <t>(18.69, 28.09)</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(11.44, 17.19)</t>
+          <t>(14.72, 22.13)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>(9.39, 14.11)</t>
+          <t>(12.08, 18.15)</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>(7.92, 11.91)</t>
+          <t>(10.2, 15.33)</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>(6.84, 10.27)</t>
+          <t>(8.8, 13.22)</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>(6.0, 9.01)</t>
+          <t>(7.72, 11.6)</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>(5.33, 8.01)</t>
+          <t>(6.86, 10.31)</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -12866,52 +12866,52 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>(27.31, 81.62)</t>
+          <t>(35.15, 105.04)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>(14.74, 44.06)</t>
+          <t>(18.98, 56.71)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>(9.85, 29.45)</t>
+          <t>(12.68, 37.9)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>(7.3, 21.82)</t>
+          <t>(9.4, 28.09)</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(5.75, 17.19)</t>
+          <t>(7.4, 22.13)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>(4.72, 14.11)</t>
+          <t>(6.07, 18.15)</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>(3.99, 11.91)</t>
+          <t>(5.13, 15.33)</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>(3.44, 10.27)</t>
+          <t>(4.43, 13.22)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>(3.02, 9.01)</t>
+          <t>(3.88, 11.6)</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>(2.68, 8.01)</t>
+          <t>(3.45, 10.31)</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -12934,52 +12934,52 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>(147.4, 149.96)</t>
+          <t>(189.68, 192.99)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>(79.57, 80.96)</t>
+          <t>(102.41, 104.19)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>(53.17, 54.1)</t>
+          <t>(68.44, 69.63)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>(39.41, 40.09)</t>
+          <t>(50.72, 51.6)</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(31.05, 31.59)</t>
+          <t>(39.96, 40.66)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>(25.47, 25.92)</t>
+          <t>(32.78, 33.36)</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>(21.51, 21.88)</t>
+          <t>(27.68, 28.16)</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>(18.55, 18.88)</t>
+          <t>(23.88, 24.3)</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>(16.28, 16.56)</t>
+          <t>(20.95, 21.31)</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>(14.47, 14.72)</t>
+          <t>(18.62, 18.95)</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -13002,52 +13002,52 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>(2.57, 149.96)</t>
+          <t>(3.31, 192.99)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>(1.39, 80.96)</t>
+          <t>(1.78, 104.19)</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>(0.93, 54.1)</t>
+          <t>(1.19, 69.63)</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>(0.69, 40.09)</t>
+          <t>(0.88, 51.6)</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(0.54, 31.59)</t>
+          <t>(0.7, 40.66)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>(0.44, 25.92)</t>
+          <t>(0.57, 33.36)</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>(0.37, 21.88)</t>
+          <t>(0.48, 28.16)</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>(0.32, 18.88)</t>
+          <t>(0.42, 24.3)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>(0.28, 16.56)</t>
+          <t>(0.37, 21.31)</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>(0.25, 14.72)</t>
+          <t>(0.32, 18.95)</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -13070,52 +13070,52 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>(55.06, 94.67)</t>
+          <t>(70.86, 121.82)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>(29.73, 51.11)</t>
+          <t>(38.26, 65.77)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>(19.86, 34.15)</t>
+          <t>(25.57, 43.95)</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>(14.72, 25.31)</t>
+          <t>(18.95, 32.57)</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(11.6, 19.94)</t>
+          <t>(14.93, 25.66)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>(9.52, 16.36)</t>
+          <t>(12.25, 21.06)</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>(8.03, 13.81)</t>
+          <t>(10.34, 17.78)</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>(6.93, 11.92)</t>
+          <t>(8.92, 15.34)</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>(6.08, 10.45)</t>
+          <t>(7.83, 13.45)</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>(5.4, 9.29)</t>
+          <t>(6.96, 11.96)</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -13138,52 +13138,52 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>(39.6, 94.67)</t>
+          <t>(50.97, 121.82)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>(21.38, 51.11)</t>
+          <t>(27.52, 65.77)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>(14.29, 34.15)</t>
+          <t>(18.39, 43.95)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>(10.59, 25.31)</t>
+          <t>(13.63, 32.57)</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(8.34, 19.94)</t>
+          <t>(10.74, 25.66)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>(6.84, 16.36)</t>
+          <t>(8.81, 21.06)</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>(5.78, 13.81)</t>
+          <t>(7.44, 17.78)</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>(4.99, 11.92)</t>
+          <t>(6.42, 15.34)</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>(4.37, 10.45)</t>
+          <t>(5.63, 13.45)</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>(3.89, 9.29)</t>
+          <t>(5.0, 11.96)</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -13206,52 +13206,52 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>(201.18, 287.63)</t>
+          <t>(258.89, 370.15)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>(108.61, 155.28)</t>
+          <t>(139.78, 199.84)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>(72.58, 103.77)</t>
+          <t>(93.41, 133.55)</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>(53.79, 76.9)</t>
+          <t>(69.23, 98.97)</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(42.38, 60.59)</t>
+          <t>(54.54, 77.98)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>(34.77, 49.71)</t>
+          <t>(44.75, 63.98)</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>(29.36, 41.97)</t>
+          <t>(37.78, 54.02)</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>(25.32, 36.21)</t>
+          <t>(32.6, 46.6)</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>(22.21, 31.76)</t>
+          <t>(28.59, 40.88)</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>(19.75, 28.23)</t>
+          <t>(25.42, 36.34)</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -13274,52 +13274,52 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>(86.45, 287.63)</t>
+          <t>(111.25, 370.15)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>(46.67, 155.28)</t>
+          <t>(60.07, 199.84)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>(31.19, 103.77)</t>
+          <t>(40.14, 133.55)</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>(23.11, 76.9)</t>
+          <t>(29.75, 98.97)</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(18.21, 60.59)</t>
+          <t>(23.44, 77.98)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>(14.94, 49.71)</t>
+          <t>(19.23, 63.98)</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>(12.61, 41.97)</t>
+          <t>(16.24, 54.02)</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>(10.88, 36.21)</t>
+          <t>(14.01, 46.6)</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>(9.55, 31.76)</t>
+          <t>(12.29, 40.88)</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>(8.49, 28.23)</t>
+          <t>(10.92, 36.34)</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -13342,52 +13342,52 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>(142.6, 157.38)</t>
+          <t>(183.51, 202.52)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>(76.98, 84.96)</t>
+          <t>(99.07, 109.34)</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>(51.44, 56.78)</t>
+          <t>(66.21, 73.07)</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>(38.12, 42.08)</t>
+          <t>(49.07, 54.15)</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(30.04, 33.15)</t>
+          <t>(38.66, 42.67)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>(24.64, 27.2)</t>
+          <t>(31.72, 35.0)</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>(20.81, 22.96)</t>
+          <t>(26.78, 29.56)</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>(17.95, 19.81)</t>
+          <t>(23.1, 25.5)</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>(15.75, 17.38)</t>
+          <t>(20.27, 22.37)</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>(14.0, 15.45)</t>
+          <t>(18.02, 19.88)</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -13410,52 +13410,52 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>(14.78, 157.38)</t>
+          <t>(19.02, 202.52)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>(7.98, 84.96)</t>
+          <t>(10.27, 109.34)</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>(5.33, 56.78)</t>
+          <t>(6.86, 73.07)</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>(3.95, 42.08)</t>
+          <t>(5.08, 54.15)</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(3.11, 33.15)</t>
+          <t>(4.01, 42.67)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>(2.55, 27.2)</t>
+          <t>(3.29, 35.0)</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>(2.16, 22.96)</t>
+          <t>(2.78, 29.56)</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>(1.86, 19.81)</t>
+          <t>(2.39, 25.5)</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>(1.63, 17.38)</t>
+          <t>(2.1, 22.37)</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>(1.45, 15.45)</t>
+          <t>(1.87, 19.88)</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -13478,52 +13478,52 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>(172.61, 232.4)</t>
+          <t>(222.13, 299.07)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>(93.19, 125.46)</t>
+          <t>(119.93, 161.46)</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>(62.27, 83.84)</t>
+          <t>(80.15, 107.9)</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>(46.15, 62.13)</t>
+          <t>(59.4, 79.97)</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(36.36, 48.95)</t>
+          <t>(46.8, 63.0)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>(29.83, 40.16)</t>
+          <t>(38.39, 51.69)</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>(25.19, 33.91)</t>
+          <t>(32.42, 43.65)</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>(21.73, 29.25)</t>
+          <t>(27.97, 37.65)</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>(19.06, 25.66)</t>
+          <t>(24.53, 33.03)</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>(16.94, 22.81)</t>
+          <t>(21.81, 29.36)</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -13546,52 +13546,52 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>(59.79, 232.4)</t>
+          <t>(76.94, 299.07)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>(32.28, 125.46)</t>
+          <t>(41.54, 161.46)</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>(21.57, 83.84)</t>
+          <t>(27.76, 107.9)</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>(15.98, 62.13)</t>
+          <t>(20.57, 79.97)</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(12.59, 48.95)</t>
+          <t>(16.21, 63.0)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>(10.33, 40.16)</t>
+          <t>(13.3, 51.69)</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>(8.72, 33.91)</t>
+          <t>(11.23, 43.65)</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>(7.53, 29.25)</t>
+          <t>(9.69, 37.65)</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>(6.6, 25.66)</t>
+          <t>(8.5, 33.03)</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>(5.87, 22.81)</t>
+          <t>(7.55, 29.36)</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -13614,52 +13614,52 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>(7.74, 70.92)</t>
+          <t>(9.96, 91.27)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>(4.18, 38.29)</t>
+          <t>(5.38, 49.28)</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>(2.79, 25.59)</t>
+          <t>(3.59, 32.93)</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>(2.07, 18.96)</t>
+          <t>(2.66, 24.4)</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(1.63, 14.94)</t>
+          <t>(2.1, 19.23)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>(1.34, 12.26)</t>
+          <t>(1.72, 15.78)</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>(1.13, 10.35)</t>
+          <t>(1.45, 13.32)</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>(0.97, 8.93)</t>
+          <t>(1.25, 11.49)</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>(0.85, 7.83)</t>
+          <t>(1.1, 10.08)</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>(0.76, 6.96)</t>
+          <t>(0.98, 8.96)</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -13682,52 +13682,52 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>(54.8, 70.92)</t>
+          <t>(70.53, 91.27)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>(29.59, 38.29)</t>
+          <t>(38.08, 49.28)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>(19.77, 25.59)</t>
+          <t>(25.45, 32.93)</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>(14.65, 18.96)</t>
+          <t>(18.86, 24.4)</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(11.54, 14.94)</t>
+          <t>(14.86, 19.23)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>(9.47, 12.26)</t>
+          <t>(12.19, 15.78)</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>(8.0, 10.35)</t>
+          <t>(10.29, 13.32)</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>(6.9, 8.93)</t>
+          <t>(8.88, 11.49)</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>(6.05, 7.83)</t>
+          <t>(7.79, 10.08)</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>(5.38, 6.96)</t>
+          <t>(6.92, 8.96)</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -13750,52 +13750,52 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>(18.64, 121.82)</t>
+          <t>(23.99, 156.76)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>(10.06, 65.76)</t>
+          <t>(12.95, 84.64)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>(6.73, 43.95)</t>
+          <t>(8.66, 56.56)</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>(4.98, 32.57)</t>
+          <t>(6.41, 41.92)</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(3.93, 25.66)</t>
+          <t>(5.05, 33.03)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>(3.22, 21.05)</t>
+          <t>(4.15, 27.1)</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>(2.72, 17.78)</t>
+          <t>(3.5, 22.88)</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>(2.35, 15.33)</t>
+          <t>(3.02, 19.74)</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>(2.06, 13.45)</t>
+          <t>(2.65, 17.31)</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>(1.83, 11.96)</t>
+          <t>(2.36, 15.39)</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -13818,52 +13818,52 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>(103.17, 121.82)</t>
+          <t>(132.77, 156.76)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>(55.7, 65.76)</t>
+          <t>(71.68, 84.64)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>(37.22, 43.95)</t>
+          <t>(47.9, 56.56)</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>(27.58, 32.57)</t>
+          <t>(35.5, 41.92)</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(21.73, 25.66)</t>
+          <t>(27.97, 33.03)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>(17.83, 21.05)</t>
+          <t>(22.95, 27.1)</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>(15.05, 17.78)</t>
+          <t>(19.38, 22.88)</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>(12.99, 15.33)</t>
+          <t>(16.72, 19.74)</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>(11.39, 13.45)</t>
+          <t>(14.66, 17.31)</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>(10.13, 11.96)</t>
+          <t>(13.03, 15.39)</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -13886,52 +13886,52 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>(41.15, 237.26)</t>
+          <t>(52.96, 305.33)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>(22.22, 128.09)</t>
+          <t>(28.59, 164.85)</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>(14.85, 85.6)</t>
+          <t>(19.11, 110.16)</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>(11.0, 63.43)</t>
+          <t>(14.16, 81.64)</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(8.67, 49.98)</t>
+          <t>(11.16, 64.32)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>(7.11, 41.0)</t>
+          <t>(9.15, 52.77)</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>(6.0, 34.62)</t>
+          <t>(7.73, 44.56)</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>(5.18, 29.87)</t>
+          <t>(6.67, 38.44)</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>(4.54, 26.2)</t>
+          <t>(5.85, 33.72)</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>(4.04, 23.29)</t>
+          <t>(5.2, 29.98)</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -13954,52 +13954,52 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>(196.11, 237.26)</t>
+          <t>(252.37, 305.33)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>(105.87, 128.09)</t>
+          <t>(136.26, 164.85)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>(70.75, 85.6)</t>
+          <t>(91.06, 110.16)</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>(52.43, 63.43)</t>
+          <t>(67.48, 81.64)</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(41.31, 49.98)</t>
+          <t>(53.17, 64.32)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>(33.89, 41.0)</t>
+          <t>(43.62, 52.77)</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>(28.62, 34.62)</t>
+          <t>(36.83, 44.56)</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>(24.69, 29.87)</t>
+          <t>(31.77, 38.44)</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>(21.66, 26.2)</t>
+          <t>(27.87, 33.72)</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>(19.25, 23.29)</t>
+          <t>(24.78, 29.98)</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -14022,52 +14022,52 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>(0.0, 123.35)</t>
+          <t>(0.0, 158.74)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>(0.0, 66.59)</t>
+          <t>(0.0, 85.7)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>(0.0, 44.5)</t>
+          <t>(0.0, 57.27)</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>(0.0, 32.98)</t>
+          <t>(0.0, 42.45)</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(0.0, 25.98)</t>
+          <t>(0.0, 33.44)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>(0.0, 21.32)</t>
+          <t>(0.0, 27.44)</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>(0.0, 18.0)</t>
+          <t>(0.0, 23.17)</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>(0.0, 15.53)</t>
+          <t>(0.0, 19.99)</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>(0.0, 13.62)</t>
+          <t>(0.0, 17.53)</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>(0.0, 12.11)</t>
+          <t>(0.0, 15.58)</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -14090,52 +14090,52 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>(0.0, 123.35)</t>
+          <t>(0.0, 158.74)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>(0.0, 66.59)</t>
+          <t>(0.0, 85.7)</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>(0.0, 44.5)</t>
+          <t>(0.0, 57.27)</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>(0.0, 32.98)</t>
+          <t>(0.0, 42.45)</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(0.0, 25.98)</t>
+          <t>(0.0, 33.44)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>(0.0, 21.32)</t>
+          <t>(0.0, 27.44)</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>(0.0, 18.0)</t>
+          <t>(0.0, 23.17)</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>(0.0, 15.53)</t>
+          <t>(0.0, 19.99)</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>(0.0, 13.62)</t>
+          <t>(0.0, 17.53)</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>(0.0, 12.11)</t>
+          <t>(0.0, 15.58)</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -16363,25 +16363,25 @@
         <v>0.01824146924750992</v>
       </c>
       <c r="E2" t="n">
-        <v>31.02154776701866</v>
+        <v>31.02154776701865</v>
       </c>
       <c r="F2" t="n">
-        <v>2680.261727070412</v>
+        <v>2680.261727070411</v>
       </c>
       <c r="G2" t="n">
-        <v>1.200427598925421</v>
+        <v>1.457662084409439</v>
       </c>
       <c r="H2" t="n">
         <v>2.9348865911421</v>
       </c>
       <c r="I2" t="n">
-        <v>1824676.826353009</v>
+        <v>2547279.289764409</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01538535729238877</v>
+        <v>0.01526095200714532</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6421900859217268</v>
+        <v>0.8264256458975006</v>
       </c>
     </row>
     <row r="3">
@@ -16400,25 +16400,25 @@
         <v>0.05067074790974978</v>
       </c>
       <c r="E3" t="n">
-        <v>86.17096601949629</v>
+        <v>86.17096601949626</v>
       </c>
       <c r="F3" t="n">
-        <v>7445.17146408448</v>
+        <v>7445.171464084477</v>
       </c>
       <c r="G3" t="n">
-        <v>1.200427598925421</v>
+        <v>1.457662084409439</v>
       </c>
       <c r="H3" t="n">
-        <v>8.152462753172506</v>
+        <v>8.152462753172502</v>
       </c>
       <c r="I3" t="n">
-        <v>3041128.043921682</v>
+        <v>4245465.482940682</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01384316824346184</v>
+        <v>0.01373215657536467</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3466911519082727</v>
+        <v>0.4461821134899511</v>
       </c>
     </row>
     <row r="4">
@@ -16437,25 +16437,25 @@
         <v>0.09931466590310954</v>
       </c>
       <c r="E4" t="n">
-        <v>168.8950933982127</v>
+        <v>168.8950933982126</v>
       </c>
       <c r="F4" t="n">
-        <v>14592.53606960558</v>
+        <v>14592.53606960557</v>
       </c>
       <c r="G4" t="n">
-        <v>1.200427598925421</v>
+        <v>1.457662084409439</v>
       </c>
       <c r="H4" t="n">
-        <v>15.97882699621811</v>
+        <v>15.9788269962181</v>
       </c>
       <c r="I4" t="n">
-        <v>4257579.261490354</v>
+        <v>5943651.676116955</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01295112329939843</v>
+        <v>0.0128476948598514</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2316789963626576</v>
+        <v>0.2981745601793407</v>
       </c>
     </row>
     <row r="5">
@@ -16480,19 +16480,19 @@
         <v>24122.35554363371</v>
       </c>
       <c r="G5" t="n">
-        <v>1.200427598925421</v>
+        <v>1.457662084409439</v>
       </c>
       <c r="H5" t="n">
         <v>26.41397932027891</v>
       </c>
       <c r="I5" t="n">
-        <v>5474030.479059028</v>
+        <v>7641837.869293228</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01234015035010719</v>
+        <v>0.01224184464939308</v>
       </c>
       <c r="K5" t="n">
-        <v>0.171694034854443</v>
+        <v>0.2209773537634847</v>
       </c>
     </row>
     <row r="6">
@@ -16511,25 +16511,25 @@
         <v>0.2452464198831888</v>
       </c>
       <c r="E6" t="n">
-        <v>417.067475534362</v>
+        <v>417.0674755343618</v>
       </c>
       <c r="F6" t="n">
-        <v>36034.62988616887</v>
+        <v>36034.62988616886</v>
       </c>
       <c r="G6" t="n">
-        <v>1.200427598925421</v>
+        <v>1.457662084409439</v>
       </c>
       <c r="H6" t="n">
-        <v>39.45791972535492</v>
+        <v>39.45791972535491</v>
       </c>
       <c r="I6" t="n">
-        <v>6690481.6966277</v>
+        <v>9340024.062469501</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0118829494532778</v>
+        <v>0.01178843874176854</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1352722861220867</v>
+        <v>0.1741033068053998</v>
       </c>
     </row>
     <row r="7">
@@ -16548,25 +16548,25 @@
         <v>0.3425342558699084</v>
       </c>
       <c r="E7" t="n">
-        <v>582.5157302917949</v>
+        <v>582.5157302917946</v>
       </c>
       <c r="F7" t="n">
-        <v>50329.35909721108</v>
+        <v>50329.35909721105</v>
       </c>
       <c r="G7" t="n">
-        <v>1.200427598925421</v>
+        <v>1.457662084409439</v>
       </c>
       <c r="H7" t="n">
-        <v>55.11064821144612</v>
+        <v>55.1106482114461</v>
       </c>
       <c r="I7" t="n">
-        <v>7906932.914196372</v>
+        <v>11038210.25564577</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01152153335738611</v>
+        <v>0.01142999900920052</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1109798655573259</v>
+        <v>0.142838820218025</v>
       </c>
     </row>
     <row r="8">
@@ -16585,25 +16585,25 @@
         <v>0.456036731187748</v>
       </c>
       <c r="E8" t="n">
-        <v>775.5386941754667</v>
+        <v>775.5386941754664</v>
       </c>
       <c r="F8" t="n">
-        <v>67006.54317676033</v>
+        <v>67006.5431767603</v>
       </c>
       <c r="G8" t="n">
-        <v>1.200427598925421</v>
+        <v>1.457662084409439</v>
       </c>
       <c r="H8" t="n">
-        <v>73.37216477855256</v>
+        <v>73.37216477855253</v>
       </c>
       <c r="I8" t="n">
-        <v>9123384.131765045</v>
+        <v>12736396.44882205</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01122495372138249</v>
+        <v>0.01113584610178152</v>
       </c>
       <c r="K8" t="n">
-        <v>0.09370668302085056</v>
+        <v>0.1206077943626459</v>
       </c>
     </row>
     <row r="9">
@@ -16622,25 +16622,25 @@
         <v>0.5857538458367073</v>
       </c>
       <c r="E9" t="n">
-        <v>996.1363671853769</v>
+        <v>996.1363671853766</v>
       </c>
       <c r="F9" t="n">
-        <v>86066.18212481657</v>
+        <v>86066.18212481654</v>
       </c>
       <c r="G9" t="n">
-        <v>1.200427598925421</v>
+        <v>1.457662084409439</v>
       </c>
       <c r="H9" t="n">
-        <v>94.24246942667413</v>
+        <v>94.24246942667411</v>
       </c>
       <c r="I9" t="n">
-        <v>10339835.34933372</v>
+        <v>14434582.64199832</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01097488494094747</v>
+        <v>0.01088781240816079</v>
       </c>
       <c r="K9" t="n">
-        <v>0.08084037503130398</v>
+        <v>0.1040483319506292</v>
       </c>
     </row>
     <row r="10">
@@ -16662,22 +16662,22 @@
         <v>1244.308749321526</v>
       </c>
       <c r="F10" t="n">
-        <v>107508.2759413799</v>
+        <v>107508.2759413798</v>
       </c>
       <c r="G10" t="n">
-        <v>1.200427598925421</v>
+        <v>1.457662084409439</v>
       </c>
       <c r="H10" t="n">
-        <v>117.721562155811</v>
+        <v>117.7215621558109</v>
       </c>
       <c r="I10" t="n">
-        <v>11556286.56690239</v>
+        <v>16132768.83517459</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01075964427718696</v>
+        <v>0.01067431523357295</v>
       </c>
       <c r="K10" t="n">
-        <v>0.07091230096464102</v>
+        <v>0.09127037550291132</v>
       </c>
     </row>
     <row r="11">
@@ -16702,19 +16702,19 @@
         <v>131332.8246264502</v>
       </c>
       <c r="G11" t="n">
-        <v>1.200427598925421</v>
+        <v>1.457662084409439</v>
       </c>
       <c r="H11" t="n">
         <v>143.8094429659629</v>
       </c>
       <c r="I11" t="n">
-        <v>12772737.78447106</v>
+        <v>17830955.02835086</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01057136006073237</v>
+        <v>0.01048754992900408</v>
       </c>
       <c r="K11" t="n">
-        <v>0.06303602738903012</v>
+        <v>0.08113311691453198</v>
       </c>
     </row>
   </sheetData>
